--- a/plantillas/eventos.xlsx
+++ b/plantillas/eventos.xlsx
@@ -13510,61 +13510,73 @@
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>ev-009</t>
+          <t>ev-257</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento</t>
-        </is>
-      </c>
-      <c r="C168" s="3" t="inlineStr"/>
-      <c r="D168" s="4" t="inlineStr"/>
-      <c r="E168" s="3" t="inlineStr"/>
+          <t>periodistas</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>periodista</t>
+        </is>
+      </c>
+      <c r="D168" s="4" t="inlineStr">
+        <is>
+          <t>desaparicion</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="inlineStr">
+        <is>
+          <t>masculino</t>
+        </is>
+      </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento masivo</t>
+          <t>desaparición de periodista</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2021-03-10</t>
         </is>
       </c>
       <c r="H168" s="3" t="n">
-        <v>22.647</v>
+        <v>29.4124</v>
       </c>
       <c r="I168" s="3" t="n">
-        <v>-102.994</v>
+        <v>-110.5518</v>
       </c>
       <c r="J168" s="5" t="inlineStr">
         <is>
-          <t>Sierra de Jerez, Zacatecas</t>
+          <t>Sonora</t>
         </is>
       </c>
       <c r="K168" s="5" t="inlineStr">
         <is>
-          <t>Más de 2 mil 500 personas desplazadas de comunidades serranas de Jerez</t>
+          <t>Desaparición de Jorge Molontzin Centlal, El Confidencial</t>
         </is>
       </c>
       <c r="L168" s="5" t="inlineStr">
         <is>
-          <t>La pugna entre el CJNG y el Cártel de Sinaloa obligó a dejar sus hogares a más de 2 mil 500 personas de comunidades como Palmas Altas, Sarabia y Sauz de los García; las viviendas abandonadas fueron ocupadas como centros de operación criminal. Ubicación aproximada (cabecera de Jerez).</t>
+          <t>Registro número 28 de periodistas desaparecidos en relación con su labor informativa, según ARTICLE 19. Medio: El Confidencial. Sexo: Masculino. Sexenio: AMLO. Ubicación aproximada (centro de la entidad).</t>
         </is>
       </c>
       <c r="M168" s="3" t="inlineStr">
         <is>
-          <t>razon</t>
+          <t>article19</t>
         </is>
       </c>
       <c r="N168" s="3" t="inlineStr">
         <is>
-          <t>https://www.razon.com.mx/estados/2026/09/23/crimen-parte-familias-zacatecas-morelos-queretaro-colima-con-mas-desplazados/</t>
+          <t>https://articulo19.org/periodistasdesaparecidos/</t>
         </is>
       </c>
       <c r="O168" s="3" t="inlineStr">
         <is>
-          <t>prensa</t>
+          <t>organización</t>
         </is>
       </c>
       <c r="P168" s="3" t="inlineStr">
@@ -13576,7 +13588,7 @@
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>ev-257</t>
+          <t>ev-215</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -13591,7 +13603,7 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>desaparicion</t>
+          <t>asesinato</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
@@ -13601,12 +13613,12 @@
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>desaparición de periodista</t>
+          <t>asesinato de periodista</t>
         </is>
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2021-03-10</t>
+          <t>2021-05-03</t>
         </is>
       </c>
       <c r="H169" s="3" t="n">
@@ -13622,12 +13634,12 @@
       </c>
       <c r="K169" s="5" t="inlineStr">
         <is>
-          <t>Desaparición de Jorge Molontzin Centlal, El Confidencial</t>
+          <t>Asesinato de Benjamín Morales Hernández, Noticias Xonoidag</t>
         </is>
       </c>
       <c r="L169" s="5" t="inlineStr">
         <is>
-          <t>Registro número 28 de periodistas desaparecidos en relación con su labor informativa, según ARTICLE 19. Medio: El Confidencial. Sexo: Masculino. Sexenio: AMLO. Ubicación aproximada (centro de la entidad).</t>
+          <t>Registro número 140 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: Noticias Xonoidag. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
         </is>
       </c>
       <c r="M169" s="3" t="inlineStr">
@@ -13637,7 +13649,7 @@
       </c>
       <c r="N169" s="3" t="inlineStr">
         <is>
-          <t>https://articulo19.org/periodistasdesaparecidos/</t>
+          <t>https://articulo19.org/periodistasasesinados/</t>
         </is>
       </c>
       <c r="O169" s="3" t="inlineStr">
@@ -13654,7 +13666,7 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>ev-215</t>
+          <t>ev-214</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -13684,28 +13696,28 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2021-05-03</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="H170" s="3" t="n">
-        <v>29.4124</v>
+        <v>17.1696</v>
       </c>
       <c r="I170" s="3" t="n">
-        <v>-110.5518</v>
+        <v>-96.3472</v>
       </c>
       <c r="J170" s="5" t="inlineStr">
         <is>
-          <t>Sonora</t>
+          <t>Oaxaca</t>
         </is>
       </c>
       <c r="K170" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Benjamín Morales Hernández, Noticias Xonoidag</t>
+          <t>Asesinato de Gustavo Sánchez Cabrera, Noticias Minuto a Minuto</t>
         </is>
       </c>
       <c r="L170" s="5" t="inlineStr">
         <is>
-          <t>Registro número 140 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: Noticias Xonoidag. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
+          <t>Registro número 141 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: Noticias Minuto a Minuto. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
         </is>
       </c>
       <c r="M170" s="3" t="inlineStr">
@@ -13732,7 +13744,7 @@
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>ev-214</t>
+          <t>ev-213</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -13762,28 +13774,28 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="H171" s="3" t="n">
-        <v>17.1696</v>
+        <v>27.2043</v>
       </c>
       <c r="I171" s="3" t="n">
-        <v>-96.3472</v>
+        <v>-102.3112</v>
       </c>
       <c r="J171" s="5" t="inlineStr">
         <is>
-          <t>Oaxaca</t>
+          <t>Coahuila</t>
         </is>
       </c>
       <c r="K171" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Gustavo Sánchez Cabrera, Noticias Minuto a Minuto</t>
+          <t>Asesinato de Saúl Tijerina Rentería, Noticias en la Web</t>
         </is>
       </c>
       <c r="L171" s="5" t="inlineStr">
         <is>
-          <t>Registro número 141 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: Noticias Minuto a Minuto. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
+          <t>Registro número 142 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: Noticias en la Web. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
         </is>
       </c>
       <c r="M171" s="3" t="inlineStr">
@@ -13810,7 +13822,7 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>ev-213</t>
+          <t>ev-212</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -13840,28 +13852,28 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2021-06-22</t>
+          <t>2021-07-22</t>
         </is>
       </c>
       <c r="H172" s="3" t="n">
-        <v>27.2043</v>
+        <v>29.4124</v>
       </c>
       <c r="I172" s="3" t="n">
-        <v>-102.3112</v>
+        <v>-110.5518</v>
       </c>
       <c r="J172" s="5" t="inlineStr">
         <is>
-          <t>Coahuila</t>
+          <t>Sonora</t>
         </is>
       </c>
       <c r="K172" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Saúl Tijerina Rentería, Noticias en la Web</t>
+          <t>Asesinato de Ricardo López Domínguez, Infoguaymas</t>
         </is>
       </c>
       <c r="L172" s="5" t="inlineStr">
         <is>
-          <t>Registro número 142 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: Noticias en la Web. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
+          <t>Registro número 143 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: Infoguaymas. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
         </is>
       </c>
       <c r="M172" s="3" t="inlineStr">
@@ -13888,7 +13900,7 @@
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>ev-212</t>
+          <t>ev-211</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -13918,28 +13930,28 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2021-07-22</t>
+          <t>2021-08-19</t>
         </is>
       </c>
       <c r="H173" s="3" t="n">
-        <v>29.4124</v>
+        <v>19.8095</v>
       </c>
       <c r="I173" s="3" t="n">
-        <v>-110.5518</v>
+        <v>-96.874</v>
       </c>
       <c r="J173" s="5" t="inlineStr">
         <is>
-          <t>Sonora</t>
+          <t>Veracruz</t>
         </is>
       </c>
       <c r="K173" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Ricardo López Domínguez, Infoguaymas</t>
+          <t>Asesinato de Jacinto Romero Flores, Ori Stereo</t>
         </is>
       </c>
       <c r="L173" s="5" t="inlineStr">
         <is>
-          <t>Registro número 143 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: Infoguaymas. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
+          <t>Registro número 144 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: Ori Stereo. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
         </is>
       </c>
       <c r="M173" s="3" t="inlineStr">
@@ -13966,7 +13978,7 @@
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>ev-211</t>
+          <t>ev-210</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -13996,28 +14008,28 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2021-08-19</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="H174" s="3" t="n">
-        <v>19.8095</v>
+        <v>16.2574</v>
       </c>
       <c r="I174" s="3" t="n">
-        <v>-96.874</v>
+        <v>-92.24550000000001</v>
       </c>
       <c r="J174" s="5" t="inlineStr">
         <is>
-          <t>Veracruz</t>
+          <t>Chiapas</t>
         </is>
       </c>
       <c r="K174" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Jacinto Romero Flores, Ori Stereo</t>
+          <t>Asesinato de Fredy López Arévalo, Revista Jovel</t>
         </is>
       </c>
       <c r="L174" s="5" t="inlineStr">
         <is>
-          <t>Registro número 144 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: Ori Stereo. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
+          <t>Registro número 145 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: Revista Jovel. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
         </is>
       </c>
       <c r="M174" s="3" t="inlineStr">
@@ -14044,7 +14056,7 @@
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>ev-210</t>
+          <t>ev-209</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -14074,28 +14086,28 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2021-10-28</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="H175" s="3" t="n">
-        <v>16.2574</v>
+        <v>17.6026</v>
       </c>
       <c r="I175" s="3" t="n">
-        <v>-92.24550000000001</v>
+        <v>-99.94929999999999</v>
       </c>
       <c r="J175" s="5" t="inlineStr">
         <is>
-          <t>Chiapas</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="K175" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Fredy López Arévalo, Revista Jovel</t>
+          <t>Asesinato de Alfredo Cardoso Echeverría, Las Dos Costas</t>
         </is>
       </c>
       <c r="L175" s="5" t="inlineStr">
         <is>
-          <t>Registro número 145 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: Revista Jovel. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
+          <t>Registro número 146 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: Las Dos Costas. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
         </is>
       </c>
       <c r="M175" s="3" t="inlineStr">
@@ -14122,7 +14134,7 @@
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>ev-209</t>
+          <t>ev-208</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -14152,28 +14164,28 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2022-01-10</t>
         </is>
       </c>
       <c r="H176" s="3" t="n">
-        <v>17.6026</v>
+        <v>19.8095</v>
       </c>
       <c r="I176" s="3" t="n">
-        <v>-99.94929999999999</v>
+        <v>-96.874</v>
       </c>
       <c r="J176" s="5" t="inlineStr">
         <is>
-          <t>Guerrero</t>
+          <t>Veracruz</t>
         </is>
       </c>
       <c r="K176" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Alfredo Cardoso Echeverría, Las Dos Costas</t>
+          <t>Asesinato de José Luis Arenas Gamboa, Inforegio Network</t>
         </is>
       </c>
       <c r="L176" s="5" t="inlineStr">
         <is>
-          <t>Registro número 146 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: Las Dos Costas. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
+          <t>Registro número 147 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: Inforegio Network. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
         </is>
       </c>
       <c r="M176" s="3" t="inlineStr">
@@ -14200,7 +14212,7 @@
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>ev-208</t>
+          <t>ev-207</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -14230,28 +14242,28 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2022-01-10</t>
+          <t>2022-01-17</t>
         </is>
       </c>
       <c r="H177" s="3" t="n">
-        <v>19.8095</v>
+        <v>30.3606</v>
       </c>
       <c r="I177" s="3" t="n">
-        <v>-96.874</v>
+        <v>-115.2467</v>
       </c>
       <c r="J177" s="5" t="inlineStr">
         <is>
-          <t>Veracruz</t>
+          <t>Baja California</t>
         </is>
       </c>
       <c r="K177" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de José Luis Arenas Gamboa, Inforegio Network</t>
+          <t>Asesinato de Margarito Martínez, freelance</t>
         </is>
       </c>
       <c r="L177" s="5" t="inlineStr">
         <is>
-          <t>Registro número 147 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: Inforegio Network. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
+          <t>Registro número 148 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: freelance. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
         </is>
       </c>
       <c r="M177" s="3" t="inlineStr">
@@ -14278,7 +14290,7 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>ev-207</t>
+          <t>ev-206</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -14298,7 +14310,7 @@
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>masculino</t>
+          <t>femenino</t>
         </is>
       </c>
       <c r="F178" s="3" t="inlineStr">
@@ -14308,7 +14320,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2022-01-17</t>
+          <t>2022-01-23</t>
         </is>
       </c>
       <c r="H178" s="3" t="n">
@@ -14324,12 +14336,12 @@
       </c>
       <c r="K178" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Margarito Martínez, freelance</t>
+          <t>Asesinato de Lourdes Maldonado López, Sintoniza Sin Censura</t>
         </is>
       </c>
       <c r="L178" s="5" t="inlineStr">
         <is>
-          <t>Registro número 148 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: freelance. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
+          <t>Registro número 149 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: Sintoniza Sin Censura. Sexo: femenino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
         </is>
       </c>
       <c r="M178" s="3" t="inlineStr">
@@ -14356,7 +14368,7 @@
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>ev-206</t>
+          <t>ev-205</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -14376,7 +14388,7 @@
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>femenino</t>
+          <t>masculino</t>
         </is>
       </c>
       <c r="F179" s="3" t="inlineStr">
@@ -14386,28 +14398,28 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2022-01-23</t>
+          <t>2022-01-31</t>
         </is>
       </c>
       <c r="H179" s="3" t="n">
-        <v>30.3606</v>
+        <v>19.1535</v>
       </c>
       <c r="I179" s="3" t="n">
-        <v>-115.2467</v>
+        <v>-101.6713</v>
       </c>
       <c r="J179" s="5" t="inlineStr">
         <is>
-          <t>Baja California</t>
+          <t>Michoacán</t>
         </is>
       </c>
       <c r="K179" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Lourdes Maldonado López, Sintoniza Sin Censura</t>
+          <t>Asesinato de Roberto Toledo, Monitor Michoacán</t>
         </is>
       </c>
       <c r="L179" s="5" t="inlineStr">
         <is>
-          <t>Registro número 149 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: Sintoniza Sin Censura. Sexo: femenino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
+          <t>Registro número 150 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: Monitor Michoacán. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
         </is>
       </c>
       <c r="M179" s="3" t="inlineStr">
@@ -14434,7 +14446,7 @@
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>ev-205</t>
+          <t>ev-204</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -14464,28 +14476,28 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2022-01-31</t>
+          <t>2022-02-10</t>
         </is>
       </c>
       <c r="H180" s="3" t="n">
-        <v>19.1535</v>
+        <v>17.1696</v>
       </c>
       <c r="I180" s="3" t="n">
-        <v>-101.6713</v>
+        <v>-96.3472</v>
       </c>
       <c r="J180" s="5" t="inlineStr">
         <is>
-          <t>Michoacán</t>
+          <t>Oaxaca</t>
         </is>
       </c>
       <c r="K180" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Roberto Toledo, Monitor Michoacán</t>
+          <t>Asesinato de Heber López Vázquez, Noticias web</t>
         </is>
       </c>
       <c r="L180" s="5" t="inlineStr">
         <is>
-          <t>Registro número 150 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: Monitor Michoacán. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
+          <t>Registro número 151 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: Noticias web. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
         </is>
       </c>
       <c r="M180" s="3" t="inlineStr">
@@ -14512,7 +14524,7 @@
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>ev-204</t>
+          <t>ev-253</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -14542,28 +14554,28 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2022-02-10</t>
+          <t>2022-02-24</t>
         </is>
       </c>
       <c r="H181" s="3" t="n">
-        <v>17.1696</v>
+        <v>29.4124</v>
       </c>
       <c r="I181" s="3" t="n">
-        <v>-96.3472</v>
+        <v>-110.5518</v>
       </c>
       <c r="J181" s="5" t="inlineStr">
         <is>
-          <t>Oaxaca</t>
+          <t>Sonora</t>
         </is>
       </c>
       <c r="K181" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Heber López Vázquez, Noticias web</t>
+          <t>Asesinato de Jorge Luis Camero Zazueta, El Informativo</t>
         </is>
       </c>
       <c r="L181" s="5" t="inlineStr">
         <is>
-          <t>Registro número 151 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: Noticias web. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
+          <t>Registro número 153 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: El Informativo. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
         </is>
       </c>
       <c r="M181" s="3" t="inlineStr">
@@ -14590,7 +14602,7 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>ev-253</t>
+          <t>ev-252</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -14620,28 +14632,28 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2022-02-24</t>
+          <t>2022-03-04</t>
         </is>
       </c>
       <c r="H182" s="3" t="n">
-        <v>29.4124</v>
+        <v>23.088</v>
       </c>
       <c r="I182" s="3" t="n">
-        <v>-110.5518</v>
+        <v>-103.2042</v>
       </c>
       <c r="J182" s="5" t="inlineStr">
         <is>
-          <t>Sonora</t>
+          <t>Zacatecas</t>
         </is>
       </c>
       <c r="K182" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Jorge Luis Camero Zazueta, El Informativo</t>
+          <t>Asesinato de Juan Carlos Muñiz, Testigo Minero</t>
         </is>
       </c>
       <c r="L182" s="5" t="inlineStr">
         <is>
-          <t>Registro número 153 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: El Informativo. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
+          <t>Registro número 152 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: Testigo Minero. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
         </is>
       </c>
       <c r="M182" s="3" t="inlineStr">
@@ -14668,7 +14680,7 @@
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>ev-252</t>
+          <t>ev-251</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -14698,28 +14710,28 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2022-03-04</t>
+          <t>2022-03-15</t>
         </is>
       </c>
       <c r="H183" s="3" t="n">
-        <v>23.088</v>
+        <v>19.1535</v>
       </c>
       <c r="I183" s="3" t="n">
-        <v>-103.2042</v>
+        <v>-101.6713</v>
       </c>
       <c r="J183" s="5" t="inlineStr">
         <is>
-          <t>Zacatecas</t>
+          <t>Michoacán</t>
         </is>
       </c>
       <c r="K183" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Juan Carlos Muñiz, Testigo Minero</t>
+          <t>Asesinato de Armando Linares López, Monitor Michoacán</t>
         </is>
       </c>
       <c r="L183" s="5" t="inlineStr">
         <is>
-          <t>Registro número 152 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: Testigo Minero. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
+          <t>Registro número 154 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: Monitor Michoacán. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
         </is>
       </c>
       <c r="M183" s="3" t="inlineStr">
@@ -14746,7 +14758,7 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>ev-251</t>
+          <t>ev-250</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -14776,28 +14788,28 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2022-03-15</t>
+          <t>2022-05-05</t>
         </is>
       </c>
       <c r="H184" s="3" t="n">
-        <v>19.1535</v>
+        <v>24.7581</v>
       </c>
       <c r="I184" s="3" t="n">
-        <v>-101.6713</v>
+        <v>-107.424</v>
       </c>
       <c r="J184" s="5" t="inlineStr">
         <is>
-          <t>Michoacán</t>
+          <t>Sinaloa</t>
         </is>
       </c>
       <c r="K184" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Armando Linares López, Monitor Michoacán</t>
+          <t>Asesinato de Luis Enrique Ramírez Ramos, El Debate, Fuentes Fidedignas</t>
         </is>
       </c>
       <c r="L184" s="5" t="inlineStr">
         <is>
-          <t>Registro número 154 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: Monitor Michoacán. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
+          <t>Registro número 155 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: El Debate, Fuentes Fidedignas. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
         </is>
       </c>
       <c r="M184" s="3" t="inlineStr">
@@ -14824,7 +14836,7 @@
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>ev-250</t>
+          <t>ev-249</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -14854,28 +14866,28 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2022-05-05</t>
+          <t>2022-06-29</t>
         </is>
       </c>
       <c r="H185" s="3" t="n">
-        <v>24.7581</v>
+        <v>24.9638</v>
       </c>
       <c r="I185" s="3" t="n">
-        <v>-107.424</v>
+        <v>-98.3567</v>
       </c>
       <c r="J185" s="5" t="inlineStr">
         <is>
-          <t>Sinaloa</t>
+          <t>Tamaulipas</t>
         </is>
       </c>
       <c r="K185" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Luis Enrique Ramírez Ramos, El Debate, Fuentes Fidedignas</t>
+          <t>Asesinato de Antonio de la Cruz, El Expreso</t>
         </is>
       </c>
       <c r="L185" s="5" t="inlineStr">
         <is>
-          <t>Registro número 155 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: El Debate, Fuentes Fidedignas. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
+          <t>Registro número 156 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: El Expreso. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
         </is>
       </c>
       <c r="M185" s="3" t="inlineStr">
@@ -14902,7 +14914,7 @@
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>ev-249</t>
+          <t>ev-248</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -14932,28 +14944,28 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2022-06-29</t>
+          <t>2022-08-11</t>
         </is>
       </c>
       <c r="H186" s="3" t="n">
-        <v>24.9638</v>
+        <v>28.7044</v>
       </c>
       <c r="I186" s="3" t="n">
-        <v>-98.3567</v>
+        <v>-106.0375</v>
       </c>
       <c r="J186" s="5" t="inlineStr">
         <is>
-          <t>Tamaulipas</t>
+          <t>Chihuahua</t>
         </is>
       </c>
       <c r="K186" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Antonio de la Cruz, El Expreso</t>
+          <t>Asesinato de Alan González, Radio Switch 105.9 FM</t>
         </is>
       </c>
       <c r="L186" s="5" t="inlineStr">
         <is>
-          <t>Registro número 156 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: El Expreso. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
+          <t>Registro número 157 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: Radio Switch 105.9 FM. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
         </is>
       </c>
       <c r="M186" s="3" t="inlineStr">
@@ -14980,7 +14992,7 @@
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>ev-248</t>
+          <t>ev-247</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -15010,28 +15022,28 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2022-08-11</t>
+          <t>2022-08-16</t>
         </is>
       </c>
       <c r="H187" s="3" t="n">
-        <v>28.7044</v>
+        <v>29.4124</v>
       </c>
       <c r="I187" s="3" t="n">
-        <v>-106.0375</v>
+        <v>-110.5518</v>
       </c>
       <c r="J187" s="5" t="inlineStr">
         <is>
-          <t>Chihuahua</t>
+          <t>Sonora</t>
         </is>
       </c>
       <c r="K187" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Alan González, Radio Switch 105.9 FM</t>
+          <t>Asesinato de Juan Arjón López, A qué le temes</t>
         </is>
       </c>
       <c r="L187" s="5" t="inlineStr">
         <is>
-          <t>Registro número 157 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: Radio Switch 105.9 FM. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
+          <t>Registro número 158 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: A qué le temes. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
         </is>
       </c>
       <c r="M187" s="3" t="inlineStr">
@@ -15058,7 +15070,7 @@
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>ev-247</t>
+          <t>ev-246</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -15088,28 +15100,28 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2022-08-16</t>
+          <t>2022-08-22</t>
         </is>
       </c>
       <c r="H188" s="3" t="n">
-        <v>29.4124</v>
+        <v>17.6026</v>
       </c>
       <c r="I188" s="3" t="n">
-        <v>-110.5518</v>
+        <v>-99.94929999999999</v>
       </c>
       <c r="J188" s="5" t="inlineStr">
         <is>
-          <t>Sonora</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="K188" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Juan Arjón López, A qué le temes</t>
+          <t>Asesinato de Fredid Román Román, Semanario La Realidad</t>
         </is>
       </c>
       <c r="L188" s="5" t="inlineStr">
         <is>
-          <t>Registro número 158 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: A qué le temes. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
+          <t>Registro número 159 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: Semanario La Realidad. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
         </is>
       </c>
       <c r="M188" s="3" t="inlineStr">
@@ -15136,7 +15148,7 @@
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>ev-246</t>
+          <t>ev-256</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -15151,7 +15163,7 @@
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>asesinato</t>
+          <t>desaparicion</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
@@ -15161,33 +15173,33 @@
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>asesinato de periodista</t>
+          <t>desaparición de periodista</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2022-08-22</t>
+          <t>2022-09-20</t>
         </is>
       </c>
       <c r="H189" s="3" t="n">
-        <v>17.6026</v>
+        <v>16.2574</v>
       </c>
       <c r="I189" s="3" t="n">
-        <v>-99.94929999999999</v>
+        <v>-92.24550000000001</v>
       </c>
       <c r="J189" s="5" t="inlineStr">
         <is>
-          <t>Guerrero</t>
+          <t>Chiapas</t>
         </is>
       </c>
       <c r="K189" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Fredid Román Román, Semanario La Realidad</t>
+          <t>Desaparición de Roberto Carlos Flores Mendoza, Chiapas Denuncia Ya</t>
         </is>
       </c>
       <c r="L189" s="5" t="inlineStr">
         <is>
-          <t>Registro número 159 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: Semanario La Realidad. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
+          <t>Registro número 29 de periodistas desaparecidos en relación con su labor informativa, según ARTICLE 19. Medio: Chiapas Denuncia Ya. Sexo: Masculino. Sexenio: AMLO. Ubicación aproximada (centro de la entidad).</t>
         </is>
       </c>
       <c r="M189" s="3" t="inlineStr">
@@ -15197,7 +15209,7 @@
       </c>
       <c r="N189" s="3" t="inlineStr">
         <is>
-          <t>https://articulo19.org/periodistasasesinados/</t>
+          <t>https://articulo19.org/periodistasdesaparecidos/</t>
         </is>
       </c>
       <c r="O189" s="3" t="inlineStr">
@@ -15214,7 +15226,7 @@
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>ev-256</t>
+          <t>ev-255</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -15244,28 +15256,28 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2022-09-20</t>
+          <t>2022-12-27</t>
         </is>
       </c>
       <c r="H190" s="3" t="n">
-        <v>16.2574</v>
+        <v>17.6026</v>
       </c>
       <c r="I190" s="3" t="n">
-        <v>-92.24550000000001</v>
+        <v>-99.94929999999999</v>
       </c>
       <c r="J190" s="5" t="inlineStr">
         <is>
-          <t>Chiapas</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="K190" s="5" t="inlineStr">
         <is>
-          <t>Desaparición de Roberto Carlos Flores Mendoza, Chiapas Denuncia Ya</t>
+          <t>Desaparición de Alan García Aguilar, Escenario Calentano</t>
         </is>
       </c>
       <c r="L190" s="5" t="inlineStr">
         <is>
-          <t>Registro número 29 de periodistas desaparecidos en relación con su labor informativa, según ARTICLE 19. Medio: Chiapas Denuncia Ya. Sexo: Masculino. Sexenio: AMLO. Ubicación aproximada (centro de la entidad).</t>
+          <t>Registro número 30 de periodistas desaparecidos en relación con su labor informativa, según ARTICLE 19. Medio: Escenario Calentano. Sexo: Masculino. Sexenio: AMLO. Ubicación aproximada (centro de la entidad).</t>
         </is>
       </c>
       <c r="M190" s="3" t="inlineStr">
@@ -15292,7 +15304,7 @@
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>ev-255</t>
+          <t>ev-245</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -15307,7 +15319,7 @@
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>desaparicion</t>
+          <t>asesinato</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
@@ -15317,33 +15329,33 @@
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>desaparición de periodista</t>
+          <t>asesinato de periodista</t>
         </is>
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2022-12-27</t>
+          <t>2023-05-23</t>
         </is>
       </c>
       <c r="H191" s="3" t="n">
-        <v>17.6026</v>
+        <v>19.345</v>
       </c>
       <c r="I191" s="3" t="n">
-        <v>-99.94929999999999</v>
+        <v>-97.4217</v>
       </c>
       <c r="J191" s="5" t="inlineStr">
         <is>
-          <t>Guerrero</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="K191" s="5" t="inlineStr">
         <is>
-          <t>Desaparición de Alan García Aguilar, Escenario Calentano</t>
+          <t>Asesinato de Marco Aurelio Ramirez Hernandez, Independiente</t>
         </is>
       </c>
       <c r="L191" s="5" t="inlineStr">
         <is>
-          <t>Registro número 30 de periodistas desaparecidos en relación con su labor informativa, según ARTICLE 19. Medio: Escenario Calentano. Sexo: Masculino. Sexenio: AMLO. Ubicación aproximada (centro de la entidad).</t>
+          <t>Registro número 160 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: Independiente. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
         </is>
       </c>
       <c r="M191" s="3" t="inlineStr">
@@ -15353,7 +15365,7 @@
       </c>
       <c r="N191" s="3" t="inlineStr">
         <is>
-          <t>https://articulo19.org/periodistasdesaparecidos/</t>
+          <t>https://articulo19.org/periodistasasesinados/</t>
         </is>
       </c>
       <c r="O191" s="3" t="inlineStr">
@@ -15370,61 +15382,73 @@
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>ev-010</t>
+          <t>ev-254</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento</t>
-        </is>
-      </c>
-      <c r="C192" s="3" t="inlineStr"/>
-      <c r="D192" s="4" t="inlineStr"/>
-      <c r="E192" s="3" t="inlineStr"/>
+          <t>periodistas</t>
+        </is>
+      </c>
+      <c r="C192" s="3" t="inlineStr">
+        <is>
+          <t>periodista</t>
+        </is>
+      </c>
+      <c r="D192" s="4" t="inlineStr">
+        <is>
+          <t>desaparicion</t>
+        </is>
+      </c>
+      <c r="E192" s="3" t="inlineStr">
+        <is>
+          <t>masculino</t>
+        </is>
+      </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento masivo</t>
+          <t>desaparición de periodista</t>
         </is>
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2023-05-01</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="H192" s="3" t="n">
-        <v>15.664</v>
+        <v>19.8095</v>
       </c>
       <c r="I192" s="3" t="n">
-        <v>-92.14</v>
+        <v>-96.874</v>
       </c>
       <c r="J192" s="5" t="inlineStr">
         <is>
-          <t>Frontera Comalapa, Chiapas</t>
+          <t>Veracruz</t>
         </is>
       </c>
       <c r="K192" s="5" t="inlineStr">
         <is>
-          <t>Unas 4 mil personas abandonan Frontera Comalapa en cinco días</t>
+          <t>Desaparición de Juan Carlos Hinojosa Viveros, La de 8News</t>
         </is>
       </c>
       <c r="L192" s="5" t="inlineStr">
         <is>
-          <t>Enfrentamientos entre el CJNG y el Cártel de Sinaloa por el corredor La Mesilla-Frontera Comalapa obligaron a unas 4 mil personas a dejar sus hogares en cinco días, según documentación del Frayba retomada por Infobae. Fecha aproximada (mayo de 2023). Ubicación aproximada (cabecera municipal).</t>
+          <t>Registro número 31 de periodistas desaparecidos en relación con su labor informativa, según ARTICLE 19. Medio: La de 8News. Sexo: Masculino. Sexenio: AMLO. Ubicación aproximada (centro de la entidad).</t>
         </is>
       </c>
       <c r="M192" s="3" t="inlineStr">
         <is>
-          <t>infobae</t>
+          <t>article19</t>
         </is>
       </c>
       <c r="N192" s="3" t="inlineStr">
         <is>
-          <t>https://www.infobae.com/mexico/2026/09/11/el-95-de-los-desplazados-regresa-a-chiapas-tras-operativos-contra-el-cartel-del-pacifico-el-cartel-de-chiapas-y-guatemala-y-el-cjng/</t>
+          <t>https://articulo19.org/periodistasdesaparecidos/</t>
         </is>
       </c>
       <c r="O192" s="3" t="inlineStr">
         <is>
-          <t>prensa</t>
+          <t>organización</t>
         </is>
       </c>
       <c r="P192" s="3" t="inlineStr">
@@ -15436,7 +15460,7 @@
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>ev-245</t>
+          <t>ev-244</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -15466,28 +15490,28 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2023-05-23</t>
+          <t>2023-07-07</t>
         </is>
       </c>
       <c r="H193" s="3" t="n">
-        <v>19.345</v>
+        <v>21.8316</v>
       </c>
       <c r="I193" s="3" t="n">
-        <v>-97.4217</v>
+        <v>-104.8633</v>
       </c>
       <c r="J193" s="5" t="inlineStr">
         <is>
-          <t>Puebla</t>
+          <t>Nayarit</t>
         </is>
       </c>
       <c r="K193" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Marco Aurelio Ramirez Hernandez, Independiente</t>
+          <t>Asesinato de Luis Martín Sánchez Íñiguez, La Jornada / Crítica ADN</t>
         </is>
       </c>
       <c r="L193" s="5" t="inlineStr">
         <is>
-          <t>Registro número 160 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: Independiente. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
+          <t>Registro número 161 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: La Jornada / Crítica ADN. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
         </is>
       </c>
       <c r="M193" s="3" t="inlineStr">
@@ -15514,7 +15538,7 @@
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>ev-254</t>
+          <t>ev-243</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -15529,7 +15553,7 @@
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>desaparicion</t>
+          <t>asesinato</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
@@ -15539,33 +15563,33 @@
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>desaparición de periodista</t>
+          <t>asesinato de periodista</t>
         </is>
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>2023-07-15</t>
         </is>
       </c>
       <c r="H194" s="3" t="n">
-        <v>19.8095</v>
+        <v>17.6026</v>
       </c>
       <c r="I194" s="3" t="n">
-        <v>-96.874</v>
+        <v>-99.94929999999999</v>
       </c>
       <c r="J194" s="5" t="inlineStr">
         <is>
-          <t>Veracruz</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="K194" s="5" t="inlineStr">
         <is>
-          <t>Desaparición de Juan Carlos Hinojosa Viveros, La de 8News</t>
+          <t>Asesinato de Nelson Matus Peña, Lo Real de Guerrero</t>
         </is>
       </c>
       <c r="L194" s="5" t="inlineStr">
         <is>
-          <t>Registro número 31 de periodistas desaparecidos en relación con su labor informativa, según ARTICLE 19. Medio: La de 8News. Sexo: Masculino. Sexenio: AMLO. Ubicación aproximada (centro de la entidad).</t>
+          <t>Registro número 162 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: Lo Real de Guerrero. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
         </is>
       </c>
       <c r="M194" s="3" t="inlineStr">
@@ -15575,7 +15599,7 @@
       </c>
       <c r="N194" s="3" t="inlineStr">
         <is>
-          <t>https://articulo19.org/periodistasdesaparecidos/</t>
+          <t>https://articulo19.org/periodistasasesinados/</t>
         </is>
       </c>
       <c r="O194" s="3" t="inlineStr">
@@ -15592,7 +15616,7 @@
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>ev-244</t>
+          <t>ev-242</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -15622,28 +15646,28 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2023-07-07</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="H195" s="3" t="n">
-        <v>21.8316</v>
+        <v>29.4124</v>
       </c>
       <c r="I195" s="3" t="n">
-        <v>-104.8633</v>
+        <v>-110.5518</v>
       </c>
       <c r="J195" s="5" t="inlineStr">
         <is>
-          <t>Nayarit</t>
+          <t>Sonora</t>
         </is>
       </c>
       <c r="K195" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Luis Martín Sánchez Íñiguez, La Jornada / Crítica ADN</t>
+          <t>Asesinato de Jesús Gutiérrez Vergara, Notiface Prensa Digital</t>
         </is>
       </c>
       <c r="L195" s="5" t="inlineStr">
         <is>
-          <t>Registro número 161 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: La Jornada / Crítica ADN. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
+          <t>Registro número 163 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: Notiface Prensa Digital. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
         </is>
       </c>
       <c r="M195" s="3" t="inlineStr">
@@ -15670,7 +15694,7 @@
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>ev-243</t>
+          <t>ev-241</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -15700,28 +15724,28 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2023-07-15</t>
+          <t>2023-11-16</t>
         </is>
       </c>
       <c r="H196" s="3" t="n">
-        <v>17.6026</v>
+        <v>28.7044</v>
       </c>
       <c r="I196" s="3" t="n">
-        <v>-99.94929999999999</v>
+        <v>-106.0375</v>
       </c>
       <c r="J196" s="5" t="inlineStr">
         <is>
-          <t>Guerrero</t>
+          <t>Chihuahua</t>
         </is>
       </c>
       <c r="K196" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Nelson Matus Peña, Lo Real de Guerrero</t>
+          <t>Asesinato de Ismael Villagómez Tapia, El Heraldo de Juárez</t>
         </is>
       </c>
       <c r="L196" s="5" t="inlineStr">
         <is>
-          <t>Registro número 162 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: Lo Real de Guerrero. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
+          <t>Registro número 164 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: El Heraldo de Juárez. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
         </is>
       </c>
       <c r="M196" s="3" t="inlineStr">
@@ -15748,7 +15772,7 @@
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>ev-242</t>
+          <t>ev-240</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -15778,28 +15802,28 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="H197" s="3" t="n">
-        <v>29.4124</v>
+        <v>18.7298</v>
       </c>
       <c r="I197" s="3" t="n">
-        <v>-110.5518</v>
+        <v>-99.1053</v>
       </c>
       <c r="J197" s="5" t="inlineStr">
         <is>
-          <t>Sonora</t>
+          <t>Morelos</t>
         </is>
       </c>
       <c r="K197" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Jesús Gutiérrez Vergara, Notiface Prensa Digital</t>
+          <t>Asesinato de Roberto Carlos Figueroa, Acá En El Show</t>
         </is>
       </c>
       <c r="L197" s="5" t="inlineStr">
         <is>
-          <t>Registro número 163 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: Notiface Prensa Digital. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
+          <t>Registro número 165 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: Acá En El Show. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
         </is>
       </c>
       <c r="M197" s="3" t="inlineStr">
@@ -15826,7 +15850,7 @@
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>ev-241</t>
+          <t>ev-239</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -15856,28 +15880,28 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2023-11-16</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="H198" s="3" t="n">
-        <v>28.7044</v>
+        <v>16.2574</v>
       </c>
       <c r="I198" s="3" t="n">
-        <v>-106.0375</v>
+        <v>-92.24550000000001</v>
       </c>
       <c r="J198" s="5" t="inlineStr">
         <is>
-          <t>Chihuahua</t>
+          <t>Chiapas</t>
         </is>
       </c>
       <c r="K198" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Ismael Villagómez Tapia, El Heraldo de Juárez</t>
+          <t>Asesinato de Víctor Alfonso Culebro Morales, Realidades y Radio Fórmula</t>
         </is>
       </c>
       <c r="L198" s="5" t="inlineStr">
         <is>
-          <t>Registro número 164 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: El Heraldo de Juárez. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
+          <t>Registro número 166 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: Realidades y Radio Fórmula. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
         </is>
       </c>
       <c r="M198" s="3" t="inlineStr">
@@ -15904,61 +15928,73 @@
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t>ev-011</t>
+          <t>ev-238</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento</t>
-        </is>
-      </c>
-      <c r="C199" s="3" t="inlineStr"/>
-      <c r="D199" s="4" t="inlineStr"/>
-      <c r="E199" s="3" t="inlineStr"/>
+          <t>periodistas</t>
+        </is>
+      </c>
+      <c r="C199" s="3" t="inlineStr">
+        <is>
+          <t>periodista</t>
+        </is>
+      </c>
+      <c r="D199" s="4" t="inlineStr">
+        <is>
+          <t>asesinato</t>
+        </is>
+      </c>
+      <c r="E199" s="3" t="inlineStr">
+        <is>
+          <t>masculino</t>
+        </is>
+      </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento masivo</t>
+          <t>asesinato de periodista</t>
         </is>
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="H199" s="3" t="n">
-        <v>16.891</v>
+        <v>20.8745</v>
       </c>
       <c r="I199" s="3" t="n">
-        <v>-92.628</v>
+        <v>-101.2607</v>
       </c>
       <c r="J199" s="5" t="inlineStr">
         <is>
-          <t>Chenalhó, Chiapas</t>
+          <t>Guanajuato</t>
         </is>
       </c>
       <c r="K199" s="5" t="inlineStr">
         <is>
-          <t>68 familias del sector Santa Marta desplazadas por disputa entre grupos armados</t>
+          <t>Asesinato de Alejandro Alfredo Martínez Noguez, El Hijo del Llanero Solitito</t>
         </is>
       </c>
       <c r="L199" s="5" t="inlineStr">
         <is>
-          <t>En 2024, 68 familias del sector Santa Marta, Chenalhó, fueron desplazadas por la disputa entre grupos armados de la región, según Expansión con base en la Encuesta Intercensal 2025. Mes no precisado en la nota. Ubicación aproximada (cabecera municipal).</t>
+          <t>Registro número 167 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: El Hijo del Llanero Solitito. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
         </is>
       </c>
       <c r="M199" s="3" t="inlineStr">
         <is>
-          <t>expansion</t>
+          <t>article19</t>
         </is>
       </c>
       <c r="N199" s="3" t="inlineStr">
         <is>
-          <t>https://politica.expansion.mx/mexico/2026/09/23/inegi-desplazamiento-forzado-violencia-mexico-municipios</t>
+          <t>https://articulo19.org/periodistasasesinados/</t>
         </is>
       </c>
       <c r="O199" s="3" t="inlineStr">
         <is>
-          <t>prensa</t>
+          <t>organización</t>
         </is>
       </c>
       <c r="P199" s="3" t="inlineStr">
@@ -15970,7 +16006,7 @@
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>ev-240</t>
+          <t>ev-044</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -15980,7 +16016,7 @@
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>periodista</t>
+          <t>defensor</t>
         </is>
       </c>
       <c r="D200" s="4" t="inlineStr">
@@ -15995,48 +16031,48 @@
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>asesinato de periodista</t>
+          <t>asesinato de persona defensora</t>
         </is>
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-10-20</t>
         </is>
       </c>
       <c r="H200" s="3" t="n">
-        <v>18.7298</v>
+        <v>16.737</v>
       </c>
       <c r="I200" s="3" t="n">
-        <v>-99.1053</v>
+        <v>-92.63800000000001</v>
       </c>
       <c r="J200" s="5" t="inlineStr">
         <is>
-          <t>Morelos</t>
+          <t>San Cristóbal de las Casas, Chiapas</t>
         </is>
       </c>
       <c r="K200" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Roberto Carlos Figueroa, Acá En El Show</t>
+          <t>Asesinato del padre Marcelo Pérez Pérez, defensor tsotsil de derechos humanos</t>
         </is>
       </c>
       <c r="L200" s="5" t="inlineStr">
         <is>
-          <t>Registro número 165 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: Acá En El Show. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
+          <t>Párroco de la iglesia de Guadalupe, mediador en conflictos comunitarios y defensor del territorio en los Altos de Chiapas; asesinado después de oficiar misa. Había sido difamado y tenía una orden de aprehensión vigente. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="M200" s="3" t="inlineStr">
         <is>
-          <t>article19</t>
+          <t>grupoanimal</t>
         </is>
       </c>
       <c r="N200" s="3" t="inlineStr">
         <is>
-          <t>https://articulo19.org/periodistasasesinados/</t>
+          <t>https://www.iberopuebla.mx/circulo-de-escritores/vcampos/asesinatos-defensores</t>
         </is>
       </c>
       <c r="O200" s="3" t="inlineStr">
         <is>
-          <t>organización</t>
+          <t>prensa</t>
         </is>
       </c>
       <c r="P200" s="3" t="inlineStr">
@@ -16048,7 +16084,7 @@
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t>ev-239</t>
+          <t>ev-237</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -16078,28 +16114,28 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2024-06-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="H201" s="3" t="n">
-        <v>16.2574</v>
+        <v>19.1535</v>
       </c>
       <c r="I201" s="3" t="n">
-        <v>-92.24550000000001</v>
+        <v>-101.6713</v>
       </c>
       <c r="J201" s="5" t="inlineStr">
         <is>
-          <t>Chiapas</t>
+          <t>Michoacán</t>
         </is>
       </c>
       <c r="K201" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Víctor Alfonso Culebro Morales, Realidades y Radio Fórmula</t>
+          <t>Asesinato de Mauricio Cruz Solís, Radiorama Noticias / Minuto X Minuto</t>
         </is>
       </c>
       <c r="L201" s="5" t="inlineStr">
         <is>
-          <t>Registro número 166 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: Realidades y Radio Fórmula. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
+          <t>Registro número 168 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: Radiorama Noticias / Minuto X Minuto. Sexo: masculino. Sexenio: Claudia Sheinbaum Pardo. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
         </is>
       </c>
       <c r="M201" s="3" t="inlineStr">
@@ -16126,7 +16162,7 @@
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>ev-238</t>
+          <t>ev-073</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -16136,7 +16172,7 @@
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>periodista</t>
+          <t>defensor</t>
         </is>
       </c>
       <c r="D202" s="4" t="inlineStr">
@@ -16146,48 +16182,48 @@
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
-          <t>masculino</t>
+          <t>femenino</t>
         </is>
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>asesinato de periodista</t>
+          <t>asesinato de persona defensora ambiental</t>
         </is>
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="H202" s="3" t="n">
-        <v>20.8745</v>
+        <v>19.028</v>
       </c>
       <c r="I202" s="3" t="n">
-        <v>-101.2607</v>
+        <v>-99.271</v>
       </c>
       <c r="J202" s="5" t="inlineStr">
         <is>
-          <t>Guanajuato</t>
+          <t>Huitzilac, Morelos</t>
         </is>
       </c>
       <c r="K202" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Alejandro Alfredo Martínez Noguez, El Hijo del Llanero Solitito</t>
+          <t>Asesinato de Silvia Hernández Meza, defensora del bosque de Huitzilac</t>
         </is>
       </c>
       <c r="L202" s="5" t="inlineStr">
         <is>
-          <t>Registro número 167 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: El Hijo del Llanero Solitito. Sexo: masculino. Sexenio: Andrés Manuel López Obrador. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
+          <t>Candidata a presidir los bienes comunales, reconocida por Conafor por su trabajo de reforestación y denuncia de la tala en el Parque Nacional Lagunas de Zempoala; asesinada con cuatro integrantes de su planilla durante la campaña. Fuente: memorial del informe CEMDA 2025. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="M202" s="3" t="inlineStr">
         <is>
-          <t>article19</t>
+          <t>cemda</t>
         </is>
       </c>
       <c r="N202" s="3" t="inlineStr">
         <is>
-          <t>https://articulo19.org/periodistasasesinados/</t>
+          <t>https://cemda.org.mx/wp-content/uploads/2026/04/Informe-Defensores-2025_Web_260415_173954.pdf</t>
         </is>
       </c>
       <c r="O202" s="3" t="inlineStr">
@@ -16204,61 +16240,73 @@
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
         <is>
-          <t>ev-012</t>
+          <t>ev-045</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento</t>
-        </is>
-      </c>
-      <c r="C203" s="3" t="inlineStr"/>
-      <c r="D203" s="4" t="inlineStr"/>
-      <c r="E203" s="3" t="inlineStr"/>
+          <t>periodistas</t>
+        </is>
+      </c>
+      <c r="C203" s="3" t="inlineStr">
+        <is>
+          <t>periodista</t>
+        </is>
+      </c>
+      <c r="D203" s="4" t="inlineStr">
+        <is>
+          <t>asesinato</t>
+        </is>
+      </c>
+      <c r="E203" s="3" t="inlineStr">
+        <is>
+          <t>masculino</t>
+        </is>
+      </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento masivo</t>
+          <t>asesinato de periodista</t>
         </is>
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="H203" s="3" t="n">
-        <v>15.744</v>
+        <v>19.744</v>
       </c>
       <c r="I203" s="3" t="n">
-        <v>-92.279</v>
+        <v>-99.18000000000001</v>
       </c>
       <c r="J203" s="5" t="inlineStr">
         <is>
-          <t>Chicomuselo, Chiapas</t>
+          <t>Teoloyucan, Estado de México</t>
         </is>
       </c>
       <c r="K203" s="5" t="inlineStr">
         <is>
-          <t>53 familias del barrio Galicia huyen de Chicomuselo hacia Siltepec</t>
+          <t>Asesinato de Calletano de Jesús Guerrero, Global México</t>
         </is>
       </c>
       <c r="L203" s="5" t="inlineStr">
         <is>
-          <t>Tras cinco días de enfrentamientos entre grupos criminales, 53 familias (unas 265 personas) del barrio Galicia salieron hacia Siltepec, donde 35 fueron alojadas por el municipio y 18 con familiares, según Protección Civil estatal. Ubicación aproximada (cabecera municipal).</t>
+          <t>Asesinado con arma de fuego en el estacionamiento de una parroquia. Cuatro días antes había recibido amenazas de muerte en su domicilio y el Mecanismo federal había activado su reubicación urgente. La fiscalía estatal lo vinculó después con grupos delictivos sin contactar a su familia. Ubicación aproximada (cabecera municipal). Figura como número 169 en el registro de periodistas asesinados de ARTICLE 19.</t>
         </is>
       </c>
       <c r="M203" s="3" t="inlineStr">
         <is>
-          <t>proceso</t>
+          <t>article19</t>
         </is>
       </c>
       <c r="N203" s="3" t="inlineStr">
         <is>
-          <t>https://www.proceso.com.mx/nacional/2024/8/21/violencia-en-chiapas-desplaza-53-familias-333851.html</t>
+          <t>https://articulo19.org/wp-content/uploads/2026/05/Estructuras-del-Silencio-Informe-Anual-2025-A19-MXCA_compressed.pdf</t>
         </is>
       </c>
       <c r="O203" s="3" t="inlineStr">
         <is>
-          <t>prensa</t>
+          <t>organización</t>
         </is>
       </c>
       <c r="P203" s="3" t="inlineStr">
@@ -16270,54 +16318,70 @@
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>ev-006</t>
+          <t>ev-074</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>desaparicion</t>
-        </is>
-      </c>
-      <c r="C204" s="3" t="inlineStr"/>
-      <c r="D204" s="4" t="inlineStr"/>
-      <c r="E204" s="3" t="inlineStr"/>
+          <t>periodistas</t>
+        </is>
+      </c>
+      <c r="C204" s="3" t="inlineStr">
+        <is>
+          <t>defensor</t>
+        </is>
+      </c>
+      <c r="D204" s="4" t="inlineStr">
+        <is>
+          <t>asesinato</t>
+        </is>
+      </c>
+      <c r="E204" s="3" t="inlineStr">
+        <is>
+          <t>masculino</t>
+        </is>
+      </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>fosa clandestina</t>
+          <t>asesinato de persona defensora ambiental</t>
         </is>
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="H204" s="3" t="n">
-        <v>24.7</v>
+        <v>16.963</v>
       </c>
       <c r="I204" s="3" t="n">
-        <v>-107.6</v>
+        <v>-95.093</v>
       </c>
       <c r="J204" s="5" t="inlineStr">
         <is>
-          <t>Zona rural de Culiacán, Sinaloa</t>
+          <t>San Juan Guichicovi, Oaxaca</t>
         </is>
       </c>
       <c r="K204" s="5" t="inlineStr">
         <is>
-          <t>Ejemplo: hallazgo de fosa clandestina</t>
+          <t>Asesinato de Arnoldo Nicolás Romero, comisario ejidal e integrante de UCIZONI</t>
         </is>
       </c>
       <c r="L204" s="5" t="inlineStr">
         <is>
-          <t>Registro de ejemplo. Reemplazar con base de fosas (Quinto Elemento Lab) o boletín de fiscalía.</t>
+          <t>Opositor a la imposición del Corredor Interoceánico; reportado desaparecido el 17 de enero y hallado sin vida el 21 con heridas de bala y quemaduras. Sin datos de investigación en curso. Fuente: memorial del informe CEMDA 2025. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="M204" s="3" t="inlineStr">
         <is>
-          <t>fosas-quinto</t>
-        </is>
-      </c>
-      <c r="N204" s="3" t="inlineStr"/>
+          <t>cemda</t>
+        </is>
+      </c>
+      <c r="N204" s="3" t="inlineStr">
+        <is>
+          <t>https://cemda.org.mx/wp-content/uploads/2026/04/Informe-Defensores-2025_Web_260415_173954.pdf</t>
+        </is>
+      </c>
       <c r="O204" s="3" t="inlineStr">
         <is>
           <t>organización</t>
@@ -16325,14 +16389,14 @@
       </c>
       <c r="P204" s="3" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
         <is>
-          <t>ev-044</t>
+          <t>ev-075</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -16357,48 +16421,48 @@
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>asesinato de persona defensora</t>
+          <t>asesinato de persona defensora ambiental</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2024-10-20</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="H205" s="3" t="n">
-        <v>16.737</v>
+        <v>19.947</v>
       </c>
       <c r="I205" s="3" t="n">
-        <v>-92.63800000000001</v>
+        <v>-97.553</v>
       </c>
       <c r="J205" s="5" t="inlineStr">
         <is>
-          <t>San Cristóbal de las Casas, Chiapas</t>
+          <t>Acuaco, Zaragoza, Puebla</t>
         </is>
       </c>
       <c r="K205" s="5" t="inlineStr">
         <is>
-          <t>Asesinato del padre Marcelo Pérez Pérez, defensor tsotsil de derechos humanos</t>
+          <t>Asesinato de José Luis Lucas Quirino, profesor y líder ejidal</t>
         </is>
       </c>
       <c r="L205" s="5" t="inlineStr">
         <is>
-          <t>Párroco de la iglesia de Guadalupe, mediador en conflictos comunitarios y defensor del territorio en los Altos de Chiapas; asesinado después de oficiar misa. Había sido difamado y tenía una orden de aprehensión vigente. Ubicación aproximada (cabecera municipal).</t>
+          <t>Defensor del agua y los bosques de la Sierra Nororiental frente a granjas porcícolas y minería; atacado con armas de fuego frente a la primaria que dirigía. Fuente: memorial del informe CEMDA 2025. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="M205" s="3" t="inlineStr">
         <is>
-          <t>grupoanimal</t>
+          <t>cemda</t>
         </is>
       </c>
       <c r="N205" s="3" t="inlineStr">
         <is>
-          <t>https://www.iberopuebla.mx/circulo-de-escritores/vcampos/asesinatos-defensores</t>
+          <t>https://cemda.org.mx/wp-content/uploads/2026/04/Informe-Defensores-2025_Web_260415_173954.pdf</t>
         </is>
       </c>
       <c r="O205" s="3" t="inlineStr">
         <is>
-          <t>prensa</t>
+          <t>organización</t>
         </is>
       </c>
       <c r="P205" s="3" t="inlineStr">
@@ -16410,7 +16474,7 @@
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>ev-237</t>
+          <t>ev-076</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -16420,7 +16484,7 @@
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>periodista</t>
+          <t>defensor</t>
         </is>
       </c>
       <c r="D206" s="4" t="inlineStr">
@@ -16435,43 +16499,43 @@
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>asesinato de periodista</t>
+          <t>asesinato de persona defensora ambiental</t>
         </is>
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="H206" s="3" t="n">
-        <v>19.1535</v>
+        <v>15.832</v>
       </c>
       <c r="I206" s="3" t="n">
-        <v>-101.6713</v>
+        <v>-95.953</v>
       </c>
       <c r="J206" s="5" t="inlineStr">
         <is>
-          <t>Michoacán</t>
+          <t>Barra de la Cruz, Santiago Astata, Oaxaca</t>
         </is>
       </c>
       <c r="K206" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Mauricio Cruz Solís, Radiorama Noticias / Minuto X Minuto</t>
+          <t>Asesinato de Cristino Castro Perea, defensor del santuario de tortugas de Barra de la Cruz</t>
         </is>
       </c>
       <c r="L206" s="5" t="inlineStr">
         <is>
-          <t>Registro número 168 de periodistas asesinados en posible relación con su labor informativa, según ARTICLE 19. Medio: Radiorama Noticias / Minuto X Minuto. Sexo: masculino. Sexenio: Claudia Sheinbaum Pardo. Ubicación aproximada (centro de la entidad); el registro público solo indica la entidad.</t>
+          <t>Fundador del colectivo Defensores Ambientalistas de Barra de la Cruz y beneficiario del Mecanismo federal; dos personas en motocicleta le dispararon en el quiosco de su comunidad. Fuente: memorial del informe CEMDA 2025. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="M206" s="3" t="inlineStr">
         <is>
-          <t>article19</t>
+          <t>cemda</t>
         </is>
       </c>
       <c r="N206" s="3" t="inlineStr">
         <is>
-          <t>https://articulo19.org/periodistasasesinados/</t>
+          <t>https://cemda.org.mx/wp-content/uploads/2026/04/Informe-Defensores-2025_Web_260415_173954.pdf</t>
         </is>
       </c>
       <c r="O206" s="3" t="inlineStr">
@@ -16488,61 +16552,73 @@
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
         <is>
-          <t>ev-013</t>
+          <t>ev-046</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento</t>
-        </is>
-      </c>
-      <c r="C207" s="3" t="inlineStr"/>
-      <c r="D207" s="4" t="inlineStr"/>
-      <c r="E207" s="3" t="inlineStr"/>
+          <t>periodistas</t>
+        </is>
+      </c>
+      <c r="C207" s="3" t="inlineStr">
+        <is>
+          <t>periodista</t>
+        </is>
+      </c>
+      <c r="D207" s="4" t="inlineStr">
+        <is>
+          <t>asesinato</t>
+        </is>
+      </c>
+      <c r="E207" s="3" t="inlineStr">
+        <is>
+          <t>masculino</t>
+        </is>
+      </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t>cifra oficial</t>
+          <t>asesinato de periodista</t>
         </is>
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2025-01-05</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="H207" s="3" t="n">
-        <v>24.809</v>
+        <v>20.941</v>
       </c>
       <c r="I207" s="3" t="n">
-        <v>-107.394</v>
+        <v>-101.428</v>
       </c>
       <c r="J207" s="5" t="inlineStr">
         <is>
-          <t>Culiacán, Sinaloa</t>
+          <t>Silao, Guanajuato</t>
         </is>
       </c>
       <c r="K207" s="5" t="inlineStr">
         <is>
-          <t>Sebides: mil 184 familias desplazadas desde el 9 de septiembre de 2024</t>
+          <t>Asesinato de Kristian Uriel Martínez Zavala, El Silaoense MX</t>
         </is>
       </c>
       <c r="L207" s="5" t="inlineStr">
         <is>
-          <t>La titular de Sebides informó que mil 184 familias se habían trasladado temporalmente desde el inicio de la pugna entre facciones del Cártel de Sinaloa, en Culiacán, Concordia, Rosario, Cosalá, Elota y San Ignacio. Cifra estatal ubicada en la capital.</t>
+          <t>Documentado por ARTICLE 19 como asesinato en posible relación con su labor periodística. Ubicación aproximada (cabecera municipal). Figura como número 170 en el registro de periodistas asesinados de ARTICLE 19.</t>
         </is>
       </c>
       <c r="M207" s="3" t="inlineStr">
         <is>
-          <t>sebides</t>
+          <t>article19</t>
         </is>
       </c>
       <c r="N207" s="3" t="inlineStr">
         <is>
-          <t>https://www.luznoticias.mx/2025-01-05/sinaloa/mil-184-familias-han-sido-desplazadas-en-sinaloa-por-inseguridad-/230180</t>
+          <t>https://articulo19.org/wp-content/uploads/2026/05/Estructuras-del-Silencio-Informe-Anual-2025-A19-MXCA_compressed.pdf</t>
         </is>
       </c>
       <c r="O207" s="3" t="inlineStr">
         <is>
-          <t>oficial</t>
+          <t>organización</t>
         </is>
       </c>
       <c r="P207" s="3" t="inlineStr">
@@ -16554,7 +16630,7 @@
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t>ev-073</t>
+          <t>ev-047</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -16564,63 +16640,63 @@
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>defensor</t>
+          <t>periodista</t>
         </is>
       </c>
       <c r="D208" s="4" t="inlineStr">
         <is>
-          <t>asesinato</t>
+          <t>proteccion</t>
         </is>
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
-          <t>femenino</t>
+          <t>no aplica</t>
         </is>
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
-          <t>asesinato de persona defensora ambiental</t>
+          <t>cifra oficial</t>
         </is>
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="H208" s="3" t="n">
-        <v>19.028</v>
+        <v>24.809</v>
       </c>
       <c r="I208" s="3" t="n">
-        <v>-99.271</v>
+        <v>-107.394</v>
       </c>
       <c r="J208" s="5" t="inlineStr">
         <is>
-          <t>Huitzilac, Morelos</t>
+          <t>Culiacán, Sinaloa</t>
         </is>
       </c>
       <c r="K208" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Silvia Hernández Meza, defensora del bosque de Huitzilac</t>
+          <t>Instituto de Protección de Sinaloa atiende a 77 periodistas y defensores en medio año de crisis</t>
         </is>
       </c>
       <c r="L208" s="5" t="inlineStr">
         <is>
-          <t>Candidata a presidir los bienes comunales, reconocida por Conafor por su trabajo de reforestación y denuncia de la tala en el Parque Nacional Lagunas de Zempoala; asesinada con cuatro integrantes de su planilla durante la campaña. Fuente: memorial del informe CEMDA 2025. Ubicación aproximada (cabecera municipal).</t>
+          <t>En seis meses de la pugna entre facciones del Cártel de Sinaloa, el Instituto otorgó 333 medidas cautelares a periodistas, activistas y 16 familiares. Agresiones más comunes: amenazas, disparos contra medios, daños a vehículos y viviendas, privación de la libertad y censura. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="M208" s="3" t="inlineStr">
         <is>
-          <t>cemda</t>
+          <t>instituto-sinaloa</t>
         </is>
       </c>
       <c r="N208" s="3" t="inlineStr">
         <is>
-          <t>https://cemda.org.mx/wp-content/uploads/2026/04/Informe-Defensores-2025_Web_260415_173954.pdf</t>
+          <t>https://www.noroeste.com.mx/culiacan/atiende-instituto-de-proteccion-a-77-periodistas-y-activistas-de-sinaloa-en-medio-de-crisis-de-violencia-BI11082146</t>
         </is>
       </c>
       <c r="O208" s="3" t="inlineStr">
         <is>
-          <t>organización</t>
+          <t>oficial</t>
         </is>
       </c>
       <c r="P208" s="3" t="inlineStr">
@@ -16632,7 +16708,7 @@
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
         <is>
-          <t>ev-045</t>
+          <t>ev-048</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -16647,43 +16723,43 @@
       </c>
       <c r="D209" s="4" t="inlineStr">
         <is>
-          <t>asesinato</t>
+          <t>agresion</t>
         </is>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
-          <t>masculino</t>
+          <t>no determinado</t>
         </is>
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
-          <t>asesinato de periodista</t>
+          <t>agresión física por autoridad</t>
         </is>
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="H209" s="3" t="n">
-        <v>19.744</v>
+        <v>17.989</v>
       </c>
       <c r="I209" s="3" t="n">
-        <v>-99.18000000000001</v>
+        <v>-92.93000000000001</v>
       </c>
       <c r="J209" s="5" t="inlineStr">
         <is>
-          <t>Teoloyucan, Estado de México</t>
+          <t>Villahermosa, Tabasco</t>
         </is>
       </c>
       <c r="K209" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Calletano de Jesús Guerrero, Global México</t>
+          <t>Fotoperiodista de El Universal lesionado por agente de seguridad estatal durante cobertura</t>
         </is>
       </c>
       <c r="L209" s="5" t="inlineStr">
         <is>
-          <t>Asesinado con arma de fuego en el estacionamiento de una parroquia. Cuatro días antes había recibido amenazas de muerte en su domicilio y el Mecanismo federal había activado su reubicación urgente. La fiscalía estatal lo vinculó después con grupos delictivos sin contactar a su familia. Ubicación aproximada (cabecera municipal). Figura como número 169 en el registro de periodistas asesinados de ARTICLE 19.</t>
+          <t>Derribado y golpeado por una persona en función policial de la Secretaría de Seguridad de Tabasco mientras cubría un homicidio. ARTICLE 19 registró 53 agresiones físicas en 2025, con participación recurrente de agentes del Estado. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="M209" s="3" t="inlineStr">
@@ -16710,7 +16786,7 @@
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>ev-074</t>
+          <t>ev-049</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -16720,7 +16796,7 @@
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>defensor</t>
+          <t>periodista</t>
         </is>
       </c>
       <c r="D210" s="4" t="inlineStr">
@@ -16735,43 +16811,43 @@
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>asesinato de persona defensora ambiental</t>
+          <t>asesinato de periodista</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="H210" s="3" t="n">
-        <v>16.963</v>
+        <v>21.298</v>
       </c>
       <c r="I210" s="3" t="n">
-        <v>-95.093</v>
+        <v>-100.517</v>
       </c>
       <c r="J210" s="5" t="inlineStr">
         <is>
-          <t>San Juan Guichicovi, Oaxaca</t>
+          <t>San Luis de la Paz, Guanajuato</t>
         </is>
       </c>
       <c r="K210" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Arnoldo Nicolás Romero, comisario ejidal e integrante de UCIZONI</t>
+          <t>Asesinato de Raúl Irán Villarreal Belmont, Observatorio Ciudadano San Luis de la Paz</t>
         </is>
       </c>
       <c r="L210" s="5" t="inlineStr">
         <is>
-          <t>Opositor a la imposición del Corredor Interoceánico; reportado desaparecido el 17 de enero y hallado sin vida el 21 con heridas de bala y quemaduras. Sin datos de investigación en curso. Fuente: memorial del informe CEMDA 2025. Ubicación aproximada (cabecera municipal).</t>
+          <t>Documentado por ARTICLE 19 como asesinato en posible relación con su labor periodística. Ubicación aproximada (cabecera municipal). Figura como número 171 en el registro de periodistas asesinados de ARTICLE 19.</t>
         </is>
       </c>
       <c r="M210" s="3" t="inlineStr">
         <is>
-          <t>cemda</t>
+          <t>article19</t>
         </is>
       </c>
       <c r="N210" s="3" t="inlineStr">
         <is>
-          <t>https://cemda.org.mx/wp-content/uploads/2026/04/Informe-Defensores-2025_Web_260415_173954.pdf</t>
+          <t>https://articulo19.org/wp-content/uploads/2026/05/Estructuras-del-Silencio-Informe-Anual-2025-A19-MXCA_compressed.pdf</t>
         </is>
       </c>
       <c r="O210" s="3" t="inlineStr">
@@ -16788,7 +16864,7 @@
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
         <is>
-          <t>ev-075</t>
+          <t>ev-050</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -16798,12 +16874,12 @@
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>defensor</t>
+          <t>periodista</t>
         </is>
       </c>
       <c r="D211" s="4" t="inlineStr">
         <is>
-          <t>asesinato</t>
+          <t>desaparicion</t>
         </is>
       </c>
       <c r="E211" s="3" t="inlineStr">
@@ -16813,43 +16889,43 @@
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>asesinato de persona defensora ambiental</t>
+          <t>desaparición de periodista</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="H211" s="3" t="n">
-        <v>19.947</v>
+        <v>22.055</v>
       </c>
       <c r="I211" s="3" t="n">
-        <v>-97.553</v>
+        <v>-98.18300000000001</v>
       </c>
       <c r="J211" s="5" t="inlineStr">
         <is>
-          <t>Acuaco, Zaragoza, Puebla</t>
+          <t>Pánuco, Veracruz</t>
         </is>
       </c>
       <c r="K211" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de José Luis Lucas Quirino, profesor y líder ejidal</t>
+          <t>Desaparición de Miguel Ángel Anaya Castillo, director de Pánuco On Line</t>
         </is>
       </c>
       <c r="L211" s="5" t="inlineStr">
         <is>
-          <t>Defensor del agua y los bosques de la Sierra Nororiental frente a granjas porcícolas y minería; atacado con armas de fuego frente a la primaria que dirigía. Fuente: memorial del informe CEMDA 2025. Ubicación aproximada (cabecera municipal).</t>
+          <t>Desaparecido desde el 13 de abril de 2025; mes y medio antes había sido hostigado en su domicilio. ARTICLE 19 contabiliza 32 periodistas desaparecidos desde 2000, concentrados en Tamaulipas, Veracruz y Michoacán. Ubicación aproximada (cabecera municipal). Figura como número 32 en el registro de periodistas desaparecidos de ARTICLE 19.</t>
         </is>
       </c>
       <c r="M211" s="3" t="inlineStr">
         <is>
-          <t>cemda</t>
+          <t>article19</t>
         </is>
       </c>
       <c r="N211" s="3" t="inlineStr">
         <is>
-          <t>https://cemda.org.mx/wp-content/uploads/2026/04/Informe-Defensores-2025_Web_260415_173954.pdf</t>
+          <t>https://articulo19.org/wp-content/uploads/2026/05/Estructuras-del-Silencio-Informe-Anual-2025-A19-MXCA_compressed.pdf</t>
         </is>
       </c>
       <c r="O211" s="3" t="inlineStr">
@@ -16866,69 +16942,85 @@
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>ev-005</t>
+          <t>ev-078</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>desaparicion</t>
-        </is>
-      </c>
-      <c r="C212" s="3" t="inlineStr"/>
-      <c r="D212" s="4" t="inlineStr"/>
-      <c r="E212" s="3" t="inlineStr"/>
+          <t>periodistas</t>
+        </is>
+      </c>
+      <c r="C212" s="3" t="inlineStr">
+        <is>
+          <t>defensor</t>
+        </is>
+      </c>
+      <c r="D212" s="4" t="inlineStr">
+        <is>
+          <t>asesinato</t>
+        </is>
+      </c>
+      <c r="E212" s="3" t="inlineStr">
+        <is>
+          <t>femenino</t>
+        </is>
+      </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>búsqueda en campo</t>
+          <t>asesinato de persona defensora ambiental</t>
         </is>
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="H212" s="3" t="n">
-        <v>26.4222</v>
+        <v>20.773</v>
       </c>
       <c r="I212" s="3" t="n">
-        <v>-108.6203</v>
+        <v>-103.693</v>
       </c>
       <c r="J212" s="5" t="inlineStr">
         <is>
-          <t>El Fuerte, Sinaloa</t>
+          <t>El Arenal, Jalisco</t>
         </is>
       </c>
       <c r="K212" s="5" t="inlineStr">
         <is>
-          <t>Ejemplo: jornada de búsqueda de colectivo</t>
+          <t>Desaparición y asesinato de Karina Ruiz Ocampo, defensora del derecho al agua</t>
         </is>
       </c>
       <c r="L212" s="5" t="inlineStr">
         <is>
-          <t>Registro de ejemplo. Campos sugeridos: colectivo, hallazgos, autoridades presentes.</t>
+          <t>Representante legal de la asociación vecinal La Cima, Nuestra Prioridad; sacada de su casa por la fuerza el 14 de abril y hallada sin vida el 3 de mayo. Se investiga como feminicidio. Fuente: memorial del informe CEMDA 2025. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="M212" s="3" t="inlineStr">
         <is>
-          <t>ceb-sin</t>
-        </is>
-      </c>
-      <c r="N212" s="3" t="inlineStr"/>
+          <t>cemda</t>
+        </is>
+      </c>
+      <c r="N212" s="3" t="inlineStr">
+        <is>
+          <t>https://cemda.org.mx/wp-content/uploads/2026/04/Informe-Defensores-2025_Web_260415_173954.pdf</t>
+        </is>
+      </c>
       <c r="O212" s="3" t="inlineStr">
         <is>
-          <t>campo</t>
+          <t>organización</t>
         </is>
       </c>
       <c r="P212" s="3" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
         <is>
-          <t>ev-076</t>
+          <t>ev-077</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -16958,28 +17050,28 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="H213" s="3" t="n">
-        <v>15.832</v>
+        <v>16.982</v>
       </c>
       <c r="I213" s="3" t="n">
-        <v>-95.953</v>
+        <v>-99.7</v>
       </c>
       <c r="J213" s="5" t="inlineStr">
         <is>
-          <t>Barra de la Cruz, Santiago Astata, Oaxaca</t>
+          <t>Cacahuatepec, Acapulco, Guerrero</t>
         </is>
       </c>
       <c r="K213" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Cristino Castro Perea, defensor del santuario de tortugas de Barra de la Cruz</t>
+          <t>Ataque mortal contra Marco Antonio Suástegui, líder del CECOP</t>
         </is>
       </c>
       <c r="L213" s="5" t="inlineStr">
         <is>
-          <t>Fundador del colectivo Defensores Ambientalistas de Barra de la Cruz y beneficiario del Mecanismo federal; dos personas en motocicleta le dispararon en el quiosco de su comunidad. Fuente: memorial del informe CEMDA 2025. Ubicación aproximada (cabecera municipal).</t>
+          <t>Defensor del río Papagayo y opositor histórico a la presa La Parota; atacado al salir de la playa Icacos y fallecido ocho días después. Su familia estaba incorporada al Mecanismo tras la desaparición de su hermano en 2021. Fuente: memorial del informe CEMDA 2025. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="M213" s="3" t="inlineStr">
@@ -17006,69 +17098,85 @@
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>ev-001</t>
+          <t>ev-051</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>migracion</t>
-        </is>
-      </c>
-      <c r="C214" s="3" t="inlineStr"/>
-      <c r="D214" s="4" t="inlineStr"/>
-      <c r="E214" s="3" t="inlineStr"/>
+          <t>periodistas</t>
+        </is>
+      </c>
+      <c r="C214" s="3" t="inlineStr">
+        <is>
+          <t>periodista</t>
+        </is>
+      </c>
+      <c r="D214" s="4" t="inlineStr">
+        <is>
+          <t>asesinato</t>
+        </is>
+      </c>
+      <c r="E214" s="3" t="inlineStr">
+        <is>
+          <t>masculino</t>
+        </is>
+      </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>albergue</t>
+          <t>asesinato de periodista</t>
         </is>
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="H214" s="3" t="n">
-        <v>23.2329</v>
+        <v>16.863</v>
       </c>
       <c r="I214" s="3" t="n">
-        <v>-106.4062</v>
+        <v>-99.88200000000001</v>
       </c>
       <c r="J214" s="5" t="inlineStr">
         <is>
-          <t>Mazatlán, Sinaloa</t>
+          <t>Acapulco, Guerrero</t>
         </is>
       </c>
       <c r="K214" s="5" t="inlineStr">
         <is>
-          <t>Ejemplo: albergue para personas en tránsito</t>
+          <t>Asesinato de José Carlos González Herrera, El Guerrero / Opinión Ciudadana</t>
         </is>
       </c>
       <c r="L214" s="5" t="inlineStr">
         <is>
-          <t>Registro de ejemplo. Reemplazar con datos de campo (capacidad, personas atendidas por mes).</t>
+          <t>Documentado por ARTICLE 19 como asesinato en posible relación con su labor periodística. Ubicación aproximada (cabecera municipal). Figura como número 172 en el registro de periodistas asesinados de ARTICLE 19.</t>
         </is>
       </c>
       <c r="M214" s="3" t="inlineStr">
         <is>
-          <t>ceb-sin</t>
-        </is>
-      </c>
-      <c r="N214" s="3" t="inlineStr"/>
+          <t>article19</t>
+        </is>
+      </c>
+      <c r="N214" s="3" t="inlineStr">
+        <is>
+          <t>https://articulo19.org/wp-content/uploads/2026/05/Estructuras-del-Silencio-Informe-Anual-2025-A19-MXCA_compressed.pdf</t>
+        </is>
+      </c>
       <c r="O214" s="3" t="inlineStr">
         <is>
-          <t>sin verificar</t>
+          <t>organización</t>
         </is>
       </c>
       <c r="P214" s="3" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
         <is>
-          <t>ev-046</t>
+          <t>ev-052</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -17083,43 +17191,43 @@
       </c>
       <c r="D215" s="4" t="inlineStr">
         <is>
-          <t>asesinato</t>
+          <t>amenaza</t>
         </is>
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
-          <t>masculino</t>
+          <t>femenino</t>
         </is>
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>asesinato de periodista</t>
+          <t>amenaza</t>
         </is>
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="H215" s="3" t="n">
-        <v>20.941</v>
+        <v>20.674</v>
       </c>
       <c r="I215" s="3" t="n">
-        <v>-101.428</v>
+        <v>-103.347</v>
       </c>
       <c r="J215" s="5" t="inlineStr">
         <is>
-          <t>Silao, Guanajuato</t>
+          <t>Guadalajara, Jalisco</t>
         </is>
       </c>
       <c r="K215" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Kristian Uriel Martínez Zavala, El Silaoense MX</t>
+          <t>Periodista encuentra nota de amenaza de muerte dentro de su camioneta</t>
         </is>
       </c>
       <c r="L215" s="5" t="inlineStr">
         <is>
-          <t>Documentado por ARTICLE 19 como asesinato en posible relación con su labor periodística. Ubicación aproximada (cabecera municipal). Figura como número 170 en el registro de periodistas asesinados de ARTICLE 19.</t>
+          <t>El 25 de junio de 2025 una periodista halló roto un cristal de su vehículo y una nota con la leyenda 'Te vas a morir'; ARTICLE 19 exigió acción inmediata del Estado. En 2025 la organización documentó 110 amenazas, una cada cuatro días. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="M215" s="3" t="inlineStr">
@@ -17146,7 +17254,7 @@
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>ev-047</t>
+          <t>ev-079</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -17156,63 +17264,63 @@
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>periodista</t>
+          <t>defensor</t>
         </is>
       </c>
       <c r="D216" s="4" t="inlineStr">
         <is>
-          <t>proteccion</t>
+          <t>asesinato</t>
         </is>
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
-          <t>no aplica</t>
+          <t>masculino</t>
         </is>
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>cifra oficial</t>
+          <t>asesinato de persona defensora ambiental</t>
         </is>
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="H216" s="3" t="n">
-        <v>24.809</v>
+        <v>19.684</v>
       </c>
       <c r="I216" s="3" t="n">
-        <v>-107.394</v>
+        <v>-101.954</v>
       </c>
       <c r="J216" s="5" t="inlineStr">
         <is>
-          <t>Culiacán, Sinaloa</t>
+          <t>Cherán, Michoacán</t>
         </is>
       </c>
       <c r="K216" s="5" t="inlineStr">
         <is>
-          <t>Instituto de Protección de Sinaloa atiende a 77 periodistas y defensores en medio año de crisis</t>
+          <t>Asesinato de Francisco Macías Sánchez, integrante de la ronda comunitaria de Cherán</t>
         </is>
       </c>
       <c r="L216" s="5" t="inlineStr">
         <is>
-          <t>En seis meses de la pugna entre facciones del Cártel de Sinaloa, el Instituto otorgó 333 medidas cautelares a periodistas, activistas y 16 familiares. Agresiones más comunes: amenazas, disparos contra medios, daños a vehículos y viviendas, privación de la libertad y censura. Ubicación aproximada (cabecera municipal).</t>
+          <t>De 18 años, patrullaba el bosque comunal cuando un grupo del crimen organizado atacó a la ronda en las afueras del Rancho de Pino; otro comunero resultó herido. Fuente: memorial del informe CEMDA 2025. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="M216" s="3" t="inlineStr">
         <is>
-          <t>instituto-sinaloa</t>
+          <t>cemda</t>
         </is>
       </c>
       <c r="N216" s="3" t="inlineStr">
         <is>
-          <t>https://www.noroeste.com.mx/culiacan/atiende-instituto-de-proteccion-a-77-periodistas-y-activistas-de-sinaloa-en-medio-de-crisis-de-violencia-BI11082146</t>
+          <t>https://cemda.org.mx/wp-content/uploads/2026/04/Informe-Defensores-2025_Web_260415_173954.pdf</t>
         </is>
       </c>
       <c r="O216" s="3" t="inlineStr">
         <is>
-          <t>oficial</t>
+          <t>organización</t>
         </is>
       </c>
       <c r="P216" s="3" t="inlineStr">
@@ -17224,7 +17332,7 @@
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
         <is>
-          <t>ev-048</t>
+          <t>ev-053</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -17239,43 +17347,43 @@
       </c>
       <c r="D217" s="4" t="inlineStr">
         <is>
-          <t>agresion</t>
+          <t>asesinato</t>
         </is>
       </c>
       <c r="E217" s="3" t="inlineStr">
         <is>
-          <t>no determinado</t>
+          <t>masculino</t>
         </is>
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
-          <t>agresión física por autoridad</t>
+          <t>asesinato de periodista</t>
         </is>
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H217" s="3" t="n">
-        <v>17.989</v>
+        <v>27.493</v>
       </c>
       <c r="I217" s="3" t="n">
-        <v>-92.93000000000001</v>
+        <v>-109.938</v>
       </c>
       <c r="J217" s="5" t="inlineStr">
         <is>
-          <t>Villahermosa, Tabasco</t>
+          <t>Ciudad Obregón, Sonora</t>
         </is>
       </c>
       <c r="K217" s="5" t="inlineStr">
         <is>
-          <t>Fotoperiodista de El Universal lesionado por agente de seguridad estatal durante cobertura</t>
+          <t>Asesinato de Ángel Sevilla, Noticias 644</t>
         </is>
       </c>
       <c r="L217" s="5" t="inlineStr">
         <is>
-          <t>Derribado y golpeado por una persona en función policial de la Secretaría de Seguridad de Tabasco mientras cubría un homicidio. ARTICLE 19 registró 53 agresiones físicas en 2025, con participación recurrente de agentes del Estado. Ubicación aproximada (cabecera municipal).</t>
+          <t>Documentado por ARTICLE 19 como asesinato en posible relación con su labor periodística. Ubicación aproximada (el informe solo indica Sonora). Figura como número 173 en el registro de periodistas asesinados de ARTICLE 19.</t>
         </is>
       </c>
       <c r="M217" s="3" t="inlineStr">
@@ -17302,7 +17410,7 @@
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
         <is>
-          <t>ev-049</t>
+          <t>ev-054</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -17332,28 +17440,28 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H218" s="3" t="n">
-        <v>21.298</v>
+        <v>16.863</v>
       </c>
       <c r="I218" s="3" t="n">
-        <v>-100.517</v>
+        <v>-99.88200000000001</v>
       </c>
       <c r="J218" s="5" t="inlineStr">
         <is>
-          <t>San Luis de la Paz, Guanajuato</t>
+          <t>Acapulco, Guerrero</t>
         </is>
       </c>
       <c r="K218" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Raúl Irán Villarreal Belmont, Observatorio Ciudadano San Luis de la Paz</t>
+          <t>Asesinato de Ronald Paz Pedro, NotiExpress Pedro</t>
         </is>
       </c>
       <c r="L218" s="5" t="inlineStr">
         <is>
-          <t>Documentado por ARTICLE 19 como asesinato en posible relación con su labor periodística. Ubicación aproximada (cabecera municipal). Figura como número 171 en el registro de periodistas asesinados de ARTICLE 19.</t>
+          <t>Segundo periodista asesinado en Acapulco en 2025, según ARTICLE 19 y RSF. Ubicación aproximada (cabecera municipal). Figura como número 174 en el registro de periodistas asesinados de ARTICLE 19.</t>
         </is>
       </c>
       <c r="M218" s="3" t="inlineStr">
@@ -17380,61 +17488,73 @@
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
         <is>
-          <t>ev-014</t>
+          <t>ev-080</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento</t>
-        </is>
-      </c>
-      <c r="C219" s="3" t="inlineStr"/>
-      <c r="D219" s="4" t="inlineStr"/>
-      <c r="E219" s="3" t="inlineStr"/>
+          <t>periodistas</t>
+        </is>
+      </c>
+      <c r="C219" s="3" t="inlineStr">
+        <is>
+          <t>defensor</t>
+        </is>
+      </c>
+      <c r="D219" s="4" t="inlineStr">
+        <is>
+          <t>asesinato</t>
+        </is>
+      </c>
+      <c r="E219" s="3" t="inlineStr">
+        <is>
+          <t>masculino</t>
+        </is>
+      </c>
       <c r="F219" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento masivo</t>
+          <t>asesinato de persona defensora ambiental</t>
         </is>
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="H219" s="3" t="n">
-        <v>19.088</v>
+        <v>17.546</v>
       </c>
       <c r="I219" s="3" t="n">
-        <v>-102.353</v>
+        <v>-98.577</v>
       </c>
       <c r="J219" s="5" t="inlineStr">
         <is>
-          <t>Apatzingán, Michoacán</t>
+          <t>Tlapa de Comonfort, Guerrero</t>
         </is>
       </c>
       <c r="K219" s="5" t="inlineStr">
         <is>
-          <t>Cerca de 500 familias desplazadas de la zona rural de Apatzingán desde inicios de 2025</t>
+          <t>Asesinato de Sergio Hugo Ureiro Castañeda, defensor de la Plazuela de los Cántaros</t>
         </is>
       </c>
       <c r="L219" s="5" t="inlineStr">
         <is>
-          <t>Una diputada local informó que desde inicios de 2025 unas 500 familias habían salido de localidades como Las Huertas, El Alcalde, El Guayabo, Holanda, El Morado, Bateas, Loma de Los Hoyos y Presa del Rosario por minas terrestres y enfrentamientos; más de 300 habían regresado y unas 150 seguían fuera. Ubicación aproximada (cabecera municipal).</t>
+          <t>Líder del movimiento que recuperó la plaza pública y área verde de Tlapa; un mes antes su casa fue incendiada. Asesinado en una gasolinera del centro. Fuente: memorial del informe CEMDA 2025. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="M219" s="3" t="inlineStr">
         <is>
-          <t>jornada</t>
+          <t>cemda</t>
         </is>
       </c>
       <c r="N219" s="3" t="inlineStr">
         <is>
-          <t>https://www.jornada.com.mx/noticia/2025/03/31/estados/cerca-de-500-familias-en-michoacan-se-han-desplazado-de-manera-forzada</t>
+          <t>https://cemda.org.mx/wp-content/uploads/2026/04/Informe-Defensores-2025_Web_260415_173954.pdf</t>
         </is>
       </c>
       <c r="O219" s="3" t="inlineStr">
         <is>
-          <t>prensa</t>
+          <t>organización</t>
         </is>
       </c>
       <c r="P219" s="3" t="inlineStr">
@@ -17446,61 +17566,73 @@
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
         <is>
-          <t>ev-015</t>
+          <t>ev-055</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento</t>
-        </is>
-      </c>
-      <c r="C220" s="3" t="inlineStr"/>
-      <c r="D220" s="4" t="inlineStr"/>
-      <c r="E220" s="3" t="inlineStr"/>
+          <t>periodistas</t>
+        </is>
+      </c>
+      <c r="C220" s="3" t="inlineStr">
+        <is>
+          <t>periodista</t>
+        </is>
+      </c>
+      <c r="D220" s="4" t="inlineStr">
+        <is>
+          <t>asesinato</t>
+        </is>
+      </c>
+      <c r="E220" s="3" t="inlineStr">
+        <is>
+          <t>masculino</t>
+        </is>
+      </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
-          <t>padrón oficial</t>
+          <t>asesinato de periodista</t>
         </is>
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2025-10-25</t>
         </is>
       </c>
       <c r="H220" s="3" t="n">
-        <v>23.284</v>
+        <v>24.027</v>
       </c>
       <c r="I220" s="3" t="n">
-        <v>-106.069</v>
+        <v>-104.653</v>
       </c>
       <c r="J220" s="5" t="inlineStr">
         <is>
-          <t>Concordia, Sinaloa</t>
+          <t>Durango, Durango</t>
         </is>
       </c>
       <c r="K220" s="5" t="inlineStr">
         <is>
-          <t>Padrón Sebides: 261 familias desplazadas en Concordia (septiembre 2024 a marzo 2025)</t>
+          <t>Asesinato de Miguel Ángel Beltrán Martínez, periodista independiente</t>
         </is>
       </c>
       <c r="L220" s="5" t="inlineStr">
         <is>
-          <t>Entre septiembre de 2024 y marzo de 2025 Sebides registró 810 familias desplazadas de 104 comunidades en Sinaloa; a Concordia corresponden 261 familias. Los nombres de las comunidades son reservados por la ley estatal. Ubicación aproximada (cabecera municipal).</t>
+          <t>Documentado por ARTICLE 19 como asesinato en posible relación con su labor periodística. Ubicación aproximada (el informe solo indica Durango). Figura como número 175 en el registro de periodistas asesinados de ARTICLE 19.</t>
         </is>
       </c>
       <c r="M220" s="3" t="inlineStr">
         <is>
-          <t>sebides</t>
+          <t>article19</t>
         </is>
       </c>
       <c r="N220" s="3" t="inlineStr">
         <is>
-          <t>https://riodoce.mx/2025/04/07/mas-de-800-familias-desplazadas-por-la-violencia-en-sinaloa/</t>
+          <t>https://articulo19.org/wp-content/uploads/2026/05/Estructuras-del-Silencio-Informe-Anual-2025-A19-MXCA_compressed.pdf</t>
         </is>
       </c>
       <c r="O220" s="3" t="inlineStr">
         <is>
-          <t>oficial</t>
+          <t>organización</t>
         </is>
       </c>
       <c r="P220" s="3" t="inlineStr">
@@ -17512,61 +17644,73 @@
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
         <is>
-          <t>ev-016</t>
+          <t>ev-081</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento</t>
-        </is>
-      </c>
-      <c r="C221" s="3" t="inlineStr"/>
-      <c r="D221" s="4" t="inlineStr"/>
-      <c r="E221" s="3" t="inlineStr"/>
+          <t>periodistas</t>
+        </is>
+      </c>
+      <c r="C221" s="3" t="inlineStr">
+        <is>
+          <t>defensor</t>
+        </is>
+      </c>
+      <c r="D221" s="4" t="inlineStr">
+        <is>
+          <t>asesinato</t>
+        </is>
+      </c>
+      <c r="E221" s="3" t="inlineStr">
+        <is>
+          <t>masculino</t>
+        </is>
+      </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>padrón oficial</t>
+          <t>asesinato de persona defensora ambiental</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="H221" s="3" t="n">
-        <v>24.412</v>
+        <v>19.237</v>
       </c>
       <c r="I221" s="3" t="n">
-        <v>-106.69</v>
+        <v>-104.567</v>
       </c>
       <c r="J221" s="5" t="inlineStr">
         <is>
-          <t>Cosalá, Sinaloa</t>
+          <t>Cihuatlán, Jalisco</t>
         </is>
       </c>
       <c r="K221" s="5" t="inlineStr">
         <is>
-          <t>Padrón Sebides: 238 familias desplazadas en Cosalá (septiembre 2024 a marzo 2025)</t>
+          <t>Asesinato de Cándido Esaú Román Pérez, abogado y representante ejidal</t>
         </is>
       </c>
       <c r="L221" s="5" t="inlineStr">
         <is>
-          <t>Entre septiembre de 2024 y marzo de 2025 Sebides registró 810 familias desplazadas de 104 comunidades en Sinaloa; a Cosalá corresponden 238 familias. Los nombres de las comunidades son reservados por la ley estatal. Ubicación aproximada (cabecera municipal).</t>
+          <t>Defendía al ejido General Emiliano Zapata frente al despojo de tierras en Melaque, con amparo obtenido; asesinado afuera de su casa. La fiscalía reconoce su activismo como línea principal. Fuente: memorial del informe CEMDA 2025. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="M221" s="3" t="inlineStr">
         <is>
-          <t>sebides</t>
+          <t>cemda</t>
         </is>
       </c>
       <c r="N221" s="3" t="inlineStr">
         <is>
-          <t>https://riodoce.mx/2025/04/07/mas-de-800-familias-desplazadas-por-la-violencia-en-sinaloa/</t>
+          <t>https://cemda.org.mx/wp-content/uploads/2026/04/Informe-Defensores-2025_Web_260415_173954.pdf</t>
         </is>
       </c>
       <c r="O221" s="3" t="inlineStr">
         <is>
-          <t>oficial</t>
+          <t>organización</t>
         </is>
       </c>
       <c r="P221" s="3" t="inlineStr">
@@ -17578,61 +17722,73 @@
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t>ev-017</t>
+          <t>ev-082</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento</t>
-        </is>
-      </c>
-      <c r="C222" s="3" t="inlineStr"/>
-      <c r="D222" s="4" t="inlineStr"/>
-      <c r="E222" s="3" t="inlineStr"/>
+          <t>periodistas</t>
+        </is>
+      </c>
+      <c r="C222" s="3" t="inlineStr">
+        <is>
+          <t>defensor</t>
+        </is>
+      </c>
+      <c r="D222" s="4" t="inlineStr">
+        <is>
+          <t>asesinato</t>
+        </is>
+      </c>
+      <c r="E222" s="3" t="inlineStr">
+        <is>
+          <t>masculino</t>
+        </is>
+      </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
-          <t>padrón oficial</t>
+          <t>asesinato de persona defensora ambiental</t>
         </is>
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H222" s="3" t="n">
-        <v>24.809</v>
+        <v>22.345</v>
       </c>
       <c r="I222" s="3" t="n">
-        <v>-107.394</v>
+        <v>-103.605</v>
       </c>
       <c r="J222" s="5" t="inlineStr">
         <is>
-          <t>Culiacán, Sinaloa</t>
+          <t>Azqueltán, Villa Guerrero, Jalisco</t>
         </is>
       </c>
       <c r="K222" s="5" t="inlineStr">
         <is>
-          <t>Padrón Sebides: 127 familias desplazadas en Culiacán (septiembre 2024 a marzo 2025)</t>
+          <t>Asesinato de Marcos Aguilar Rojas, representante agrario de Azqueltán</t>
         </is>
       </c>
       <c r="L222" s="5" t="inlineStr">
         <is>
-          <t>Entre septiembre de 2024 y marzo de 2025 Sebides registró 810 familias desplazadas de 104 comunidades en Sinaloa; a Culiacán corresponden 127 familias. Los nombres de las comunidades son reservados por la ley estatal. Ubicación aproximada (cabecera municipal).</t>
+          <t>Comunidad tepehuana-wixárika en juicio agrario por 45 mil hectáreas; atacado con su hermano al retirar ganado invasor en el predio comunal El Caracol. Los agresores están identificados y sin proceso. Fuente: memorial del informe CEMDA 2025. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="M222" s="3" t="inlineStr">
         <is>
-          <t>sebides</t>
+          <t>cemda</t>
         </is>
       </c>
       <c r="N222" s="3" t="inlineStr">
         <is>
-          <t>https://riodoce.mx/2025/04/07/mas-de-800-familias-desplazadas-por-la-violencia-en-sinaloa/</t>
+          <t>https://cemda.org.mx/wp-content/uploads/2026/04/Informe-Defensores-2025_Web_260415_173954.pdf</t>
         </is>
       </c>
       <c r="O222" s="3" t="inlineStr">
         <is>
-          <t>oficial</t>
+          <t>organización</t>
         </is>
       </c>
       <c r="P222" s="3" t="inlineStr">
@@ -17644,61 +17800,73 @@
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
         <is>
-          <t>ev-018</t>
+          <t>ev-056</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento</t>
-        </is>
-      </c>
-      <c r="C223" s="3" t="inlineStr"/>
-      <c r="D223" s="4" t="inlineStr"/>
-      <c r="E223" s="3" t="inlineStr"/>
+          <t>periodistas</t>
+        </is>
+      </c>
+      <c r="C223" s="3" t="inlineStr">
+        <is>
+          <t>periodista</t>
+        </is>
+      </c>
+      <c r="D223" s="4" t="inlineStr">
+        <is>
+          <t>acoso_judicial</t>
+        </is>
+      </c>
+      <c r="E223" s="3" t="inlineStr">
+        <is>
+          <t>masculino</t>
+        </is>
+      </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
-          <t>padrón oficial</t>
+          <t>acoso judicial</t>
         </is>
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="H223" s="3" t="n">
-        <v>22.991</v>
+        <v>19.043</v>
       </c>
       <c r="I223" s="3" t="n">
-        <v>-105.857</v>
+        <v>-98.19799999999999</v>
       </c>
       <c r="J223" s="5" t="inlineStr">
         <is>
-          <t>Rosario, Sinaloa</t>
+          <t>Puebla, Puebla</t>
         </is>
       </c>
       <c r="K223" s="5" t="inlineStr">
         <is>
-          <t>Padrón Sebides: 65 familias desplazadas en Rosario (septiembre 2024 a marzo 2025)</t>
+          <t>Vinculación a proceso del director del portal e-consulta por su labor periodística</t>
         </is>
       </c>
       <c r="L223" s="5" t="inlineStr">
         <is>
-          <t>Entre septiembre de 2024 y marzo de 2025 Sebides registró 810 familias desplazadas de 104 comunidades en Sinaloa; a Rosario corresponden 65 familias. Los nombres de las comunidades son reservados por la ley estatal. Ubicación aproximada (cabecera municipal).</t>
+          <t>ARTICLE 19 señaló el caso como precedente grave de uso del derecho penal para intimidar. En 2025 documentó 69 periodistas y medios víctimas de acoso judicial en 21 entidades. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="M223" s="3" t="inlineStr">
         <is>
-          <t>sebides</t>
+          <t>article19</t>
         </is>
       </c>
       <c r="N223" s="3" t="inlineStr">
         <is>
-          <t>https://riodoce.mx/2025/04/07/mas-de-800-familias-desplazadas-por-la-violencia-en-sinaloa/</t>
+          <t>https://articulo19.org/wp-content/uploads/2026/05/Estructuras-del-Silencio-Informe-Anual-2025-A19-MXCA_compressed.pdf</t>
         </is>
       </c>
       <c r="O223" s="3" t="inlineStr">
         <is>
-          <t>oficial</t>
+          <t>organización</t>
         </is>
       </c>
       <c r="P223" s="3" t="inlineStr">
@@ -17710,61 +17878,73 @@
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t>ev-019</t>
+          <t>ev-057</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento</t>
-        </is>
-      </c>
-      <c r="C224" s="3" t="inlineStr"/>
-      <c r="D224" s="4" t="inlineStr"/>
-      <c r="E224" s="3" t="inlineStr"/>
+          <t>periodistas</t>
+        </is>
+      </c>
+      <c r="C224" s="3" t="inlineStr">
+        <is>
+          <t>periodista</t>
+        </is>
+      </c>
+      <c r="D224" s="4" t="inlineStr">
+        <is>
+          <t>acoso_judicial</t>
+        </is>
+      </c>
+      <c r="E224" s="3" t="inlineStr">
+        <is>
+          <t>no determinado</t>
+        </is>
+      </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t>padrón oficial</t>
+          <t>acoso judicial</t>
         </is>
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="H224" s="3" t="n">
-        <v>23.921</v>
+        <v>18.134</v>
       </c>
       <c r="I224" s="3" t="n">
-        <v>-106.892</v>
+        <v>-94.422</v>
       </c>
       <c r="J224" s="5" t="inlineStr">
         <is>
-          <t>Elota, Sinaloa</t>
+          <t>Coatzacoalcos, Veracruz</t>
         </is>
       </c>
       <c r="K224" s="5" t="inlineStr">
         <is>
-          <t>Padrón Sebides: 41 familias desplazadas en Elota (septiembre 2024 a marzo 2025)</t>
+          <t>Fiscalía de Veracruz imputa a periodista por terrorismo por hechos ligados a su labor</t>
         </is>
       </c>
       <c r="L224" s="5" t="inlineStr">
         <is>
-          <t>Entre septiembre de 2024 y marzo de 2025 Sebides registró 810 familias desplazadas de 104 comunidades en Sinaloa; a Elota corresponden 41 familias. Los nombres de las comunidades son reservados por la ley estatal. Ubicación aproximada (cabecera municipal).</t>
+          <t>La imputación fue desestimada, pero se mantenían vigentes otras dos. ARTICLE 19 la calificó como uno de los episodios más alarmantes del año. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="M224" s="3" t="inlineStr">
         <is>
-          <t>sebides</t>
+          <t>article19</t>
         </is>
       </c>
       <c r="N224" s="3" t="inlineStr">
         <is>
-          <t>https://riodoce.mx/2025/04/07/mas-de-800-familias-desplazadas-por-la-violencia-en-sinaloa/</t>
+          <t>https://articulo19.org/wp-content/uploads/2026/05/Estructuras-del-Silencio-Informe-Anual-2025-A19-MXCA_compressed.pdf</t>
         </is>
       </c>
       <c r="O224" s="3" t="inlineStr">
         <is>
-          <t>oficial</t>
+          <t>organización</t>
         </is>
       </c>
       <c r="P224" s="3" t="inlineStr">
@@ -17776,61 +17956,73 @@
     <row r="225">
       <c r="A225" s="3" t="inlineStr">
         <is>
-          <t>ev-020</t>
+          <t>ev-058</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento</t>
-        </is>
-      </c>
-      <c r="C225" s="3" t="inlineStr"/>
-      <c r="D225" s="4" t="inlineStr"/>
-      <c r="E225" s="3" t="inlineStr"/>
+          <t>periodistas</t>
+        </is>
+      </c>
+      <c r="C225" s="3" t="inlineStr">
+        <is>
+          <t>periodista</t>
+        </is>
+      </c>
+      <c r="D225" s="4" t="inlineStr">
+        <is>
+          <t>asesinato</t>
+        </is>
+      </c>
+      <c r="E225" s="3" t="inlineStr">
+        <is>
+          <t>masculino</t>
+        </is>
+      </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
-          <t>padrón oficial</t>
+          <t>asesinato de periodista</t>
         </is>
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H225" s="3" t="n">
-        <v>23.936</v>
+        <v>20.533</v>
       </c>
       <c r="I225" s="3" t="n">
-        <v>-106.425</v>
+        <v>-97.459</v>
       </c>
       <c r="J225" s="5" t="inlineStr">
         <is>
-          <t>San Ignacio, Sinaloa</t>
+          <t>Poza Rica, Veracruz</t>
         </is>
       </c>
       <c r="K225" s="5" t="inlineStr">
         <is>
-          <t>Padrón Sebides: 40 familias desplazadas en San Ignacio (septiembre 2024 a marzo 2025)</t>
+          <t>Asesinato de Carlos Castro en Poza Rica</t>
         </is>
       </c>
       <c r="L225" s="5" t="inlineStr">
         <is>
-          <t>Entre septiembre de 2024 y marzo de 2025 Sebides registró 810 familias desplazadas de 104 comunidades en Sinaloa; a San Ignacio corresponden 40 familias. Los nombres de las comunidades son reservados por la ley estatal. Ubicación aproximada (cabecera municipal).</t>
+          <t>Asesinado el 8 de enero dentro de un restaurante de la avenida 20 de Noviembre, primer periodista asesinado en 2026 según el recuento de N+ y CPJ. Ubicación aproximada (cabecera municipal). Figura como número 176 (Carlos Leonardo Ramírez Castro) en el registro de periodistas asesinados de ARTICLE 19.</t>
         </is>
       </c>
       <c r="M225" s="3" t="inlineStr">
         <is>
-          <t>sebides</t>
+          <t>nmas</t>
         </is>
       </c>
       <c r="N225" s="3" t="inlineStr">
         <is>
-          <t>https://riodoce.mx/2025/04/07/mas-de-800-familias-desplazadas-por-la-violencia-en-sinaloa/</t>
+          <t>https://www.nmas.com.mx/seguridad/asesinatos/cuantos-y-quienes-son-los-periodistas-asesinados-en-mexico-este-2026/</t>
         </is>
       </c>
       <c r="O225" s="3" t="inlineStr">
         <is>
-          <t>oficial</t>
+          <t>prensa</t>
         </is>
       </c>
       <c r="P225" s="3" t="inlineStr">
@@ -17842,61 +18034,73 @@
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t>ev-021</t>
+          <t>ev-059</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento</t>
-        </is>
-      </c>
-      <c r="C226" s="3" t="inlineStr"/>
-      <c r="D226" s="4" t="inlineStr"/>
-      <c r="E226" s="3" t="inlineStr"/>
+          <t>periodistas</t>
+        </is>
+      </c>
+      <c r="C226" s="3" t="inlineStr">
+        <is>
+          <t>periodista</t>
+        </is>
+      </c>
+      <c r="D226" s="4" t="inlineStr">
+        <is>
+          <t>agresion</t>
+        </is>
+      </c>
+      <c r="E226" s="3" t="inlineStr">
+        <is>
+          <t>masculino</t>
+        </is>
+      </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
-          <t>padrón oficial</t>
+          <t>agresión por autoridad</t>
         </is>
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="H226" s="3" t="n">
-        <v>24.765</v>
+        <v>24.809</v>
       </c>
       <c r="I226" s="3" t="n">
-        <v>-107.702</v>
+        <v>-107.394</v>
       </c>
       <c r="J226" s="5" t="inlineStr">
         <is>
-          <t>Navolato, Sinaloa</t>
+          <t>Culiacán, Sinaloa</t>
         </is>
       </c>
       <c r="K226" s="5" t="inlineStr">
         <is>
-          <t>Padrón Sebides: 38 familias desplazadas en Navolato (septiembre 2024 a marzo 2025)</t>
+          <t>Policía estatal apunta su arma contra reportero de la fuente de seguridad</t>
         </is>
       </c>
       <c r="L226" s="5" t="inlineStr">
         <is>
-          <t>Entre septiembre de 2024 y marzo de 2025 Sebides registró 810 familias desplazadas de 104 comunidades en Sinaloa; a Navolato corresponden 38 familias. Los nombres de las comunidades son reservados por la ley estatal. Ubicación aproximada (cabecera municipal).</t>
+          <t>Tras un enfrentamiento entre fuerzas de seguridad y un grupo armado, agentes de la Policía Estatal Preventiva agredieron a un reportero; el hecho quedó en video. El Instituto de Protección documentó 235 agresiones al gremio entre 2022 y 2025. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="M226" s="3" t="inlineStr">
         <is>
-          <t>sebides</t>
+          <t>proceso</t>
         </is>
       </c>
       <c r="N226" s="3" t="inlineStr">
         <is>
-          <t>https://riodoce.mx/2025/04/07/mas-de-800-familias-desplazadas-por-la-violencia-en-sinaloa/</t>
+          <t>https://www.proceso.com.mx/nacional/estados/2026/1/19/policia-estatal-de-sinaloa-apunta-su-arma-hacia-reportero-en-culiacan-video-366842.html</t>
         </is>
       </c>
       <c r="O226" s="3" t="inlineStr">
         <is>
-          <t>oficial</t>
+          <t>prensa</t>
         </is>
       </c>
       <c r="P226" s="3" t="inlineStr">
@@ -17908,7 +18112,7 @@
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
         <is>
-          <t>ev-050</t>
+          <t>ev-060</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -17918,12 +18122,12 @@
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>periodista</t>
+          <t>defensor</t>
         </is>
       </c>
       <c r="D227" s="4" t="inlineStr">
         <is>
-          <t>desaparicion</t>
+          <t>asesinato</t>
         </is>
       </c>
       <c r="E227" s="3" t="inlineStr">
@@ -17933,43 +18137,43 @@
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>desaparición de periodista</t>
+          <t>asesinato de persona defensora</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="H227" s="3" t="n">
-        <v>22.055</v>
+        <v>19.392</v>
       </c>
       <c r="I227" s="3" t="n">
-        <v>-98.18300000000001</v>
+        <v>-101.278</v>
       </c>
       <c r="J227" s="5" t="inlineStr">
         <is>
-          <t>Pánuco, Veracruz</t>
+          <t>El Zangarro, Villa Madero, Michoacán</t>
         </is>
       </c>
       <c r="K227" s="5" t="inlineStr">
         <is>
-          <t>Desaparición de Miguel Ángel Anaya Castillo, director de Pánuco On Line</t>
+          <t>Asesinato de Roberto Chávez, Comité de Defensa Ambiental de El Zangarro</t>
         </is>
       </c>
       <c r="L227" s="5" t="inlineStr">
         <is>
-          <t>Desaparecido desde el 13 de abril de 2025; mes y medio antes había sido hostigado en su domicilio. ARTICLE 19 contabiliza 32 periodistas desaparecidos desde 2000, concentrados en Tamaulipas, Veracruz y Michoacán. Ubicación aproximada (cabecera municipal). Figura como número 32 en el registro de periodistas desaparecidos de ARTICLE 19.</t>
+          <t>Defensor ambiental de 64 años, asesinado a balazos la noche del 12 de abril al regresar a su casa. CEMDA contabiliza al menos 195 personas defensoras ambientales asesinadas en México entre 2016 y 2026. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="M227" s="3" t="inlineStr">
         <is>
-          <t>article19</t>
+          <t>cemda</t>
         </is>
       </c>
       <c r="N227" s="3" t="inlineStr">
         <is>
-          <t>https://articulo19.org/wp-content/uploads/2026/05/Estructuras-del-Silencio-Informe-Anual-2025-A19-MXCA_compressed.pdf</t>
+          <t>https://grupoanimal.mx/explicaciones/defensores-ambientales-asesinados-mexico</t>
         </is>
       </c>
       <c r="O227" s="3" t="inlineStr">
@@ -17986,7 +18190,7 @@
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t>ev-078</t>
+          <t>ev-061</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -18006,38 +18210,38 @@
       </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
-          <t>femenino</t>
+          <t>masculino</t>
         </is>
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
-          <t>asesinato de persona defensora ambiental</t>
+          <t>desaparición y asesinato de persona defensora</t>
         </is>
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H228" s="3" t="n">
-        <v>20.773</v>
+        <v>19.401</v>
       </c>
       <c r="I228" s="3" t="n">
-        <v>-103.693</v>
+        <v>-101.732</v>
       </c>
       <c r="J228" s="5" t="inlineStr">
         <is>
-          <t>El Arenal, Jalisco</t>
+          <t>Zirahuén, Salvador Escalante, Michoacán</t>
         </is>
       </c>
       <c r="K228" s="5" t="inlineStr">
         <is>
-          <t>Desaparición y asesinato de Karina Ruiz Ocampo, defensora del derecho al agua</t>
+          <t>Lázaro Mendoza Ramírez, defensor de la región lacustre de Zirahuén, desaparecido y hallado sin vida</t>
         </is>
       </c>
       <c r="L228" s="5" t="inlineStr">
         <is>
-          <t>Representante legal de la asociación vecinal La Cima, Nuestra Prioridad; sacada de su casa por la fuerza el 14 de abril y hallada sin vida el 3 de mayo. Se investiga como feminicidio. Fuente: memorial del informe CEMDA 2025. Ubicación aproximada (cabecera municipal).</t>
+          <t>Desaparecido el 14 de abril; su cuerpo fue localizado calcinado en su camioneta e identificado por ADN. Segundo defensor ambiental asesinado en Michoacán en menos de una semana. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="M228" s="3" t="inlineStr">
@@ -18047,7 +18251,7 @@
       </c>
       <c r="N228" s="3" t="inlineStr">
         <is>
-          <t>https://cemda.org.mx/wp-content/uploads/2026/04/Informe-Defensores-2025_Web_260415_173954.pdf</t>
+          <t>https://grupoanimal.mx/sociedad/ambientalistas-asesinados-semana-michoacan</t>
         </is>
       </c>
       <c r="O228" s="3" t="inlineStr">
@@ -18064,7 +18268,7 @@
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
         <is>
-          <t>ev-077</t>
+          <t>ev-062</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -18074,58 +18278,58 @@
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>defensor</t>
+          <t>periodista</t>
         </is>
       </c>
       <c r="D229" s="4" t="inlineStr">
         <is>
-          <t>asesinato</t>
+          <t>informe</t>
         </is>
       </c>
       <c r="E229" s="3" t="inlineStr">
         <is>
-          <t>masculino</t>
+          <t>no aplica</t>
         </is>
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>asesinato de persona defensora ambiental</t>
+          <t>informe</t>
         </is>
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H229" s="3" t="n">
-        <v>16.982</v>
+        <v>19.432</v>
       </c>
       <c r="I229" s="3" t="n">
-        <v>-99.7</v>
+        <v>-99.133</v>
       </c>
       <c r="J229" s="5" t="inlineStr">
         <is>
-          <t>Cacahuatepec, Acapulco, Guerrero</t>
+          <t>Ciudad de México</t>
         </is>
       </c>
       <c r="K229" s="5" t="inlineStr">
         <is>
-          <t>Ataque mortal contra Marco Antonio Suástegui, líder del CECOP</t>
+          <t>ARTICLE 19: 451 agresiones a la prensa en 2025, siete asesinatos y ocho tentativas</t>
         </is>
       </c>
       <c r="L229" s="5" t="inlineStr">
         <is>
-          <t>Defensor del río Papagayo y opositor histórico a la presa La Parota; atacado al salir de la playa Icacos y fallecido ocho días después. Su familia estaba incorporada al Mecanismo tras la desaparición de su hermano en 2021. Fuente: memorial del informe CEMDA 2025. Ubicación aproximada (cabecera municipal).</t>
+          <t>Informe Estructuras del silencio. Una agresión cada 19 horas; 44 por ciento ambiente hostil, 34 abuso del poder público, 12 violencia física. El Estado fue el agresor en 227 casos. Ciudad de México, Puebla y Veracruz encabezan; Sinaloa registra solo nueve casos, lo que la organización atribuye a autocensura y a denuncias por canales confidenciales. 2025 fue también el año más letal para personas buscadoras (siete asesinatos y cuatro desapariciones). Cifra nacional ubicada en la capital.</t>
         </is>
       </c>
       <c r="M229" s="3" t="inlineStr">
         <is>
-          <t>cemda</t>
+          <t>article19</t>
         </is>
       </c>
       <c r="N229" s="3" t="inlineStr">
         <is>
-          <t>https://cemda.org.mx/wp-content/uploads/2026/04/Informe-Defensores-2025_Web_260415_173954.pdf</t>
+          <t>https://articulo19.org/wp-content/uploads/2026/05/Estructuras-del-Silencio-Informe-Anual-2025-A19-MXCA_compressed.pdf</t>
         </is>
       </c>
       <c r="O229" s="3" t="inlineStr">
@@ -18142,7 +18346,7 @@
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>ev-051</t>
+          <t>ev-063</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -18152,63 +18356,63 @@
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>periodista</t>
+          <t>ambos</t>
         </is>
       </c>
       <c r="D230" s="4" t="inlineStr">
         <is>
-          <t>asesinato</t>
+          <t>agresion</t>
         </is>
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>masculino</t>
+          <t>no determinado</t>
         </is>
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
-          <t>asesinato de periodista</t>
+          <t>agresión por autoridad</t>
         </is>
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H230" s="3" t="n">
-        <v>16.863</v>
+        <v>24.809</v>
       </c>
       <c r="I230" s="3" t="n">
-        <v>-99.88200000000001</v>
+        <v>-107.394</v>
       </c>
       <c r="J230" s="5" t="inlineStr">
         <is>
-          <t>Acapulco, Guerrero</t>
+          <t>La Conquista, Culiacán, Sinaloa</t>
         </is>
       </c>
       <c r="K230" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de José Carlos González Herrera, El Guerrero / Opinión Ciudadana</t>
+          <t>Militares golpean a dos periodistas acreditados durante un operativo</t>
         </is>
       </c>
       <c r="L230" s="5" t="inlineStr">
         <is>
-          <t>Documentado por ARTICLE 19 como asesinato en posible relación con su labor periodística. Ubicación aproximada (cabecera municipal). Figura como número 172 en el registro de periodistas asesinados de ARTICLE 19.</t>
+          <t>Elementos del Ejército golpearon y empujaron a dos periodistas identificados y arrebataron un teléfono; un agente del GOES estatal intervino para protegerlos. El Instituto documentó 125 agresiones entre agosto de 2022 y febrero de 2026, 45 atribuidas a particulares presuntamente vinculados con el crimen. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="M230" s="3" t="inlineStr">
         <is>
-          <t>article19</t>
+          <t>revistaespejo</t>
         </is>
       </c>
       <c r="N230" s="3" t="inlineStr">
         <is>
-          <t>https://articulo19.org/wp-content/uploads/2026/05/Estructuras-del-Silencio-Informe-Anual-2025-A19-MXCA_compressed.pdf</t>
+          <t>https://revistaespejo.com/2026/05/14/periodistas-de-culiacan-acusan-agresiones-por-parte-de-militares/</t>
         </is>
       </c>
       <c r="O230" s="3" t="inlineStr">
         <is>
-          <t>organización</t>
+          <t>prensa</t>
         </is>
       </c>
       <c r="P230" s="3" t="inlineStr">
@@ -18220,29 +18424,41 @@
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
         <is>
-          <t>ev-002</t>
+          <t>ev-064</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>migracion</t>
-        </is>
-      </c>
-      <c r="C231" s="3" t="inlineStr"/>
-      <c r="D231" s="4" t="inlineStr"/>
-      <c r="E231" s="3" t="inlineStr"/>
+          <t>periodistas</t>
+        </is>
+      </c>
+      <c r="C231" s="3" t="inlineStr">
+        <is>
+          <t>periodista</t>
+        </is>
+      </c>
+      <c r="D231" s="4" t="inlineStr">
+        <is>
+          <t>proteccion</t>
+        </is>
+      </c>
+      <c r="E231" s="3" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
-          <t>rescate</t>
+          <t>cifra gremial</t>
         </is>
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H231" s="3" t="n">
-        <v>24.8091</v>
+        <v>24.809</v>
       </c>
       <c r="I231" s="3" t="n">
         <v>-107.394</v>
@@ -18254,35 +18470,39 @@
       </c>
       <c r="K231" s="5" t="inlineStr">
         <is>
-          <t>Ejemplo: personas migrantes rescatadas en carretera</t>
+          <t>Asociación 7 de Junio: más de 100 incidentes contra periodistas desde septiembre de 2024</t>
         </is>
       </c>
       <c r="L231" s="5" t="inlineStr">
         <is>
-          <t>Registro de ejemplo basado en nota de prensa. Reemplazar.</t>
+          <t>El presidente de la asociación denunció que menos de 20 casos se han formalizado ante la vicefiscalía especializada y que las autoridades reclasifican agresiones como robos sin analizar el contexto periodístico. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="M231" s="3" t="inlineStr">
         <is>
-          <t>prensa-local</t>
-        </is>
-      </c>
-      <c r="N231" s="3" t="inlineStr"/>
+          <t>asociacion-7-junio</t>
+        </is>
+      </c>
+      <c r="N231" s="3" t="inlineStr">
+        <is>
+          <t>https://www.sectorprimario.mx/2026/05/15/mas-de-100-agresiones-silencian-al-periodismo-en-sinaloa/</t>
+        </is>
+      </c>
       <c r="O231" s="3" t="inlineStr">
         <is>
-          <t>prensa</t>
+          <t>organización</t>
         </is>
       </c>
       <c r="P231" s="3" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>ev-052</t>
+          <t>ev-065</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -18297,7 +18517,7 @@
       </c>
       <c r="D232" s="4" t="inlineStr">
         <is>
-          <t>amenaza</t>
+          <t>asesinato</t>
         </is>
       </c>
       <c r="E232" s="3" t="inlineStr">
@@ -18307,48 +18527,48 @@
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
-          <t>amenaza</t>
+          <t>secuestro y asesinato de periodista</t>
         </is>
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H232" s="3" t="n">
-        <v>20.674</v>
+        <v>17.995</v>
       </c>
       <c r="I232" s="3" t="n">
-        <v>-103.347</v>
+        <v>-94.348</v>
       </c>
       <c r="J232" s="5" t="inlineStr">
         <is>
-          <t>Guadalajara, Jalisco</t>
+          <t>Moloacán, Veracruz</t>
         </is>
       </c>
       <c r="K232" s="5" t="inlineStr">
         <is>
-          <t>Periodista encuentra nota de amenaza de muerte dentro de su camioneta</t>
+          <t>Roxana Guzmán Ramírez, Pulso Informativo del Sureste, secuestrada y hallada sin vida</t>
         </is>
       </c>
       <c r="L232" s="5" t="inlineStr">
         <is>
-          <t>El 25 de junio de 2025 una periodista halló roto un cristal de su vehículo y una nota con la leyenda 'Te vas a morir'; ARTICLE 19 exigió acción inmediata del Estado. En 2025 la organización documentó 110 amenazas, una cada cuatro días. Ubicación aproximada (cabecera municipal).</t>
+          <t>Sacada de su casa por hombres armados el 2 de junio de 2026; sus restos fueron identificados el 3 de julio en un predio de Moloacán. Las autoridades señalaron a funcionarios municipales como responsables, según CPJ. Ubicación aproximada (cabecera municipal). Figura como número 178 en el registro de periodistas asesinados de ARTICLE 19.</t>
         </is>
       </c>
       <c r="M232" s="3" t="inlineStr">
         <is>
-          <t>article19</t>
+          <t>excelsior</t>
         </is>
       </c>
       <c r="N232" s="3" t="inlineStr">
         <is>
-          <t>https://articulo19.org/wp-content/uploads/2026/05/Estructuras-del-Silencio-Informe-Anual-2025-A19-MXCA_compressed.pdf</t>
+          <t>https://www.excelsior.com.mx/nacional/suma-mexico-seis-periodistas-asesinados-2026-cpj-exige-frenar-ataques-y-fin-impunidad</t>
         </is>
       </c>
       <c r="O232" s="3" t="inlineStr">
         <is>
-          <t>organización</t>
+          <t>prensa</t>
         </is>
       </c>
       <c r="P232" s="3" t="inlineStr">
@@ -18360,17 +18580,29 @@
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
         <is>
-          <t>ev-022</t>
+          <t>ev-066</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento</t>
-        </is>
-      </c>
-      <c r="C233" s="3" t="inlineStr"/>
-      <c r="D233" s="4" t="inlineStr"/>
-      <c r="E233" s="3" t="inlineStr"/>
+          <t>periodistas</t>
+        </is>
+      </c>
+      <c r="C233" s="3" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+      <c r="D233" s="4" t="inlineStr">
+        <is>
+          <t>proteccion</t>
+        </is>
+      </c>
+      <c r="E233" s="3" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
           <t>cifra oficial</t>
@@ -18378,38 +18610,38 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="H233" s="3" t="n">
-        <v>23.936</v>
+        <v>24.809</v>
       </c>
       <c r="I233" s="3" t="n">
-        <v>-106.425</v>
+        <v>-107.394</v>
       </c>
       <c r="J233" s="5" t="inlineStr">
         <is>
-          <t>San Ignacio, Sinaloa</t>
+          <t>Culiacán, Sinaloa</t>
         </is>
       </c>
       <c r="K233" s="5" t="inlineStr">
         <is>
-          <t>Sebides: padrón histórico de 3 mil 48 personas desplazadas; en San Ignacio el desplazamiento es permanente</t>
+          <t>Instituto de Protección alerta repunte de agresiones desde marzo de 2026</t>
         </is>
       </c>
       <c r="L233" s="5" t="inlineStr">
         <is>
-          <t>La titular de Sebides distinguió un padrón histórico de 3 mil 48 personas (Choix, El Fuerte, Ahome, Sinaloa, Guasave, Salvador Alvarado, Culiacán, Mazatlán, Concordia, Rosario) y un registro preventivo de familias que van y vienen; en San Ignacio las familias de comunidades serranas ya no volverán y el municipio busca terreno para vivienda. Ubicación aproximada (cabecera municipal).</t>
+          <t>133 medidas de protección activadas en 2026, 27 quejas entre enero y abril, y 12 periodistas que han salido del estado por amenazas en los últimos años. Agresiones tanto de fuerzas de seguridad como de grupos armados, incluidas mujeres periodistas en cobertura. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="M233" s="3" t="inlineStr">
         <is>
-          <t>sebides</t>
+          <t>instituto-sinaloa</t>
         </is>
       </c>
       <c r="N233" s="3" t="inlineStr">
         <is>
-          <t>https://lineadirectaportal.com/sinaloa/mas-de-3-mil-desplazados-en-sinaloa-en-san-ignacio-el-desplazamiento-es-permanente-sebides-2025-06-28__1422180</t>
+          <t>https://noticieroaltavoz.com/este-7-de-junio-dia-de-la-libertad-de-expresion-alertan-por-repunte-de-agresiones-contra-periodistas-en-sinaloa/</t>
         </is>
       </c>
       <c r="O233" s="3" t="inlineStr">
@@ -18426,7 +18658,7 @@
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t>ev-079</t>
+          <t>ev-067</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -18436,7 +18668,7 @@
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>defensor</t>
+          <t>periodista</t>
         </is>
       </c>
       <c r="D234" s="4" t="inlineStr">
@@ -18451,43 +18683,43 @@
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>asesinato de persona defensora ambiental</t>
+          <t>asesinato de periodista</t>
         </is>
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H234" s="3" t="n">
-        <v>19.684</v>
+        <v>20.533</v>
       </c>
       <c r="I234" s="3" t="n">
-        <v>-101.954</v>
+        <v>-97.459</v>
       </c>
       <c r="J234" s="5" t="inlineStr">
         <is>
-          <t>Cherán, Michoacán</t>
+          <t>Poza Rica, Veracruz</t>
         </is>
       </c>
       <c r="K234" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Francisco Macías Sánchez, integrante de la ronda comunitaria de Cherán</t>
+          <t>Asesinato de Luis Ángel López Valdez, Reportaje Policiaco Veracruzano</t>
         </is>
       </c>
       <c r="L234" s="5" t="inlineStr">
         <is>
-          <t>De 18 años, patrullaba el bosque comunal cuando un grupo del crimen organizado atacó a la ronda en las afueras del Rancho de Pino; otro comunero resultó herido. Fuente: memorial del informe CEMDA 2025. Ubicación aproximada (cabecera municipal).</t>
+          <t>Asesinado a balazos la madrugada del 11 de junio en la colonia Cazones, cerca de donde fue asesinado Carlos Castro en enero. Contaba con medidas de acompañamiento y vigilancia. Ubicación aproximada (cabecera municipal). Figura como número 177 en el registro de periodistas asesinados de ARTICLE 19.</t>
         </is>
       </c>
       <c r="M234" s="3" t="inlineStr">
         <is>
-          <t>cemda</t>
+          <t>rsf</t>
         </is>
       </c>
       <c r="N234" s="3" t="inlineStr">
         <is>
-          <t>https://cemda.org.mx/wp-content/uploads/2026/04/Informe-Defensores-2025_Web_260415_173954.pdf</t>
+          <t>https://rsf.org/es/m%C3%A9xico-el-asesinato-de-francisco-alejandro-leyva-aguilar-s%C3%A9ptimo-periodista-asesinado-en-2026</t>
         </is>
       </c>
       <c r="O234" s="3" t="inlineStr">
@@ -18504,7 +18736,7 @@
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t>ev-053</t>
+          <t>ev-068</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -18529,43 +18761,43 @@
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>asesinato de periodista</t>
+          <t>desaparición y asesinato de periodista</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="H235" s="3" t="n">
-        <v>27.493</v>
+        <v>17.643</v>
       </c>
       <c r="I235" s="3" t="n">
-        <v>-109.938</v>
+        <v>-101.552</v>
       </c>
       <c r="J235" s="5" t="inlineStr">
         <is>
-          <t>Ciudad Obregón, Sonora</t>
+          <t>Zihuatanejo de Azueta, Guerrero</t>
         </is>
       </c>
       <c r="K235" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Ángel Sevilla, Noticias 644</t>
+          <t>Alex Serna, periodista ambiental, desaparecido el 20 de junio y asesinado</t>
         </is>
       </c>
       <c r="L235" s="5" t="inlineStr">
         <is>
-          <t>Documentado por ARTICLE 19 como asesinato en posible relación con su labor periodística. Ubicación aproximada (el informe solo indica Sonora). Figura como número 173 en el registro de periodistas asesinados de ARTICLE 19.</t>
+          <t>Manuel Alejandro Moreno Serna, periodista ambiental independiente, fue reportado desaparecido el 20 de junio tras denuncias sobre tala y daños en la región del río Salitreras; un audio atribuido a él afirmaba estar secuestrado en represalia. RSF lo registra como asesinado el 3 de julio. Ubicación aproximada (cabecera municipal). Figura como número 179 (Manuel Alejandro Moreno Serna) en el registro de periodistas asesinados de ARTICLE 19.</t>
         </is>
       </c>
       <c r="M235" s="3" t="inlineStr">
         <is>
-          <t>article19</t>
+          <t>rsf</t>
         </is>
       </c>
       <c r="N235" s="3" t="inlineStr">
         <is>
-          <t>https://articulo19.org/wp-content/uploads/2026/05/Estructuras-del-Silencio-Informe-Anual-2025-A19-MXCA_compressed.pdf</t>
+          <t>https://rsf.org/es/alex-serna-especializado-en-temas-ambientales-es-el-quinto-periodista-asesinado-en-m%C3%A9xico-desde</t>
         </is>
       </c>
       <c r="O235" s="3" t="inlineStr">
@@ -18582,7 +18814,7 @@
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t>ev-054</t>
+          <t>ev-069</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -18612,38 +18844,38 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H236" s="3" t="n">
-        <v>16.863</v>
+        <v>19.284</v>
       </c>
       <c r="I236" s="3" t="n">
-        <v>-99.88200000000001</v>
+        <v>-98.43899999999999</v>
       </c>
       <c r="J236" s="5" t="inlineStr">
         <is>
-          <t>Acapulco, Guerrero</t>
+          <t>San Martín Texmelucan, Puebla</t>
         </is>
       </c>
       <c r="K236" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Ronald Paz Pedro, NotiExpress Pedro</t>
+          <t>Asesinato de Josué Martínez Contreras, director de Noticias San Martín Texmelucan</t>
         </is>
       </c>
       <c r="L236" s="5" t="inlineStr">
         <is>
-          <t>Segundo periodista asesinado en Acapulco en 2025, según ARTICLE 19 y RSF. Ubicación aproximada (cabecera municipal). Figura como número 174 en el registro de periodistas asesinados de ARTICLE 19.</t>
+          <t>Asesinado a tiros el 16 de julio. Una ex autoridad local señalada por amenazas previas fue detenida dos días después por otro delito. ARTICLE 19 documentó 39 agresiones en Puebla en 2025, la segunda cifra del país. Ubicación aproximada (cabecera municipal). Figura como número 180 en el registro de periodistas asesinados de ARTICLE 19.</t>
         </is>
       </c>
       <c r="M236" s="3" t="inlineStr">
         <is>
-          <t>article19</t>
+          <t>rsf</t>
         </is>
       </c>
       <c r="N236" s="3" t="inlineStr">
         <is>
-          <t>https://articulo19.org/wp-content/uploads/2026/05/Estructuras-del-Silencio-Informe-Anual-2025-A19-MXCA_compressed.pdf</t>
+          <t>https://rsf.org/es/m%C3%A9xico-sexto-periodista-asesinado-en-2026-el-gobierno-debe-actuar-con-urgencia-frente-la-violencia</t>
         </is>
       </c>
       <c r="O236" s="3" t="inlineStr">
@@ -18660,7 +18892,7 @@
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t>ev-080</t>
+          <t>ev-070</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -18670,12 +18902,12 @@
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>defensor</t>
+          <t>periodista</t>
         </is>
       </c>
       <c r="D237" s="4" t="inlineStr">
         <is>
-          <t>asesinato</t>
+          <t>ataque_medio</t>
         </is>
       </c>
       <c r="E237" s="3" t="inlineStr">
@@ -18685,48 +18917,48 @@
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
-          <t>asesinato de persona defensora ambiental</t>
+          <t>ataque a medio</t>
         </is>
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H237" s="3" t="n">
-        <v>17.546</v>
+        <v>24.809</v>
       </c>
       <c r="I237" s="3" t="n">
-        <v>-98.577</v>
+        <v>-107.394</v>
       </c>
       <c r="J237" s="5" t="inlineStr">
         <is>
-          <t>Tlapa de Comonfort, Guerrero</t>
+          <t>Culiacán, Sinaloa</t>
         </is>
       </c>
       <c r="K237" s="5" t="inlineStr">
         <is>
-          <t>Asesinato de Sergio Hugo Ureiro Castañeda, defensor de la Plazuela de los Cántaros</t>
+          <t>Ataque armado contra domicilio vinculado al director de Grupo Adiscusión</t>
         </is>
       </c>
       <c r="L237" s="5" t="inlineStr">
         <is>
-          <t>Líder del movimiento que recuperó la plaza pública y área verde de Tlapa; un mes antes su casa fue incendiada. Asesinado en una gasolinera del centro. Fuente: memorial del informe CEMDA 2025. Ubicación aproximada (cabecera municipal).</t>
+          <t>El Instituto de Protección condenó el ataque y pidió investigar la posible relación con la actividad periodística de la víctima. Ubicación aproximada (cabecera municipal).</t>
         </is>
       </c>
       <c r="M237" s="3" t="inlineStr">
         <is>
-          <t>cemda</t>
+          <t>noroeste</t>
         </is>
       </c>
       <c r="N237" s="3" t="inlineStr">
         <is>
-          <t>https://cemda.org.mx/wp-content/uploads/2026/04/Informe-Defensores-2025_Web_260415_173954.pdf</t>
+          <t>https://www.noroeste.com.mx/culiacan/instituto-de-proteccion-a-periodistas-condena-ataque-contra-domicilio-vinculado-a-director-de-adiscusion-HP24187055</t>
         </is>
       </c>
       <c r="O237" s="3" t="inlineStr">
         <is>
-          <t>organización</t>
+          <t>prensa</t>
         </is>
       </c>
       <c r="P237" s="3" t="inlineStr">
@@ -18738,56 +18970,68 @@
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t>ev-023</t>
+          <t>ev-071</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento</t>
-        </is>
-      </c>
-      <c r="C238" s="3" t="inlineStr"/>
-      <c r="D238" s="4" t="inlineStr"/>
-      <c r="E238" s="3" t="inlineStr"/>
+          <t>periodistas</t>
+        </is>
+      </c>
+      <c r="C238" s="3" t="inlineStr">
+        <is>
+          <t>periodista</t>
+        </is>
+      </c>
+      <c r="D238" s="4" t="inlineStr">
+        <is>
+          <t>asesinato</t>
+        </is>
+      </c>
+      <c r="E238" s="3" t="inlineStr">
+        <is>
+          <t>masculino</t>
+        </is>
+      </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento masivo</t>
+          <t>asesinato de periodista</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="H238" s="3" t="n">
-        <v>25.363</v>
+        <v>17.146</v>
       </c>
       <c r="I238" s="3" t="n">
-        <v>-107.551</v>
+        <v>-96.752</v>
       </c>
       <c r="J238" s="5" t="inlineStr">
         <is>
-          <t>San Miguel, sierra de Badiraguato, Sinaloa</t>
+          <t>San Pablo Etla, Oaxaca</t>
         </is>
       </c>
       <c r="K238" s="5" t="inlineStr">
         <is>
-          <t>54 familias de San Miguel se desplazan a Hidalgo del Parral, Chihuahua</t>
+          <t>Asesinato de Francisco Alejandro Leyva Aguilar, periodista y articulista</t>
         </is>
       </c>
       <c r="L238" s="5" t="inlineStr">
         <is>
-          <t>Según el informe de la Misión Civil de Observación en Chihuahua, 54 familias de la comunidad de San Miguel, a cinco horas de Badiraguato y dos de Atascaderos, salieron en septiembre de 2025 hacia Chihuahua y residen en Parral. Ubicación aproximada (cabecera de Badiraguato).</t>
+          <t>Asesinado a tiros el 22 de julio; un año antes había denunciado oficialmente amenazas de muerte. Séptimo periodista asesinado en 2026 según RSF, sexto según CPJ. Ubicación aproximada (cabecera municipal). Figura como número 181 en el registro de periodistas asesinados de ARTICLE 19.</t>
         </is>
       </c>
       <c r="M238" s="3" t="inlineStr">
         <is>
-          <t>mco-chihuahua</t>
+          <t>rsf</t>
         </is>
       </c>
       <c r="N238" s="3" t="inlineStr">
         <is>
-          <t>https://www.eldiariodechihuahua.mx/estado/2026/sep/24/llegan-desplazados-de-durango-y-sinaloa-840648.html</t>
+          <t>https://rsf.org/es/m%C3%A9xico-el-asesinato-de-francisco-alejandro-leyva-aguilar-s%C3%A9ptimo-periodista-asesinado-en-2026</t>
         </is>
       </c>
       <c r="O238" s="3" t="inlineStr">
@@ -18804,61 +19048,73 @@
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t>ev-024</t>
+          <t>ev-072</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento</t>
-        </is>
-      </c>
-      <c r="C239" s="3" t="inlineStr"/>
-      <c r="D239" s="4" t="inlineStr"/>
-      <c r="E239" s="3" t="inlineStr"/>
+          <t>periodistas</t>
+        </is>
+      </c>
+      <c r="C239" s="3" t="inlineStr">
+        <is>
+          <t>ambos</t>
+        </is>
+      </c>
+      <c r="D239" s="4" t="inlineStr">
+        <is>
+          <t>informe</t>
+        </is>
+      </c>
+      <c r="E239" s="3" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
-          <t>desplazamiento masivo</t>
+          <t>informe</t>
         </is>
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H239" s="3" t="n">
-        <v>25</v>
+        <v>19.432</v>
       </c>
       <c r="I239" s="3" t="n">
-        <v>-107.38</v>
+        <v>-99.133</v>
       </c>
       <c r="J239" s="5" t="inlineStr">
         <is>
-          <t>Tepuche, Culiacán, Sinaloa</t>
+          <t>Ciudad de México</t>
         </is>
       </c>
       <c r="K239" s="5" t="inlineStr">
         <is>
-          <t>328 familias salen de la zona serrana de Tepuche; Tachinolpa, Guayabito y Ayuné quedan sin población</t>
+          <t>Espacio OSC: el Mecanismo rechazó 70 por ciento de las solicitudes de protección entre 2024 y junio de 2026</t>
         </is>
       </c>
       <c r="L239" s="5" t="inlineStr">
         <is>
-          <t>La violencia en la sierra al norte de Culiacán desplazó a 328 familias; cinco escuelas de Culiacán, Mocorito y Navolato pasaron a clases a distancia. Sebides reportó que el padrón estatal llegaba a mil 61 familias y que Ayuné podría repoblarse si se restablecen agua y caminos. Ubicación aproximada (sindicatura de Tepuche).</t>
+          <t>De 409 solicitudes recibidas, 289 fueron rechazadas; las organizaciones señalan que algunas personas han perdido la vida con medidas o esperando incorporación. Al 31 de mayo de 2026 el Mecanismo protegía a 2 mil 20 personas (690 periodistas y mil 330 defensoras). Cifra nacional ubicada en la capital.</t>
         </is>
       </c>
       <c r="M239" s="3" t="inlineStr">
         <is>
-          <t>sillarota</t>
+          <t>espacio-osc</t>
         </is>
       </c>
       <c r="N239" s="3" t="inlineStr">
         <is>
-          <t>https://lasillarota.com/estados/2025/9/17/violencia-en-sinaloa-obliga-desplazamientos-clases-en-linea-467963.html</t>
+          <t>https://www.proceso.com.mx/nacional/2026/9/4/osc-urge-al-gobierno-federal-a-fortalecer-mecanismo-de-proteccion-para-defensores-y-periodistas-379345.html</t>
         </is>
       </c>
       <c r="O239" s="3" t="inlineStr">
         <is>
-          <t>prensa</t>
+          <t>organización</t>
         </is>
       </c>
       <c r="P239" s="3" t="inlineStr">
@@ -18868,2818 +19124,706 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="3" t="inlineStr">
-        <is>
-          <t>ev-055</t>
-        </is>
-      </c>
-      <c r="B240" s="3" t="inlineStr">
-        <is>
-          <t>periodistas</t>
-        </is>
-      </c>
-      <c r="C240" s="3" t="inlineStr">
-        <is>
-          <t>periodista</t>
-        </is>
-      </c>
-      <c r="D240" s="4" t="inlineStr">
-        <is>
-          <t>asesinato</t>
-        </is>
-      </c>
-      <c r="E240" s="3" t="inlineStr">
-        <is>
-          <t>masculino</t>
-        </is>
-      </c>
-      <c r="F240" s="3" t="inlineStr">
-        <is>
-          <t>asesinato de periodista</t>
-        </is>
-      </c>
-      <c r="G240" s="3" t="inlineStr">
-        <is>
-          <t>2025-10-25</t>
-        </is>
-      </c>
-      <c r="H240" s="3" t="n">
-        <v>24.027</v>
-      </c>
-      <c r="I240" s="3" t="n">
-        <v>-104.653</v>
-      </c>
-      <c r="J240" s="5" t="inlineStr">
-        <is>
-          <t>Durango, Durango</t>
-        </is>
-      </c>
-      <c r="K240" s="5" t="inlineStr">
-        <is>
-          <t>Asesinato de Miguel Ángel Beltrán Martínez, periodista independiente</t>
-        </is>
-      </c>
-      <c r="L240" s="5" t="inlineStr">
-        <is>
-          <t>Documentado por ARTICLE 19 como asesinato en posible relación con su labor periodística. Ubicación aproximada (el informe solo indica Durango). Figura como número 175 en el registro de periodistas asesinados de ARTICLE 19.</t>
-        </is>
-      </c>
-      <c r="M240" s="3" t="inlineStr">
-        <is>
-          <t>article19</t>
-        </is>
-      </c>
-      <c r="N240" s="3" t="inlineStr">
-        <is>
-          <t>https://articulo19.org/wp-content/uploads/2026/05/Estructuras-del-Silencio-Informe-Anual-2025-A19-MXCA_compressed.pdf</t>
-        </is>
-      </c>
-      <c r="O240" s="3" t="inlineStr">
-        <is>
-          <t>organización</t>
-        </is>
-      </c>
-      <c r="P240" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="A240" s="6" t="n"/>
+      <c r="B240" s="6" t="n"/>
+      <c r="C240" s="6" t="n"/>
+      <c r="D240" s="7" t="n"/>
+      <c r="E240" s="6" t="n"/>
+      <c r="F240" s="6" t="n"/>
+      <c r="G240" s="6" t="n"/>
+      <c r="H240" s="6" t="n"/>
+      <c r="I240" s="6" t="n"/>
+      <c r="J240" s="6" t="n"/>
+      <c r="K240" s="6" t="n"/>
+      <c r="L240" s="6" t="n"/>
+      <c r="M240" s="6" t="n"/>
+      <c r="N240" s="6" t="n"/>
+      <c r="O240" s="6" t="n"/>
+      <c r="P240" s="6" t="n"/>
     </row>
     <row r="241">
-      <c r="A241" s="3" t="inlineStr">
-        <is>
-          <t>ev-081</t>
-        </is>
-      </c>
-      <c r="B241" s="3" t="inlineStr">
-        <is>
-          <t>periodistas</t>
-        </is>
-      </c>
-      <c r="C241" s="3" t="inlineStr">
-        <is>
-          <t>defensor</t>
-        </is>
-      </c>
-      <c r="D241" s="4" t="inlineStr">
-        <is>
-          <t>asesinato</t>
-        </is>
-      </c>
-      <c r="E241" s="3" t="inlineStr">
-        <is>
-          <t>masculino</t>
-        </is>
-      </c>
-      <c r="F241" s="3" t="inlineStr">
-        <is>
-          <t>asesinato de persona defensora ambiental</t>
-        </is>
-      </c>
-      <c r="G241" s="3" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="H241" s="3" t="n">
-        <v>19.237</v>
-      </c>
-      <c r="I241" s="3" t="n">
-        <v>-104.567</v>
-      </c>
-      <c r="J241" s="5" t="inlineStr">
-        <is>
-          <t>Cihuatlán, Jalisco</t>
-        </is>
-      </c>
-      <c r="K241" s="5" t="inlineStr">
-        <is>
-          <t>Asesinato de Cándido Esaú Román Pérez, abogado y representante ejidal</t>
-        </is>
-      </c>
-      <c r="L241" s="5" t="inlineStr">
-        <is>
-          <t>Defendía al ejido General Emiliano Zapata frente al despojo de tierras en Melaque, con amparo obtenido; asesinado afuera de su casa. La fiscalía reconoce su activismo como línea principal. Fuente: memorial del informe CEMDA 2025. Ubicación aproximada (cabecera municipal).</t>
-        </is>
-      </c>
-      <c r="M241" s="3" t="inlineStr">
-        <is>
-          <t>cemda</t>
-        </is>
-      </c>
-      <c r="N241" s="3" t="inlineStr">
-        <is>
-          <t>https://cemda.org.mx/wp-content/uploads/2026/04/Informe-Defensores-2025_Web_260415_173954.pdf</t>
-        </is>
-      </c>
-      <c r="O241" s="3" t="inlineStr">
-        <is>
-          <t>organización</t>
-        </is>
-      </c>
-      <c r="P241" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="A241" s="6" t="n"/>
+      <c r="B241" s="6" t="n"/>
+      <c r="C241" s="6" t="n"/>
+      <c r="D241" s="7" t="n"/>
+      <c r="E241" s="6" t="n"/>
+      <c r="F241" s="6" t="n"/>
+      <c r="G241" s="6" t="n"/>
+      <c r="H241" s="6" t="n"/>
+      <c r="I241" s="6" t="n"/>
+      <c r="J241" s="6" t="n"/>
+      <c r="K241" s="6" t="n"/>
+      <c r="L241" s="6" t="n"/>
+      <c r="M241" s="6" t="n"/>
+      <c r="N241" s="6" t="n"/>
+      <c r="O241" s="6" t="n"/>
+      <c r="P241" s="6" t="n"/>
     </row>
     <row r="242">
-      <c r="A242" s="3" t="inlineStr">
-        <is>
-          <t>ev-082</t>
-        </is>
-      </c>
-      <c r="B242" s="3" t="inlineStr">
-        <is>
-          <t>periodistas</t>
-        </is>
-      </c>
-      <c r="C242" s="3" t="inlineStr">
-        <is>
-          <t>defensor</t>
-        </is>
-      </c>
-      <c r="D242" s="4" t="inlineStr">
-        <is>
-          <t>asesinato</t>
-        </is>
-      </c>
-      <c r="E242" s="3" t="inlineStr">
-        <is>
-          <t>masculino</t>
-        </is>
-      </c>
-      <c r="F242" s="3" t="inlineStr">
-        <is>
-          <t>asesinato de persona defensora ambiental</t>
-        </is>
-      </c>
-      <c r="G242" s="3" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="H242" s="3" t="n">
-        <v>22.345</v>
-      </c>
-      <c r="I242" s="3" t="n">
-        <v>-103.605</v>
-      </c>
-      <c r="J242" s="5" t="inlineStr">
-        <is>
-          <t>Azqueltán, Villa Guerrero, Jalisco</t>
-        </is>
-      </c>
-      <c r="K242" s="5" t="inlineStr">
-        <is>
-          <t>Asesinato de Marcos Aguilar Rojas, representante agrario de Azqueltán</t>
-        </is>
-      </c>
-      <c r="L242" s="5" t="inlineStr">
-        <is>
-          <t>Comunidad tepehuana-wixárika en juicio agrario por 45 mil hectáreas; atacado con su hermano al retirar ganado invasor en el predio comunal El Caracol. Los agresores están identificados y sin proceso. Fuente: memorial del informe CEMDA 2025. Ubicación aproximada (cabecera municipal).</t>
-        </is>
-      </c>
-      <c r="M242" s="3" t="inlineStr">
-        <is>
-          <t>cemda</t>
-        </is>
-      </c>
-      <c r="N242" s="3" t="inlineStr">
-        <is>
-          <t>https://cemda.org.mx/wp-content/uploads/2026/04/Informe-Defensores-2025_Web_260415_173954.pdf</t>
-        </is>
-      </c>
-      <c r="O242" s="3" t="inlineStr">
-        <is>
-          <t>organización</t>
-        </is>
-      </c>
-      <c r="P242" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="A242" s="6" t="n"/>
+      <c r="B242" s="6" t="n"/>
+      <c r="C242" s="6" t="n"/>
+      <c r="D242" s="7" t="n"/>
+      <c r="E242" s="6" t="n"/>
+      <c r="F242" s="6" t="n"/>
+      <c r="G242" s="6" t="n"/>
+      <c r="H242" s="6" t="n"/>
+      <c r="I242" s="6" t="n"/>
+      <c r="J242" s="6" t="n"/>
+      <c r="K242" s="6" t="n"/>
+      <c r="L242" s="6" t="n"/>
+      <c r="M242" s="6" t="n"/>
+      <c r="N242" s="6" t="n"/>
+      <c r="O242" s="6" t="n"/>
+      <c r="P242" s="6" t="n"/>
     </row>
     <row r="243">
-      <c r="A243" s="3" t="inlineStr">
-        <is>
-          <t>ev-025</t>
-        </is>
-      </c>
-      <c r="B243" s="3" t="inlineStr">
-        <is>
-          <t>desplazamiento</t>
-        </is>
-      </c>
-      <c r="C243" s="3" t="inlineStr"/>
-      <c r="D243" s="4" t="inlineStr"/>
-      <c r="E243" s="3" t="inlineStr"/>
-      <c r="F243" s="3" t="inlineStr">
-        <is>
-          <t>desplazamiento masivo</t>
-        </is>
-      </c>
-      <c r="G243" s="3" t="inlineStr">
-        <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="H243" s="3" t="n">
-        <v>22.837</v>
-      </c>
-      <c r="I243" s="3" t="n">
-        <v>-105.776</v>
-      </c>
-      <c r="J243" s="5" t="inlineStr">
-        <is>
-          <t>El Tecomatillo, Escuinapa, Sinaloa</t>
-        </is>
-      </c>
-      <c r="K243" s="5" t="inlineStr">
-        <is>
-          <t>Comunidad tepehuana de El Tecomatillo desplazada por enfrentamientos</t>
-        </is>
-      </c>
-      <c r="L243" s="5" t="inlineStr">
-        <is>
-          <t>Familias tepehuanas que habían llegado a Escuinapa huyendo de la violencia en Durango fueron desplazadas de nuevo desde diciembre de 2025, cuando los enfrentamientos destruyeron viviendas junto al arroyo Buñigas; no figuran en el padrón estatal. Fecha aproximada. Ubicación aproximada (cabecera de Escuinapa).</t>
-        </is>
-      </c>
-      <c r="M243" s="3" t="inlineStr">
-        <is>
-          <t>noroeste</t>
-        </is>
-      </c>
-      <c r="N243" s="3" t="inlineStr">
-        <is>
-          <t>https://www.noroeste.com.mx/mazatlan/dejaron-durango-huyendo-de-la-violencia-y-llegaron-a-escuinapa-donde-tambien-han-tenido-que-escapar-GB23220512</t>
-        </is>
-      </c>
-      <c r="O243" s="3" t="inlineStr">
-        <is>
-          <t>prensa</t>
-        </is>
-      </c>
-      <c r="P243" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="A243" s="6" t="n"/>
+      <c r="B243" s="6" t="n"/>
+      <c r="C243" s="6" t="n"/>
+      <c r="D243" s="7" t="n"/>
+      <c r="E243" s="6" t="n"/>
+      <c r="F243" s="6" t="n"/>
+      <c r="G243" s="6" t="n"/>
+      <c r="H243" s="6" t="n"/>
+      <c r="I243" s="6" t="n"/>
+      <c r="J243" s="6" t="n"/>
+      <c r="K243" s="6" t="n"/>
+      <c r="L243" s="6" t="n"/>
+      <c r="M243" s="6" t="n"/>
+      <c r="N243" s="6" t="n"/>
+      <c r="O243" s="6" t="n"/>
+      <c r="P243" s="6" t="n"/>
     </row>
     <row r="244">
-      <c r="A244" s="3" t="inlineStr">
-        <is>
-          <t>ev-056</t>
-        </is>
-      </c>
-      <c r="B244" s="3" t="inlineStr">
-        <is>
-          <t>periodistas</t>
-        </is>
-      </c>
-      <c r="C244" s="3" t="inlineStr">
-        <is>
-          <t>periodista</t>
-        </is>
-      </c>
-      <c r="D244" s="4" t="inlineStr">
-        <is>
-          <t>acoso_judicial</t>
-        </is>
-      </c>
-      <c r="E244" s="3" t="inlineStr">
-        <is>
-          <t>masculino</t>
-        </is>
-      </c>
-      <c r="F244" s="3" t="inlineStr">
-        <is>
-          <t>acoso judicial</t>
-        </is>
-      </c>
-      <c r="G244" s="3" t="inlineStr">
-        <is>
-          <t>2025-12-24</t>
-        </is>
-      </c>
-      <c r="H244" s="3" t="n">
-        <v>19.043</v>
-      </c>
-      <c r="I244" s="3" t="n">
-        <v>-98.19799999999999</v>
-      </c>
-      <c r="J244" s="5" t="inlineStr">
-        <is>
-          <t>Puebla, Puebla</t>
-        </is>
-      </c>
-      <c r="K244" s="5" t="inlineStr">
-        <is>
-          <t>Vinculación a proceso del director del portal e-consulta por su labor periodística</t>
-        </is>
-      </c>
-      <c r="L244" s="5" t="inlineStr">
-        <is>
-          <t>ARTICLE 19 señaló el caso como precedente grave de uso del derecho penal para intimidar. En 2025 documentó 69 periodistas y medios víctimas de acoso judicial en 21 entidades. Ubicación aproximada (cabecera municipal).</t>
-        </is>
-      </c>
-      <c r="M244" s="3" t="inlineStr">
-        <is>
-          <t>article19</t>
-        </is>
-      </c>
-      <c r="N244" s="3" t="inlineStr">
-        <is>
-          <t>https://articulo19.org/wp-content/uploads/2026/05/Estructuras-del-Silencio-Informe-Anual-2025-A19-MXCA_compressed.pdf</t>
-        </is>
-      </c>
-      <c r="O244" s="3" t="inlineStr">
-        <is>
-          <t>organización</t>
-        </is>
-      </c>
-      <c r="P244" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="A244" s="6" t="n"/>
+      <c r="B244" s="6" t="n"/>
+      <c r="C244" s="6" t="n"/>
+      <c r="D244" s="7" t="n"/>
+      <c r="E244" s="6" t="n"/>
+      <c r="F244" s="6" t="n"/>
+      <c r="G244" s="6" t="n"/>
+      <c r="H244" s="6" t="n"/>
+      <c r="I244" s="6" t="n"/>
+      <c r="J244" s="6" t="n"/>
+      <c r="K244" s="6" t="n"/>
+      <c r="L244" s="6" t="n"/>
+      <c r="M244" s="6" t="n"/>
+      <c r="N244" s="6" t="n"/>
+      <c r="O244" s="6" t="n"/>
+      <c r="P244" s="6" t="n"/>
     </row>
     <row r="245">
-      <c r="A245" s="3" t="inlineStr">
-        <is>
-          <t>ev-057</t>
-        </is>
-      </c>
-      <c r="B245" s="3" t="inlineStr">
-        <is>
-          <t>periodistas</t>
-        </is>
-      </c>
-      <c r="C245" s="3" t="inlineStr">
-        <is>
-          <t>periodista</t>
-        </is>
-      </c>
-      <c r="D245" s="4" t="inlineStr">
-        <is>
-          <t>acoso_judicial</t>
-        </is>
-      </c>
-      <c r="E245" s="3" t="inlineStr">
-        <is>
-          <t>no determinado</t>
-        </is>
-      </c>
-      <c r="F245" s="3" t="inlineStr">
-        <is>
-          <t>acoso judicial</t>
-        </is>
-      </c>
-      <c r="G245" s="3" t="inlineStr">
-        <is>
-          <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="H245" s="3" t="n">
-        <v>18.134</v>
-      </c>
-      <c r="I245" s="3" t="n">
-        <v>-94.422</v>
-      </c>
-      <c r="J245" s="5" t="inlineStr">
-        <is>
-          <t>Coatzacoalcos, Veracruz</t>
-        </is>
-      </c>
-      <c r="K245" s="5" t="inlineStr">
-        <is>
-          <t>Fiscalía de Veracruz imputa a periodista por terrorismo por hechos ligados a su labor</t>
-        </is>
-      </c>
-      <c r="L245" s="5" t="inlineStr">
-        <is>
-          <t>La imputación fue desestimada, pero se mantenían vigentes otras dos. ARTICLE 19 la calificó como uno de los episodios más alarmantes del año. Ubicación aproximada (cabecera municipal).</t>
-        </is>
-      </c>
-      <c r="M245" s="3" t="inlineStr">
-        <is>
-          <t>article19</t>
-        </is>
-      </c>
-      <c r="N245" s="3" t="inlineStr">
-        <is>
-          <t>https://articulo19.org/wp-content/uploads/2026/05/Estructuras-del-Silencio-Informe-Anual-2025-A19-MXCA_compressed.pdf</t>
-        </is>
-      </c>
-      <c r="O245" s="3" t="inlineStr">
-        <is>
-          <t>organización</t>
-        </is>
-      </c>
-      <c r="P245" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="A245" s="6" t="n"/>
+      <c r="B245" s="6" t="n"/>
+      <c r="C245" s="6" t="n"/>
+      <c r="D245" s="7" t="n"/>
+      <c r="E245" s="6" t="n"/>
+      <c r="F245" s="6" t="n"/>
+      <c r="G245" s="6" t="n"/>
+      <c r="H245" s="6" t="n"/>
+      <c r="I245" s="6" t="n"/>
+      <c r="J245" s="6" t="n"/>
+      <c r="K245" s="6" t="n"/>
+      <c r="L245" s="6" t="n"/>
+      <c r="M245" s="6" t="n"/>
+      <c r="N245" s="6" t="n"/>
+      <c r="O245" s="6" t="n"/>
+      <c r="P245" s="6" t="n"/>
     </row>
     <row r="246">
-      <c r="A246" s="3" t="inlineStr">
-        <is>
-          <t>ev-058</t>
-        </is>
-      </c>
-      <c r="B246" s="3" t="inlineStr">
-        <is>
-          <t>periodistas</t>
-        </is>
-      </c>
-      <c r="C246" s="3" t="inlineStr">
-        <is>
-          <t>periodista</t>
-        </is>
-      </c>
-      <c r="D246" s="4" t="inlineStr">
-        <is>
-          <t>asesinato</t>
-        </is>
-      </c>
-      <c r="E246" s="3" t="inlineStr">
-        <is>
-          <t>masculino</t>
-        </is>
-      </c>
-      <c r="F246" s="3" t="inlineStr">
-        <is>
-          <t>asesinato de periodista</t>
-        </is>
-      </c>
-      <c r="G246" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="H246" s="3" t="n">
-        <v>20.533</v>
-      </c>
-      <c r="I246" s="3" t="n">
-        <v>-97.459</v>
-      </c>
-      <c r="J246" s="5" t="inlineStr">
-        <is>
-          <t>Poza Rica, Veracruz</t>
-        </is>
-      </c>
-      <c r="K246" s="5" t="inlineStr">
-        <is>
-          <t>Asesinato de Carlos Castro en Poza Rica</t>
-        </is>
-      </c>
-      <c r="L246" s="5" t="inlineStr">
-        <is>
-          <t>Asesinado el 8 de enero dentro de un restaurante de la avenida 20 de Noviembre, primer periodista asesinado en 2026 según el recuento de N+ y CPJ. Ubicación aproximada (cabecera municipal). Figura como número 176 (Carlos Leonardo Ramírez Castro) en el registro de periodistas asesinados de ARTICLE 19.</t>
-        </is>
-      </c>
-      <c r="M246" s="3" t="inlineStr">
-        <is>
-          <t>nmas</t>
-        </is>
-      </c>
-      <c r="N246" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nmas.com.mx/seguridad/asesinatos/cuantos-y-quienes-son-los-periodistas-asesinados-en-mexico-este-2026/</t>
-        </is>
-      </c>
-      <c r="O246" s="3" t="inlineStr">
-        <is>
-          <t>prensa</t>
-        </is>
-      </c>
-      <c r="P246" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="A246" s="6" t="n"/>
+      <c r="B246" s="6" t="n"/>
+      <c r="C246" s="6" t="n"/>
+      <c r="D246" s="7" t="n"/>
+      <c r="E246" s="6" t="n"/>
+      <c r="F246" s="6" t="n"/>
+      <c r="G246" s="6" t="n"/>
+      <c r="H246" s="6" t="n"/>
+      <c r="I246" s="6" t="n"/>
+      <c r="J246" s="6" t="n"/>
+      <c r="K246" s="6" t="n"/>
+      <c r="L246" s="6" t="n"/>
+      <c r="M246" s="6" t="n"/>
+      <c r="N246" s="6" t="n"/>
+      <c r="O246" s="6" t="n"/>
+      <c r="P246" s="6" t="n"/>
     </row>
     <row r="247">
-      <c r="A247" s="3" t="inlineStr">
-        <is>
-          <t>ev-026</t>
-        </is>
-      </c>
-      <c r="B247" s="3" t="inlineStr">
-        <is>
-          <t>desplazamiento</t>
-        </is>
-      </c>
-      <c r="C247" s="3" t="inlineStr"/>
-      <c r="D247" s="4" t="inlineStr"/>
-      <c r="E247" s="3" t="inlineStr"/>
-      <c r="F247" s="3" t="inlineStr">
-        <is>
-          <t>desplazamiento masivo</t>
-        </is>
-      </c>
-      <c r="G247" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="H247" s="3" t="n">
-        <v>24.765</v>
-      </c>
-      <c r="I247" s="3" t="n">
-        <v>-107.702</v>
-      </c>
-      <c r="J247" s="5" t="inlineStr">
-        <is>
-          <t>Las Puentes, Navolato, Sinaloa</t>
-        </is>
-      </c>
-      <c r="K247" s="5" t="inlineStr">
-        <is>
-          <t>Familias de Las Puentes se dispersan hacia Culiacán, Villa Juárez y El Diez</t>
-        </is>
-      </c>
-      <c r="L247" s="5" t="inlineStr">
-        <is>
-          <t>Sebides informó que en enero recorrió Las Puentes, donde algunas personas permanecieron y otras se trasladaron a Culiacán, Villa Juárez y El Diez; la dependencia seguía localizando a las familias. Ubicación aproximada (cabecera de Navolato).</t>
-        </is>
-      </c>
-      <c r="M247" s="3" t="inlineStr">
-        <is>
-          <t>sebides</t>
-        </is>
-      </c>
-      <c r="N247" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aztecasinaloa.com/noticias/en-sinaloa-familias-se-desplazan-por-violencia-cuales-son-los-municipios-afectados/</t>
-        </is>
-      </c>
-      <c r="O247" s="3" t="inlineStr">
-        <is>
-          <t>oficial</t>
-        </is>
-      </c>
-      <c r="P247" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="A247" s="6" t="n"/>
+      <c r="B247" s="6" t="n"/>
+      <c r="C247" s="6" t="n"/>
+      <c r="D247" s="7" t="n"/>
+      <c r="E247" s="6" t="n"/>
+      <c r="F247" s="6" t="n"/>
+      <c r="G247" s="6" t="n"/>
+      <c r="H247" s="6" t="n"/>
+      <c r="I247" s="6" t="n"/>
+      <c r="J247" s="6" t="n"/>
+      <c r="K247" s="6" t="n"/>
+      <c r="L247" s="6" t="n"/>
+      <c r="M247" s="6" t="n"/>
+      <c r="N247" s="6" t="n"/>
+      <c r="O247" s="6" t="n"/>
+      <c r="P247" s="6" t="n"/>
     </row>
     <row r="248">
-      <c r="A248" s="3" t="inlineStr">
-        <is>
-          <t>ev-059</t>
-        </is>
-      </c>
-      <c r="B248" s="3" t="inlineStr">
-        <is>
-          <t>periodistas</t>
-        </is>
-      </c>
-      <c r="C248" s="3" t="inlineStr">
-        <is>
-          <t>periodista</t>
-        </is>
-      </c>
-      <c r="D248" s="4" t="inlineStr">
-        <is>
-          <t>agresion</t>
-        </is>
-      </c>
-      <c r="E248" s="3" t="inlineStr">
-        <is>
-          <t>masculino</t>
-        </is>
-      </c>
-      <c r="F248" s="3" t="inlineStr">
-        <is>
-          <t>agresión por autoridad</t>
-        </is>
-      </c>
-      <c r="G248" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-19</t>
-        </is>
-      </c>
-      <c r="H248" s="3" t="n">
-        <v>24.809</v>
-      </c>
-      <c r="I248" s="3" t="n">
-        <v>-107.394</v>
-      </c>
-      <c r="J248" s="5" t="inlineStr">
-        <is>
-          <t>Culiacán, Sinaloa</t>
-        </is>
-      </c>
-      <c r="K248" s="5" t="inlineStr">
-        <is>
-          <t>Policía estatal apunta su arma contra reportero de la fuente de seguridad</t>
-        </is>
-      </c>
-      <c r="L248" s="5" t="inlineStr">
-        <is>
-          <t>Tras un enfrentamiento entre fuerzas de seguridad y un grupo armado, agentes de la Policía Estatal Preventiva agredieron a un reportero; el hecho quedó en video. El Instituto de Protección documentó 235 agresiones al gremio entre 2022 y 2025. Ubicación aproximada (cabecera municipal).</t>
-        </is>
-      </c>
-      <c r="M248" s="3" t="inlineStr">
-        <is>
-          <t>proceso</t>
-        </is>
-      </c>
-      <c r="N248" s="3" t="inlineStr">
-        <is>
-          <t>https://www.proceso.com.mx/nacional/estados/2026/1/19/policia-estatal-de-sinaloa-apunta-su-arma-hacia-reportero-en-culiacan-video-366842.html</t>
-        </is>
-      </c>
-      <c r="O248" s="3" t="inlineStr">
-        <is>
-          <t>prensa</t>
-        </is>
-      </c>
-      <c r="P248" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="A248" s="6" t="n"/>
+      <c r="B248" s="6" t="n"/>
+      <c r="C248" s="6" t="n"/>
+      <c r="D248" s="7" t="n"/>
+      <c r="E248" s="6" t="n"/>
+      <c r="F248" s="6" t="n"/>
+      <c r="G248" s="6" t="n"/>
+      <c r="H248" s="6" t="n"/>
+      <c r="I248" s="6" t="n"/>
+      <c r="J248" s="6" t="n"/>
+      <c r="K248" s="6" t="n"/>
+      <c r="L248" s="6" t="n"/>
+      <c r="M248" s="6" t="n"/>
+      <c r="N248" s="6" t="n"/>
+      <c r="O248" s="6" t="n"/>
+      <c r="P248" s="6" t="n"/>
     </row>
     <row r="249">
-      <c r="A249" s="3" t="inlineStr">
-        <is>
-          <t>ev-027</t>
-        </is>
-      </c>
-      <c r="B249" s="3" t="inlineStr">
-        <is>
-          <t>desplazamiento</t>
-        </is>
-      </c>
-      <c r="C249" s="3" t="inlineStr"/>
-      <c r="D249" s="4" t="inlineStr"/>
-      <c r="E249" s="3" t="inlineStr"/>
-      <c r="F249" s="3" t="inlineStr">
-        <is>
-          <t>desplazamiento masivo</t>
-        </is>
-      </c>
-      <c r="G249" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
-        </is>
-      </c>
-      <c r="H249" s="3" t="n">
-        <v>26.095</v>
-      </c>
-      <c r="I249" s="3" t="n">
-        <v>-106.965</v>
-      </c>
-      <c r="J249" s="5" t="inlineStr">
-        <is>
-          <t>Atascaderos, Guadalupe y Calvo, Chihuahua</t>
-        </is>
-      </c>
-      <c r="K249" s="5" t="inlineStr">
-        <is>
-          <t>Unas 600 personas desplazadas del seccional Atascaderos por enfrentamientos entre facciones</t>
-        </is>
-      </c>
-      <c r="L249" s="5" t="inlineStr">
-        <is>
-          <t>Entre el 18 y el 27 de febrero cientos de personas, en su mayoría indígenas, fueron atendidas en albergues de Chihuahua capital y Parral; otras llegaron a Cuauhtémoc y Delicias. Un mes después unas 200 regresaron con acompañamiento policial y militar. Organizaciones como Alianza Sierra Madre y Contec advierten un desplazamiento silencioso que ha vaciado pueblos. Ubicación aproximada (cabecera de Guadalupe y Calvo).</t>
-        </is>
-      </c>
-      <c r="M249" s="3" t="inlineStr">
-        <is>
-          <t>elimparcial</t>
-        </is>
-      </c>
-      <c r="N249" s="3" t="inlineStr">
-        <is>
-          <t>https://www.elimparcial.com/mexico/2026/04/18/indigenas-raramuri-son-desplazados-por-la-violencia-del-crimen-organizado-en-la-sierra-tarahumara-mientras-organizaciones-civiles-alertan-abandono-del-estado-y-una-crisis-humanitaria-que-ya-afecta-a-miles-de-familias-en-chihuahua/</t>
-        </is>
-      </c>
-      <c r="O249" s="3" t="inlineStr">
-        <is>
-          <t>prensa</t>
-        </is>
-      </c>
-      <c r="P249" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="A249" s="6" t="n"/>
+      <c r="B249" s="6" t="n"/>
+      <c r="C249" s="6" t="n"/>
+      <c r="D249" s="7" t="n"/>
+      <c r="E249" s="6" t="n"/>
+      <c r="F249" s="6" t="n"/>
+      <c r="G249" s="6" t="n"/>
+      <c r="H249" s="6" t="n"/>
+      <c r="I249" s="6" t="n"/>
+      <c r="J249" s="6" t="n"/>
+      <c r="K249" s="6" t="n"/>
+      <c r="L249" s="6" t="n"/>
+      <c r="M249" s="6" t="n"/>
+      <c r="N249" s="6" t="n"/>
+      <c r="O249" s="6" t="n"/>
+      <c r="P249" s="6" t="n"/>
     </row>
     <row r="250">
-      <c r="A250" s="3" t="inlineStr">
-        <is>
-          <t>ev-028</t>
-        </is>
-      </c>
-      <c r="B250" s="3" t="inlineStr">
-        <is>
-          <t>desplazamiento</t>
-        </is>
-      </c>
-      <c r="C250" s="3" t="inlineStr"/>
-      <c r="D250" s="4" t="inlineStr"/>
-      <c r="E250" s="3" t="inlineStr"/>
-      <c r="F250" s="3" t="inlineStr">
-        <is>
-          <t>cifra oficial</t>
-        </is>
-      </c>
-      <c r="G250" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="H250" s="3" t="n">
-        <v>24.809</v>
-      </c>
-      <c r="I250" s="3" t="n">
-        <v>-107.394</v>
-      </c>
-      <c r="J250" s="5" t="inlineStr">
-        <is>
-          <t>Culiacán, Sinaloa</t>
-        </is>
-      </c>
-      <c r="K250" s="5" t="inlineStr">
-        <is>
-          <t>Sebides: padrón de unas 3 mil personas y mil 300 familias más desde noviembre de 2025</t>
-        </is>
-      </c>
-      <c r="L250" s="5" t="inlineStr">
-        <is>
-          <t>El titular de Sebides informó un padrón de alrededor de 3 mil personas en desplazamiento forzado interno y mil 300 familias adicionales detectadas desde finales de 2025; Culiacán, Mazatlán y Guasave concentran la llegada. Se anunció el programa Viviendas para el Bienestar para víctimas sin casa propia. Cifra estatal ubicada en la capital.</t>
-        </is>
-      </c>
-      <c r="M250" s="3" t="inlineStr">
-        <is>
-          <t>sebides</t>
-        </is>
-      </c>
-      <c r="N250" s="3" t="inlineStr">
-        <is>
-          <t>https://revistaespejo.com/2026/03/14/gobierno-de-sinaloa-registra-mas-de-4-mil-personas-desplazadas/</t>
-        </is>
-      </c>
-      <c r="O250" s="3" t="inlineStr">
-        <is>
-          <t>oficial</t>
-        </is>
-      </c>
-      <c r="P250" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="A250" s="6" t="n"/>
+      <c r="B250" s="6" t="n"/>
+      <c r="C250" s="6" t="n"/>
+      <c r="D250" s="7" t="n"/>
+      <c r="E250" s="6" t="n"/>
+      <c r="F250" s="6" t="n"/>
+      <c r="G250" s="6" t="n"/>
+      <c r="H250" s="6" t="n"/>
+      <c r="I250" s="6" t="n"/>
+      <c r="J250" s="6" t="n"/>
+      <c r="K250" s="6" t="n"/>
+      <c r="L250" s="6" t="n"/>
+      <c r="M250" s="6" t="n"/>
+      <c r="N250" s="6" t="n"/>
+      <c r="O250" s="6" t="n"/>
+      <c r="P250" s="6" t="n"/>
     </row>
     <row r="251">
-      <c r="A251" s="3" t="inlineStr">
-        <is>
-          <t>ev-060</t>
-        </is>
-      </c>
-      <c r="B251" s="3" t="inlineStr">
-        <is>
-          <t>periodistas</t>
-        </is>
-      </c>
-      <c r="C251" s="3" t="inlineStr">
-        <is>
-          <t>defensor</t>
-        </is>
-      </c>
-      <c r="D251" s="4" t="inlineStr">
-        <is>
-          <t>asesinato</t>
-        </is>
-      </c>
-      <c r="E251" s="3" t="inlineStr">
-        <is>
-          <t>masculino</t>
-        </is>
-      </c>
-      <c r="F251" s="3" t="inlineStr">
-        <is>
-          <t>asesinato de persona defensora</t>
-        </is>
-      </c>
-      <c r="G251" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-12</t>
-        </is>
-      </c>
-      <c r="H251" s="3" t="n">
-        <v>19.392</v>
-      </c>
-      <c r="I251" s="3" t="n">
-        <v>-101.278</v>
-      </c>
-      <c r="J251" s="5" t="inlineStr">
-        <is>
-          <t>El Zangarro, Villa Madero, Michoacán</t>
-        </is>
-      </c>
-      <c r="K251" s="5" t="inlineStr">
-        <is>
-          <t>Asesinato de Roberto Chávez, Comité de Defensa Ambiental de El Zangarro</t>
-        </is>
-      </c>
-      <c r="L251" s="5" t="inlineStr">
-        <is>
-          <t>Defensor ambiental de 64 años, asesinado a balazos la noche del 12 de abril al regresar a su casa. CEMDA contabiliza al menos 195 personas defensoras ambientales asesinadas en México entre 2016 y 2026. Ubicación aproximada (cabecera municipal).</t>
-        </is>
-      </c>
-      <c r="M251" s="3" t="inlineStr">
-        <is>
-          <t>cemda</t>
-        </is>
-      </c>
-      <c r="N251" s="3" t="inlineStr">
-        <is>
-          <t>https://grupoanimal.mx/explicaciones/defensores-ambientales-asesinados-mexico</t>
-        </is>
-      </c>
-      <c r="O251" s="3" t="inlineStr">
-        <is>
-          <t>organización</t>
-        </is>
-      </c>
-      <c r="P251" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="A251" s="6" t="n"/>
+      <c r="B251" s="6" t="n"/>
+      <c r="C251" s="6" t="n"/>
+      <c r="D251" s="7" t="n"/>
+      <c r="E251" s="6" t="n"/>
+      <c r="F251" s="6" t="n"/>
+      <c r="G251" s="6" t="n"/>
+      <c r="H251" s="6" t="n"/>
+      <c r="I251" s="6" t="n"/>
+      <c r="J251" s="6" t="n"/>
+      <c r="K251" s="6" t="n"/>
+      <c r="L251" s="6" t="n"/>
+      <c r="M251" s="6" t="n"/>
+      <c r="N251" s="6" t="n"/>
+      <c r="O251" s="6" t="n"/>
+      <c r="P251" s="6" t="n"/>
     </row>
     <row r="252">
-      <c r="A252" s="3" t="inlineStr">
-        <is>
-          <t>ev-061</t>
-        </is>
-      </c>
-      <c r="B252" s="3" t="inlineStr">
-        <is>
-          <t>periodistas</t>
-        </is>
-      </c>
-      <c r="C252" s="3" t="inlineStr">
-        <is>
-          <t>defensor</t>
-        </is>
-      </c>
-      <c r="D252" s="4" t="inlineStr">
-        <is>
-          <t>asesinato</t>
-        </is>
-      </c>
-      <c r="E252" s="3" t="inlineStr">
-        <is>
-          <t>masculino</t>
-        </is>
-      </c>
-      <c r="F252" s="3" t="inlineStr">
-        <is>
-          <t>desaparición y asesinato de persona defensora</t>
-        </is>
-      </c>
-      <c r="G252" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="H252" s="3" t="n">
-        <v>19.401</v>
-      </c>
-      <c r="I252" s="3" t="n">
-        <v>-101.732</v>
-      </c>
-      <c r="J252" s="5" t="inlineStr">
-        <is>
-          <t>Zirahuén, Salvador Escalante, Michoacán</t>
-        </is>
-      </c>
-      <c r="K252" s="5" t="inlineStr">
-        <is>
-          <t>Lázaro Mendoza Ramírez, defensor de la región lacustre de Zirahuén, desaparecido y hallado sin vida</t>
-        </is>
-      </c>
-      <c r="L252" s="5" t="inlineStr">
-        <is>
-          <t>Desaparecido el 14 de abril; su cuerpo fue localizado calcinado en su camioneta e identificado por ADN. Segundo defensor ambiental asesinado en Michoacán en menos de una semana. Ubicación aproximada (cabecera municipal).</t>
-        </is>
-      </c>
-      <c r="M252" s="3" t="inlineStr">
-        <is>
-          <t>cemda</t>
-        </is>
-      </c>
-      <c r="N252" s="3" t="inlineStr">
-        <is>
-          <t>https://grupoanimal.mx/sociedad/ambientalistas-asesinados-semana-michoacan</t>
-        </is>
-      </c>
-      <c r="O252" s="3" t="inlineStr">
-        <is>
-          <t>organización</t>
-        </is>
-      </c>
-      <c r="P252" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="A252" s="6" t="n"/>
+      <c r="B252" s="6" t="n"/>
+      <c r="C252" s="6" t="n"/>
+      <c r="D252" s="7" t="n"/>
+      <c r="E252" s="6" t="n"/>
+      <c r="F252" s="6" t="n"/>
+      <c r="G252" s="6" t="n"/>
+      <c r="H252" s="6" t="n"/>
+      <c r="I252" s="6" t="n"/>
+      <c r="J252" s="6" t="n"/>
+      <c r="K252" s="6" t="n"/>
+      <c r="L252" s="6" t="n"/>
+      <c r="M252" s="6" t="n"/>
+      <c r="N252" s="6" t="n"/>
+      <c r="O252" s="6" t="n"/>
+      <c r="P252" s="6" t="n"/>
     </row>
     <row r="253">
-      <c r="A253" s="3" t="inlineStr">
-        <is>
-          <t>ev-029</t>
-        </is>
-      </c>
-      <c r="B253" s="3" t="inlineStr">
-        <is>
-          <t>desplazamiento</t>
-        </is>
-      </c>
-      <c r="C253" s="3" t="inlineStr"/>
-      <c r="D253" s="4" t="inlineStr"/>
-      <c r="E253" s="3" t="inlineStr"/>
-      <c r="F253" s="3" t="inlineStr">
-        <is>
-          <t>desplazamiento masivo</t>
-        </is>
-      </c>
-      <c r="G253" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="H253" s="3" t="n">
-        <v>24.968</v>
-      </c>
-      <c r="I253" s="3" t="n">
-        <v>-106.965</v>
-      </c>
-      <c r="J253" s="5" t="inlineStr">
-        <is>
-          <t>Tamazula, Durango</t>
-        </is>
-      </c>
-      <c r="K253" s="5" t="inlineStr">
-        <is>
-          <t>Al menos 368 personas desplazadas de Tamazula por enfrentamientos y amenazas de reclutamiento</t>
-        </is>
-      </c>
-      <c r="L253" s="5" t="inlineStr">
-        <is>
-          <t>Según el informe sobre desplazamiento forzado en Chihuahua (mayo de 2026), al menos 368 personas de Tamazula, en el Triángulo Dorado, salieron por enfrentamientos, bloqueos de rutas, desabasto y amenazas de reclutamiento de jóvenes; la cabecera solo es accesible por aire desde El Durazno. Fecha del informe. Ubicación aproximada (cabecera municipal).</t>
-        </is>
-      </c>
-      <c r="M253" s="3" t="inlineStr">
-        <is>
-          <t>mco-chihuahua</t>
-        </is>
-      </c>
-      <c r="N253" s="3" t="inlineStr">
-        <is>
-          <t>https://www.eldiariodechihuahua.mx/estado/2026/sep/24/llegan-desplazados-de-durango-y-sinaloa-840648.html</t>
-        </is>
-      </c>
-      <c r="O253" s="3" t="inlineStr">
-        <is>
-          <t>organización</t>
-        </is>
-      </c>
-      <c r="P253" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="A253" s="6" t="n"/>
+      <c r="B253" s="6" t="n"/>
+      <c r="C253" s="6" t="n"/>
+      <c r="D253" s="7" t="n"/>
+      <c r="E253" s="6" t="n"/>
+      <c r="F253" s="6" t="n"/>
+      <c r="G253" s="6" t="n"/>
+      <c r="H253" s="6" t="n"/>
+      <c r="I253" s="6" t="n"/>
+      <c r="J253" s="6" t="n"/>
+      <c r="K253" s="6" t="n"/>
+      <c r="L253" s="6" t="n"/>
+      <c r="M253" s="6" t="n"/>
+      <c r="N253" s="6" t="n"/>
+      <c r="O253" s="6" t="n"/>
+      <c r="P253" s="6" t="n"/>
     </row>
     <row r="254">
-      <c r="A254" s="3" t="inlineStr">
-        <is>
-          <t>ev-030</t>
-        </is>
-      </c>
-      <c r="B254" s="3" t="inlineStr">
-        <is>
-          <t>desplazamiento</t>
-        </is>
-      </c>
-      <c r="C254" s="3" t="inlineStr"/>
-      <c r="D254" s="4" t="inlineStr"/>
-      <c r="E254" s="3" t="inlineStr"/>
-      <c r="F254" s="3" t="inlineStr">
-        <is>
-          <t>desplazamiento masivo</t>
-        </is>
-      </c>
-      <c r="G254" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="H254" s="3" t="n">
-        <v>19.088</v>
-      </c>
-      <c r="I254" s="3" t="n">
-        <v>-102.353</v>
-      </c>
-      <c r="J254" s="5" t="inlineStr">
-        <is>
-          <t>Apatzingán, Michoacán</t>
-        </is>
-      </c>
-      <c r="K254" s="5" t="inlineStr">
-        <is>
-          <t>Balaceras desplazan a 668 personas de cinco comunidades de Apatzingán</t>
-        </is>
-      </c>
-      <c r="L254" s="5" t="inlineStr">
-        <is>
-          <t>El Observatorio de Seguridad Humana de la Región Apatzingán registró la salida de 314 personas de Holanda, 168 de Cueramato, 123 de Guanajuatillo, 58 de El Mezquital y 5 de Los Laureles tras enfrentamientos entre grupos criminales; exigió aplicar el Reglamento municipal de respuesta a emergencias de desplazamiento. Ubicación aproximada (cabecera municipal).</t>
-        </is>
-      </c>
-      <c r="M254" s="3" t="inlineStr">
-        <is>
-          <t>oshra</t>
-        </is>
-      </c>
-      <c r="N254" s="3" t="inlineStr">
-        <is>
-          <t>https://www.meganoticias.mx/morelia/noticia/violencia-desplaza-familias-en-apatzingan-michoacan-sigue-sin-cifras-oficiales/733651</t>
-        </is>
-      </c>
-      <c r="O254" s="3" t="inlineStr">
-        <is>
-          <t>organización</t>
-        </is>
-      </c>
-      <c r="P254" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="A254" s="6" t="n"/>
+      <c r="B254" s="6" t="n"/>
+      <c r="C254" s="6" t="n"/>
+      <c r="D254" s="7" t="n"/>
+      <c r="E254" s="6" t="n"/>
+      <c r="F254" s="6" t="n"/>
+      <c r="G254" s="6" t="n"/>
+      <c r="H254" s="6" t="n"/>
+      <c r="I254" s="6" t="n"/>
+      <c r="J254" s="6" t="n"/>
+      <c r="K254" s="6" t="n"/>
+      <c r="L254" s="6" t="n"/>
+      <c r="M254" s="6" t="n"/>
+      <c r="N254" s="6" t="n"/>
+      <c r="O254" s="6" t="n"/>
+      <c r="P254" s="6" t="n"/>
     </row>
     <row r="255">
-      <c r="A255" s="3" t="inlineStr">
-        <is>
-          <t>ev-031</t>
-        </is>
-      </c>
-      <c r="B255" s="3" t="inlineStr">
-        <is>
-          <t>desplazamiento</t>
-        </is>
-      </c>
-      <c r="C255" s="3" t="inlineStr"/>
-      <c r="D255" s="4" t="inlineStr"/>
-      <c r="E255" s="3" t="inlineStr"/>
-      <c r="F255" s="3" t="inlineStr">
-        <is>
-          <t>desplazamiento masivo</t>
-        </is>
-      </c>
-      <c r="G255" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="H255" s="3" t="n">
-        <v>17.595</v>
-      </c>
-      <c r="I255" s="3" t="n">
-        <v>-99.17700000000001</v>
-      </c>
-      <c r="J255" s="5" t="inlineStr">
-        <is>
-          <t>Alcozacán, Chilapa de Álvarez, Guerrero</t>
-        </is>
-      </c>
-      <c r="K255" s="5" t="inlineStr">
-        <is>
-          <t>Comunidades nahuas de Chilapa huyen a Alcozacán por ataques con drones explosivos</t>
-        </is>
-      </c>
-      <c r="L255" s="5" t="inlineStr">
-        <is>
-          <t>Entre el 6 y el 11 de mayo, ataques atribuidos a Los Ardillos con armas de alto calibre y drones cargados con explosivos vaciaron Tula, Xicotlán y Acahuehuetlán; entre 800 y más de mil 300 personas se refugiaron en la iglesia y la cancha de Alcozacán. La cifra oficial reconoció 96 desplazados y seis heridos. El saldo incluyó seis muertos, casas quemadas y ganado muerto. Ubicación aproximada (cabecera de Chilapa).</t>
-        </is>
-      </c>
-      <c r="M255" s="3" t="inlineStr">
-        <is>
-          <t>sillarota</t>
-        </is>
-      </c>
-      <c r="N255" s="3" t="inlineStr">
-        <is>
-          <t>https://lasillarota.com/estados/2026/5/14/casas-quemadas-ganado-muerto-96-desplazados-el-saldo-en-chilapa-por-los-ardillos-510079.html</t>
-        </is>
-      </c>
-      <c r="O255" s="3" t="inlineStr">
-        <is>
-          <t>prensa</t>
-        </is>
-      </c>
-      <c r="P255" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="A255" s="6" t="n"/>
+      <c r="B255" s="6" t="n"/>
+      <c r="C255" s="6" t="n"/>
+      <c r="D255" s="7" t="n"/>
+      <c r="E255" s="6" t="n"/>
+      <c r="F255" s="6" t="n"/>
+      <c r="G255" s="6" t="n"/>
+      <c r="H255" s="6" t="n"/>
+      <c r="I255" s="6" t="n"/>
+      <c r="J255" s="6" t="n"/>
+      <c r="K255" s="6" t="n"/>
+      <c r="L255" s="6" t="n"/>
+      <c r="M255" s="6" t="n"/>
+      <c r="N255" s="6" t="n"/>
+      <c r="O255" s="6" t="n"/>
+      <c r="P255" s="6" t="n"/>
     </row>
     <row r="256">
-      <c r="A256" s="3" t="inlineStr">
-        <is>
-          <t>ev-062</t>
-        </is>
-      </c>
-      <c r="B256" s="3" t="inlineStr">
-        <is>
-          <t>periodistas</t>
-        </is>
-      </c>
-      <c r="C256" s="3" t="inlineStr">
-        <is>
-          <t>periodista</t>
-        </is>
-      </c>
-      <c r="D256" s="4" t="inlineStr">
-        <is>
-          <t>informe</t>
-        </is>
-      </c>
-      <c r="E256" s="3" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="F256" s="3" t="inlineStr">
-        <is>
-          <t>informe</t>
-        </is>
-      </c>
-      <c r="G256" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="H256" s="3" t="n">
-        <v>19.432</v>
-      </c>
-      <c r="I256" s="3" t="n">
-        <v>-99.133</v>
-      </c>
-      <c r="J256" s="5" t="inlineStr">
-        <is>
-          <t>Ciudad de México</t>
-        </is>
-      </c>
-      <c r="K256" s="5" t="inlineStr">
-        <is>
-          <t>ARTICLE 19: 451 agresiones a la prensa en 2025, siete asesinatos y ocho tentativas</t>
-        </is>
-      </c>
-      <c r="L256" s="5" t="inlineStr">
-        <is>
-          <t>Informe Estructuras del silencio. Una agresión cada 19 horas; 44 por ciento ambiente hostil, 34 abuso del poder público, 12 violencia física. El Estado fue el agresor en 227 casos. Ciudad de México, Puebla y Veracruz encabezan; Sinaloa registra solo nueve casos, lo que la organización atribuye a autocensura y a denuncias por canales confidenciales. 2025 fue también el año más letal para personas buscadoras (siete asesinatos y cuatro desapariciones). Cifra nacional ubicada en la capital.</t>
-        </is>
-      </c>
-      <c r="M256" s="3" t="inlineStr">
-        <is>
-          <t>article19</t>
-        </is>
-      </c>
-      <c r="N256" s="3" t="inlineStr">
-        <is>
-          <t>https://articulo19.org/wp-content/uploads/2026/05/Estructuras-del-Silencio-Informe-Anual-2025-A19-MXCA_compressed.pdf</t>
-        </is>
-      </c>
-      <c r="O256" s="3" t="inlineStr">
-        <is>
-          <t>organización</t>
-        </is>
-      </c>
-      <c r="P256" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="A256" s="6" t="n"/>
+      <c r="B256" s="6" t="n"/>
+      <c r="C256" s="6" t="n"/>
+      <c r="D256" s="7" t="n"/>
+      <c r="E256" s="6" t="n"/>
+      <c r="F256" s="6" t="n"/>
+      <c r="G256" s="6" t="n"/>
+      <c r="H256" s="6" t="n"/>
+      <c r="I256" s="6" t="n"/>
+      <c r="J256" s="6" t="n"/>
+      <c r="K256" s="6" t="n"/>
+      <c r="L256" s="6" t="n"/>
+      <c r="M256" s="6" t="n"/>
+      <c r="N256" s="6" t="n"/>
+      <c r="O256" s="6" t="n"/>
+      <c r="P256" s="6" t="n"/>
     </row>
     <row r="257">
-      <c r="A257" s="3" t="inlineStr">
-        <is>
-          <t>ev-032</t>
-        </is>
-      </c>
-      <c r="B257" s="3" t="inlineStr">
-        <is>
-          <t>desplazamiento</t>
-        </is>
-      </c>
-      <c r="C257" s="3" t="inlineStr"/>
-      <c r="D257" s="4" t="inlineStr"/>
-      <c r="E257" s="3" t="inlineStr"/>
-      <c r="F257" s="3" t="inlineStr">
-        <is>
-          <t>retorno</t>
-        </is>
-      </c>
-      <c r="G257" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="H257" s="3" t="n">
-        <v>17.595</v>
-      </c>
-      <c r="I257" s="3" t="n">
-        <v>-99.17700000000001</v>
-      </c>
-      <c r="J257" s="5" t="inlineStr">
-        <is>
-          <t>Chilapa de Álvarez, Guerrero</t>
-        </is>
-      </c>
-      <c r="K257" s="5" t="inlineStr">
-        <is>
-          <t>Retorno de 120 personas a Tula, Xicotlán y Coatzingo con escolta de la Guardia Nacional</t>
-        </is>
-      </c>
-      <c r="L257" s="5" t="inlineStr">
-        <is>
-          <t>Tras cinco días fuera de sus hogares, 120 personas comenzaron a regresar con apoyo de la Guardia Nacional y un corredor seguro de la Defensa; la titular de Segob supervisó el retorno. Ubicación aproximada (cabecera de Chilapa).</t>
-        </is>
-      </c>
-      <c r="M257" s="3" t="inlineStr">
-        <is>
-          <t>elfinanciero</t>
-        </is>
-      </c>
-      <c r="N257" s="3" t="inlineStr">
-        <is>
-          <t>https://www.elfinanciero.com.mx/estados/2026/05/14/familias-indigenas-desplazadas-por-violencia-de-los-ardillos-en-chilapa-regresan-a-sus-comunidades/</t>
-        </is>
-      </c>
-      <c r="O257" s="3" t="inlineStr">
-        <is>
-          <t>prensa</t>
-        </is>
-      </c>
-      <c r="P257" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="A257" s="6" t="n"/>
+      <c r="B257" s="6" t="n"/>
+      <c r="C257" s="6" t="n"/>
+      <c r="D257" s="7" t="n"/>
+      <c r="E257" s="6" t="n"/>
+      <c r="F257" s="6" t="n"/>
+      <c r="G257" s="6" t="n"/>
+      <c r="H257" s="6" t="n"/>
+      <c r="I257" s="6" t="n"/>
+      <c r="J257" s="6" t="n"/>
+      <c r="K257" s="6" t="n"/>
+      <c r="L257" s="6" t="n"/>
+      <c r="M257" s="6" t="n"/>
+      <c r="N257" s="6" t="n"/>
+      <c r="O257" s="6" t="n"/>
+      <c r="P257" s="6" t="n"/>
     </row>
     <row r="258">
-      <c r="A258" s="3" t="inlineStr">
-        <is>
-          <t>ev-063</t>
-        </is>
-      </c>
-      <c r="B258" s="3" t="inlineStr">
-        <is>
-          <t>periodistas</t>
-        </is>
-      </c>
-      <c r="C258" s="3" t="inlineStr">
-        <is>
-          <t>ambos</t>
-        </is>
-      </c>
-      <c r="D258" s="4" t="inlineStr">
-        <is>
-          <t>agresion</t>
-        </is>
-      </c>
-      <c r="E258" s="3" t="inlineStr">
-        <is>
-          <t>no determinado</t>
-        </is>
-      </c>
-      <c r="F258" s="3" t="inlineStr">
-        <is>
-          <t>agresión por autoridad</t>
-        </is>
-      </c>
-      <c r="G258" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="H258" s="3" t="n">
-        <v>24.809</v>
-      </c>
-      <c r="I258" s="3" t="n">
-        <v>-107.394</v>
-      </c>
-      <c r="J258" s="5" t="inlineStr">
-        <is>
-          <t>La Conquista, Culiacán, Sinaloa</t>
-        </is>
-      </c>
-      <c r="K258" s="5" t="inlineStr">
-        <is>
-          <t>Militares golpean a dos periodistas acreditados durante un operativo</t>
-        </is>
-      </c>
-      <c r="L258" s="5" t="inlineStr">
-        <is>
-          <t>Elementos del Ejército golpearon y empujaron a dos periodistas identificados y arrebataron un teléfono; un agente del GOES estatal intervino para protegerlos. El Instituto documentó 125 agresiones entre agosto de 2022 y febrero de 2026, 45 atribuidas a particulares presuntamente vinculados con el crimen. Ubicación aproximada (cabecera municipal).</t>
-        </is>
-      </c>
-      <c r="M258" s="3" t="inlineStr">
-        <is>
-          <t>revistaespejo</t>
-        </is>
-      </c>
-      <c r="N258" s="3" t="inlineStr">
-        <is>
-          <t>https://revistaespejo.com/2026/05/14/periodistas-de-culiacan-acusan-agresiones-por-parte-de-militares/</t>
-        </is>
-      </c>
-      <c r="O258" s="3" t="inlineStr">
-        <is>
-          <t>prensa</t>
-        </is>
-      </c>
-      <c r="P258" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="A258" s="6" t="n"/>
+      <c r="B258" s="6" t="n"/>
+      <c r="C258" s="6" t="n"/>
+      <c r="D258" s="7" t="n"/>
+      <c r="E258" s="6" t="n"/>
+      <c r="F258" s="6" t="n"/>
+      <c r="G258" s="6" t="n"/>
+      <c r="H258" s="6" t="n"/>
+      <c r="I258" s="6" t="n"/>
+      <c r="J258" s="6" t="n"/>
+      <c r="K258" s="6" t="n"/>
+      <c r="L258" s="6" t="n"/>
+      <c r="M258" s="6" t="n"/>
+      <c r="N258" s="6" t="n"/>
+      <c r="O258" s="6" t="n"/>
+      <c r="P258" s="6" t="n"/>
     </row>
     <row r="259">
-      <c r="A259" s="3" t="inlineStr">
-        <is>
-          <t>ev-064</t>
-        </is>
-      </c>
-      <c r="B259" s="3" t="inlineStr">
-        <is>
-          <t>periodistas</t>
-        </is>
-      </c>
-      <c r="C259" s="3" t="inlineStr">
-        <is>
-          <t>periodista</t>
-        </is>
-      </c>
-      <c r="D259" s="4" t="inlineStr">
-        <is>
-          <t>proteccion</t>
-        </is>
-      </c>
-      <c r="E259" s="3" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="F259" s="3" t="inlineStr">
-        <is>
-          <t>cifra gremial</t>
-        </is>
-      </c>
-      <c r="G259" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="H259" s="3" t="n">
-        <v>24.809</v>
-      </c>
-      <c r="I259" s="3" t="n">
-        <v>-107.394</v>
-      </c>
-      <c r="J259" s="5" t="inlineStr">
-        <is>
-          <t>Culiacán, Sinaloa</t>
-        </is>
-      </c>
-      <c r="K259" s="5" t="inlineStr">
-        <is>
-          <t>Asociación 7 de Junio: más de 100 incidentes contra periodistas desde septiembre de 2024</t>
-        </is>
-      </c>
-      <c r="L259" s="5" t="inlineStr">
-        <is>
-          <t>El presidente de la asociación denunció que menos de 20 casos se han formalizado ante la vicefiscalía especializada y que las autoridades reclasifican agresiones como robos sin analizar el contexto periodístico. Ubicación aproximada (cabecera municipal).</t>
-        </is>
-      </c>
-      <c r="M259" s="3" t="inlineStr">
-        <is>
-          <t>asociacion-7-junio</t>
-        </is>
-      </c>
-      <c r="N259" s="3" t="inlineStr">
-        <is>
-          <t>https://www.sectorprimario.mx/2026/05/15/mas-de-100-agresiones-silencian-al-periodismo-en-sinaloa/</t>
-        </is>
-      </c>
-      <c r="O259" s="3" t="inlineStr">
-        <is>
-          <t>organización</t>
-        </is>
-      </c>
-      <c r="P259" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="A259" s="6" t="n"/>
+      <c r="B259" s="6" t="n"/>
+      <c r="C259" s="6" t="n"/>
+      <c r="D259" s="7" t="n"/>
+      <c r="E259" s="6" t="n"/>
+      <c r="F259" s="6" t="n"/>
+      <c r="G259" s="6" t="n"/>
+      <c r="H259" s="6" t="n"/>
+      <c r="I259" s="6" t="n"/>
+      <c r="J259" s="6" t="n"/>
+      <c r="K259" s="6" t="n"/>
+      <c r="L259" s="6" t="n"/>
+      <c r="M259" s="6" t="n"/>
+      <c r="N259" s="6" t="n"/>
+      <c r="O259" s="6" t="n"/>
+      <c r="P259" s="6" t="n"/>
     </row>
     <row r="260">
-      <c r="A260" s="3" t="inlineStr">
-        <is>
-          <t>ev-033</t>
-        </is>
-      </c>
-      <c r="B260" s="3" t="inlineStr">
-        <is>
-          <t>desplazamiento</t>
-        </is>
-      </c>
-      <c r="C260" s="3" t="inlineStr"/>
-      <c r="D260" s="4" t="inlineStr"/>
-      <c r="E260" s="3" t="inlineStr"/>
-      <c r="F260" s="3" t="inlineStr">
-        <is>
-          <t>retorno</t>
-        </is>
-      </c>
-      <c r="G260" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="H260" s="3" t="n">
-        <v>19.088</v>
-      </c>
-      <c r="I260" s="3" t="n">
-        <v>-102.353</v>
-      </c>
-      <c r="J260" s="5" t="inlineStr">
-        <is>
-          <t>Apatzingán, Michoacán</t>
-        </is>
-      </c>
-      <c r="K260" s="5" t="inlineStr">
-        <is>
-          <t>Cerca de 20 familias regresan a Holanda, Cueramato, Guanajuatillo y otras comunidades</t>
-        </is>
-      </c>
-      <c r="L260" s="5" t="inlineStr">
-        <is>
-          <t>Según el Observatorio de Seguridad Humana, unas 20 familias desplazadas por los enfrentamientos del 5 de mayo retornaron a sus comunidades en la zona rural de Apatzingán. Ubicación aproximada (cabecera municipal).</t>
-        </is>
-      </c>
-      <c r="M260" s="3" t="inlineStr">
-        <is>
-          <t>milenio</t>
-        </is>
-      </c>
-      <c r="N260" s="3" t="inlineStr">
-        <is>
-          <t>https://www.milenio.com/estados/regresan-familias-tras-ser-desplazadas-por-la-violencia-en-apatzingan</t>
-        </is>
-      </c>
-      <c r="O260" s="3" t="inlineStr">
-        <is>
-          <t>prensa</t>
-        </is>
-      </c>
-      <c r="P260" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="A260" s="6" t="n"/>
+      <c r="B260" s="6" t="n"/>
+      <c r="C260" s="6" t="n"/>
+      <c r="D260" s="7" t="n"/>
+      <c r="E260" s="6" t="n"/>
+      <c r="F260" s="6" t="n"/>
+      <c r="G260" s="6" t="n"/>
+      <c r="H260" s="6" t="n"/>
+      <c r="I260" s="6" t="n"/>
+      <c r="J260" s="6" t="n"/>
+      <c r="K260" s="6" t="n"/>
+      <c r="L260" s="6" t="n"/>
+      <c r="M260" s="6" t="n"/>
+      <c r="N260" s="6" t="n"/>
+      <c r="O260" s="6" t="n"/>
+      <c r="P260" s="6" t="n"/>
     </row>
     <row r="261">
-      <c r="A261" s="3" t="inlineStr">
-        <is>
-          <t>ev-034</t>
-        </is>
-      </c>
-      <c r="B261" s="3" t="inlineStr">
-        <is>
-          <t>desplazamiento</t>
-        </is>
-      </c>
-      <c r="C261" s="3" t="inlineStr"/>
-      <c r="D261" s="4" t="inlineStr"/>
-      <c r="E261" s="3" t="inlineStr"/>
-      <c r="F261" s="3" t="inlineStr">
-        <is>
-          <t>retorno</t>
-        </is>
-      </c>
-      <c r="G261" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="H261" s="3" t="n">
-        <v>22.647</v>
-      </c>
-      <c r="I261" s="3" t="n">
-        <v>-102.994</v>
-      </c>
-      <c r="J261" s="5" t="inlineStr">
-        <is>
-          <t>Palmas Altas, Jerez, Zacatecas</t>
-        </is>
-      </c>
-      <c r="K261" s="5" t="inlineStr">
-        <is>
-          <t>Familias desplazadas regresan a Palmas Altas y otras comunidades de Jerez</t>
-        </is>
-      </c>
-      <c r="L261" s="5" t="inlineStr">
-        <is>
-          <t>Con el control militar de la zona y la firma de un acuerdo para construir un cuartel regional en Palmas Altas, la mayoría de los habitantes retomó actividades agrícolas, aunque con temor y con familiares desaparecidos. Ubicación aproximada (cabecera de Jerez).</t>
-        </is>
-      </c>
-      <c r="M261" s="3" t="inlineStr">
-        <is>
-          <t>unotv</t>
-        </is>
-      </c>
-      <c r="N261" s="3" t="inlineStr">
-        <is>
-          <t>https://www.unotv.com/estados/zacatecas/con-temor-desplazados-por-la-violencia-regresan-a-comunidades-serranas-de-zacatecas/</t>
-        </is>
-      </c>
-      <c r="O261" s="3" t="inlineStr">
-        <is>
-          <t>prensa</t>
-        </is>
-      </c>
-      <c r="P261" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="A261" s="6" t="n"/>
+      <c r="B261" s="6" t="n"/>
+      <c r="C261" s="6" t="n"/>
+      <c r="D261" s="7" t="n"/>
+      <c r="E261" s="6" t="n"/>
+      <c r="F261" s="6" t="n"/>
+      <c r="G261" s="6" t="n"/>
+      <c r="H261" s="6" t="n"/>
+      <c r="I261" s="6" t="n"/>
+      <c r="J261" s="6" t="n"/>
+      <c r="K261" s="6" t="n"/>
+      <c r="L261" s="6" t="n"/>
+      <c r="M261" s="6" t="n"/>
+      <c r="N261" s="6" t="n"/>
+      <c r="O261" s="6" t="n"/>
+      <c r="P261" s="6" t="n"/>
     </row>
     <row r="262">
-      <c r="A262" s="3" t="inlineStr">
-        <is>
-          <t>ev-065</t>
-        </is>
-      </c>
-      <c r="B262" s="3" t="inlineStr">
-        <is>
-          <t>periodistas</t>
-        </is>
-      </c>
-      <c r="C262" s="3" t="inlineStr">
-        <is>
-          <t>periodista</t>
-        </is>
-      </c>
-      <c r="D262" s="4" t="inlineStr">
-        <is>
-          <t>asesinato</t>
-        </is>
-      </c>
-      <c r="E262" s="3" t="inlineStr">
-        <is>
-          <t>femenino</t>
-        </is>
-      </c>
-      <c r="F262" s="3" t="inlineStr">
-        <is>
-          <t>secuestro y asesinato de periodista</t>
-        </is>
-      </c>
-      <c r="G262" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="H262" s="3" t="n">
-        <v>17.995</v>
-      </c>
-      <c r="I262" s="3" t="n">
-        <v>-94.348</v>
-      </c>
-      <c r="J262" s="5" t="inlineStr">
-        <is>
-          <t>Moloacán, Veracruz</t>
-        </is>
-      </c>
-      <c r="K262" s="5" t="inlineStr">
-        <is>
-          <t>Roxana Guzmán Ramírez, Pulso Informativo del Sureste, secuestrada y hallada sin vida</t>
-        </is>
-      </c>
-      <c r="L262" s="5" t="inlineStr">
-        <is>
-          <t>Sacada de su casa por hombres armados el 2 de junio de 2026; sus restos fueron identificados el 3 de julio en un predio de Moloacán. Las autoridades señalaron a funcionarios municipales como responsables, según CPJ. Ubicación aproximada (cabecera municipal). Figura como número 178 en el registro de periodistas asesinados de ARTICLE 19.</t>
-        </is>
-      </c>
-      <c r="M262" s="3" t="inlineStr">
-        <is>
-          <t>excelsior</t>
-        </is>
-      </c>
-      <c r="N262" s="3" t="inlineStr">
-        <is>
-          <t>https://www.excelsior.com.mx/nacional/suma-mexico-seis-periodistas-asesinados-2026-cpj-exige-frenar-ataques-y-fin-impunidad</t>
-        </is>
-      </c>
-      <c r="O262" s="3" t="inlineStr">
-        <is>
-          <t>prensa</t>
-        </is>
-      </c>
-      <c r="P262" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="A262" s="6" t="n"/>
+      <c r="B262" s="6" t="n"/>
+      <c r="C262" s="6" t="n"/>
+      <c r="D262" s="7" t="n"/>
+      <c r="E262" s="6" t="n"/>
+      <c r="F262" s="6" t="n"/>
+      <c r="G262" s="6" t="n"/>
+      <c r="H262" s="6" t="n"/>
+      <c r="I262" s="6" t="n"/>
+      <c r="J262" s="6" t="n"/>
+      <c r="K262" s="6" t="n"/>
+      <c r="L262" s="6" t="n"/>
+      <c r="M262" s="6" t="n"/>
+      <c r="N262" s="6" t="n"/>
+      <c r="O262" s="6" t="n"/>
+      <c r="P262" s="6" t="n"/>
     </row>
     <row r="263">
-      <c r="A263" s="3" t="inlineStr">
-        <is>
-          <t>ev-066</t>
-        </is>
-      </c>
-      <c r="B263" s="3" t="inlineStr">
-        <is>
-          <t>periodistas</t>
-        </is>
-      </c>
-      <c r="C263" s="3" t="inlineStr">
-        <is>
-          <t>ambos</t>
-        </is>
-      </c>
-      <c r="D263" s="4" t="inlineStr">
-        <is>
-          <t>proteccion</t>
-        </is>
-      </c>
-      <c r="E263" s="3" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="F263" s="3" t="inlineStr">
-        <is>
-          <t>cifra oficial</t>
-        </is>
-      </c>
-      <c r="G263" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="H263" s="3" t="n">
-        <v>24.809</v>
-      </c>
-      <c r="I263" s="3" t="n">
-        <v>-107.394</v>
-      </c>
-      <c r="J263" s="5" t="inlineStr">
-        <is>
-          <t>Culiacán, Sinaloa</t>
-        </is>
-      </c>
-      <c r="K263" s="5" t="inlineStr">
-        <is>
-          <t>Instituto de Protección alerta repunte de agresiones desde marzo de 2026</t>
-        </is>
-      </c>
-      <c r="L263" s="5" t="inlineStr">
-        <is>
-          <t>133 medidas de protección activadas en 2026, 27 quejas entre enero y abril, y 12 periodistas que han salido del estado por amenazas en los últimos años. Agresiones tanto de fuerzas de seguridad como de grupos armados, incluidas mujeres periodistas en cobertura. Ubicación aproximada (cabecera municipal).</t>
-        </is>
-      </c>
-      <c r="M263" s="3" t="inlineStr">
-        <is>
-          <t>instituto-sinaloa</t>
-        </is>
-      </c>
-      <c r="N263" s="3" t="inlineStr">
-        <is>
-          <t>https://noticieroaltavoz.com/este-7-de-junio-dia-de-la-libertad-de-expresion-alertan-por-repunte-de-agresiones-contra-periodistas-en-sinaloa/</t>
-        </is>
-      </c>
-      <c r="O263" s="3" t="inlineStr">
-        <is>
-          <t>oficial</t>
-        </is>
-      </c>
-      <c r="P263" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="A263" s="6" t="n"/>
+      <c r="B263" s="6" t="n"/>
+      <c r="C263" s="6" t="n"/>
+      <c r="D263" s="7" t="n"/>
+      <c r="E263" s="6" t="n"/>
+      <c r="F263" s="6" t="n"/>
+      <c r="G263" s="6" t="n"/>
+      <c r="H263" s="6" t="n"/>
+      <c r="I263" s="6" t="n"/>
+      <c r="J263" s="6" t="n"/>
+      <c r="K263" s="6" t="n"/>
+      <c r="L263" s="6" t="n"/>
+      <c r="M263" s="6" t="n"/>
+      <c r="N263" s="6" t="n"/>
+      <c r="O263" s="6" t="n"/>
+      <c r="P263" s="6" t="n"/>
     </row>
     <row r="264">
-      <c r="A264" s="3" t="inlineStr">
-        <is>
-          <t>ev-035</t>
-        </is>
-      </c>
-      <c r="B264" s="3" t="inlineStr">
-        <is>
-          <t>desplazamiento</t>
-        </is>
-      </c>
-      <c r="C264" s="3" t="inlineStr"/>
-      <c r="D264" s="4" t="inlineStr"/>
-      <c r="E264" s="3" t="inlineStr"/>
-      <c r="F264" s="3" t="inlineStr">
-        <is>
-          <t>desplazamiento masivo</t>
-        </is>
-      </c>
-      <c r="G264" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="H264" s="3" t="n">
-        <v>22.837</v>
-      </c>
-      <c r="I264" s="3" t="n">
-        <v>-105.776</v>
-      </c>
-      <c r="J264" s="5" t="inlineStr">
-        <is>
-          <t>Escuinapa, Sinaloa</t>
-        </is>
-      </c>
-      <c r="K264" s="5" t="inlineStr">
-        <is>
-          <t>Comunidades rurales de Escuinapa quedan vacías; familias buscan refugio en Nayarit y Mazatlán</t>
-        </is>
-      </c>
-      <c r="L264" s="5" t="inlineStr">
-        <is>
-          <t>La CEDH inició la documentación de familias desplazadas por la escalada de violencia iniciada a mediados de diciembre de 2025 (coche bomba, ataques al ayuntamiento, homicidios). El alcalde negó un desplazamiento masivo pero reconoció salidas en Tecualilla, Palmillas y El Camarón. Ubicación aproximada (cabecera municipal).</t>
-        </is>
-      </c>
-      <c r="M264" s="3" t="inlineStr">
-        <is>
-          <t>infobae</t>
-        </is>
-      </c>
-      <c r="N264" s="3" t="inlineStr">
-        <is>
-          <t>https://www.infobae.com/mexico/2026/06/11/violencia-en-escuinapa-desata-desplazamiento-de-habitantes-cedh-inicia-documentacion-de-casos/</t>
-        </is>
-      </c>
-      <c r="O264" s="3" t="inlineStr">
-        <is>
-          <t>prensa</t>
-        </is>
-      </c>
-      <c r="P264" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="A264" s="6" t="n"/>
+      <c r="B264" s="6" t="n"/>
+      <c r="C264" s="6" t="n"/>
+      <c r="D264" s="7" t="n"/>
+      <c r="E264" s="6" t="n"/>
+      <c r="F264" s="6" t="n"/>
+      <c r="G264" s="6" t="n"/>
+      <c r="H264" s="6" t="n"/>
+      <c r="I264" s="6" t="n"/>
+      <c r="J264" s="6" t="n"/>
+      <c r="K264" s="6" t="n"/>
+      <c r="L264" s="6" t="n"/>
+      <c r="M264" s="6" t="n"/>
+      <c r="N264" s="6" t="n"/>
+      <c r="O264" s="6" t="n"/>
+      <c r="P264" s="6" t="n"/>
     </row>
     <row r="265">
-      <c r="A265" s="3" t="inlineStr">
-        <is>
-          <t>ev-067</t>
-        </is>
-      </c>
-      <c r="B265" s="3" t="inlineStr">
-        <is>
-          <t>periodistas</t>
-        </is>
-      </c>
-      <c r="C265" s="3" t="inlineStr">
-        <is>
-          <t>periodista</t>
-        </is>
-      </c>
-      <c r="D265" s="4" t="inlineStr">
-        <is>
-          <t>asesinato</t>
-        </is>
-      </c>
-      <c r="E265" s="3" t="inlineStr">
-        <is>
-          <t>masculino</t>
-        </is>
-      </c>
-      <c r="F265" s="3" t="inlineStr">
-        <is>
-          <t>asesinato de periodista</t>
-        </is>
-      </c>
-      <c r="G265" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="H265" s="3" t="n">
-        <v>20.533</v>
-      </c>
-      <c r="I265" s="3" t="n">
-        <v>-97.459</v>
-      </c>
-      <c r="J265" s="5" t="inlineStr">
-        <is>
-          <t>Poza Rica, Veracruz</t>
-        </is>
-      </c>
-      <c r="K265" s="5" t="inlineStr">
-        <is>
-          <t>Asesinato de Luis Ángel López Valdez, Reportaje Policiaco Veracruzano</t>
-        </is>
-      </c>
-      <c r="L265" s="5" t="inlineStr">
-        <is>
-          <t>Asesinado a balazos la madrugada del 11 de junio en la colonia Cazones, cerca de donde fue asesinado Carlos Castro en enero. Contaba con medidas de acompañamiento y vigilancia. Ubicación aproximada (cabecera municipal). Figura como número 177 en el registro de periodistas asesinados de ARTICLE 19.</t>
-        </is>
-      </c>
-      <c r="M265" s="3" t="inlineStr">
-        <is>
-          <t>rsf</t>
-        </is>
-      </c>
-      <c r="N265" s="3" t="inlineStr">
-        <is>
-          <t>https://rsf.org/es/m%C3%A9xico-el-asesinato-de-francisco-alejandro-leyva-aguilar-s%C3%A9ptimo-periodista-asesinado-en-2026</t>
-        </is>
-      </c>
-      <c r="O265" s="3" t="inlineStr">
-        <is>
-          <t>organización</t>
-        </is>
-      </c>
-      <c r="P265" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="A265" s="6" t="n"/>
+      <c r="B265" s="6" t="n"/>
+      <c r="C265" s="6" t="n"/>
+      <c r="D265" s="7" t="n"/>
+      <c r="E265" s="6" t="n"/>
+      <c r="F265" s="6" t="n"/>
+      <c r="G265" s="6" t="n"/>
+      <c r="H265" s="6" t="n"/>
+      <c r="I265" s="6" t="n"/>
+      <c r="J265" s="6" t="n"/>
+      <c r="K265" s="6" t="n"/>
+      <c r="L265" s="6" t="n"/>
+      <c r="M265" s="6" t="n"/>
+      <c r="N265" s="6" t="n"/>
+      <c r="O265" s="6" t="n"/>
+      <c r="P265" s="6" t="n"/>
     </row>
     <row r="266">
-      <c r="A266" s="3" t="inlineStr">
-        <is>
-          <t>ev-036</t>
-        </is>
-      </c>
-      <c r="B266" s="3" t="inlineStr">
-        <is>
-          <t>desplazamiento</t>
-        </is>
-      </c>
-      <c r="C266" s="3" t="inlineStr"/>
-      <c r="D266" s="4" t="inlineStr"/>
-      <c r="E266" s="3" t="inlineStr"/>
-      <c r="F266" s="3" t="inlineStr">
-        <is>
-          <t>desplazamiento masivo</t>
-        </is>
-      </c>
-      <c r="G266" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="H266" s="3" t="n">
-        <v>26.095</v>
-      </c>
-      <c r="I266" s="3" t="n">
-        <v>-106.965</v>
-      </c>
-      <c r="J266" s="5" t="inlineStr">
-        <is>
-          <t>Guadalupe y Calvo, Chihuahua</t>
-        </is>
-      </c>
-      <c r="K266" s="5" t="inlineStr">
-        <is>
-          <t>Tres comunidades ódami (Milpillas de Abajo, La Arenosa y Arroyo Azul) desplazadas tras enfrentamiento</t>
-        </is>
-      </c>
-      <c r="L266" s="5" t="inlineStr">
-        <is>
-          <t>Un enfrentamiento entre dos grupos armados por la entrada de un nuevo cártel al Triángulo Dorado desplazó a tres comunidades ódami. El Diario de Chihuahua estima que entre 2016 y 2026 al menos 11 mil 534 personas han sido expulsadas de la sierra. Ubicación aproximada (cabecera municipal).</t>
-        </is>
-      </c>
-      <c r="M266" s="3" t="inlineStr">
-        <is>
-          <t>diariochihuahua</t>
-        </is>
-      </c>
-      <c r="N266" s="3" t="inlineStr">
-        <is>
-          <t>https://www.eldiariodechihuahua.mx/estado/2026/jul/10/desplazo-crimen-a-mas-de-11-mil-en-la-sierra-816155.html</t>
-        </is>
-      </c>
-      <c r="O266" s="3" t="inlineStr">
-        <is>
-          <t>prensa</t>
-        </is>
-      </c>
-      <c r="P266" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="A266" s="6" t="n"/>
+      <c r="B266" s="6" t="n"/>
+      <c r="C266" s="6" t="n"/>
+      <c r="D266" s="7" t="n"/>
+      <c r="E266" s="6" t="n"/>
+      <c r="F266" s="6" t="n"/>
+      <c r="G266" s="6" t="n"/>
+      <c r="H266" s="6" t="n"/>
+      <c r="I266" s="6" t="n"/>
+      <c r="J266" s="6" t="n"/>
+      <c r="K266" s="6" t="n"/>
+      <c r="L266" s="6" t="n"/>
+      <c r="M266" s="6" t="n"/>
+      <c r="N266" s="6" t="n"/>
+      <c r="O266" s="6" t="n"/>
+      <c r="P266" s="6" t="n"/>
     </row>
     <row r="267">
-      <c r="A267" s="3" t="inlineStr">
-        <is>
-          <t>ev-037</t>
-        </is>
-      </c>
-      <c r="B267" s="3" t="inlineStr">
-        <is>
-          <t>desplazamiento</t>
-        </is>
-      </c>
-      <c r="C267" s="3" t="inlineStr"/>
-      <c r="D267" s="4" t="inlineStr"/>
-      <c r="E267" s="3" t="inlineStr"/>
-      <c r="F267" s="3" t="inlineStr">
-        <is>
-          <t>cifra oficial</t>
-        </is>
-      </c>
-      <c r="G267" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="H267" s="3" t="n">
-        <v>25.363</v>
-      </c>
-      <c r="I267" s="3" t="n">
-        <v>-107.551</v>
-      </c>
-      <c r="J267" s="5" t="inlineStr">
-        <is>
-          <t>Badiraguato, Sinaloa</t>
-        </is>
-      </c>
-      <c r="K267" s="5" t="inlineStr">
-        <is>
-          <t>Sebides: más de 3 mil familias desplazadas, concentradas en Badiraguato, Concordia y San Ignacio</t>
-        </is>
-      </c>
-      <c r="L267" s="5" t="inlineStr">
-        <is>
-          <t>La dependencia informó que los casos se concentran en municipios con zonas serranas como Badiraguato, Concordia y San Ignacio, y que también hay desplazamientos por fenómenos naturales y falta de infraestructura. Ubicación aproximada (cabecera municipal).</t>
-        </is>
-      </c>
-      <c r="M267" s="3" t="inlineStr">
-        <is>
-          <t>sebides</t>
-        </is>
-      </c>
-      <c r="N267" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aztecasinaloa.com/noticias/violencia-deja-a-mas-3-mil-familias-desplazadas-en-las-comunidades-serranas-sinaloa</t>
-        </is>
-      </c>
-      <c r="O267" s="3" t="inlineStr">
-        <is>
-          <t>oficial</t>
-        </is>
-      </c>
-      <c r="P267" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="A267" s="6" t="n"/>
+      <c r="B267" s="6" t="n"/>
+      <c r="C267" s="6" t="n"/>
+      <c r="D267" s="7" t="n"/>
+      <c r="E267" s="6" t="n"/>
+      <c r="F267" s="6" t="n"/>
+      <c r="G267" s="6" t="n"/>
+      <c r="H267" s="6" t="n"/>
+      <c r="I267" s="6" t="n"/>
+      <c r="J267" s="6" t="n"/>
+      <c r="K267" s="6" t="n"/>
+      <c r="L267" s="6" t="n"/>
+      <c r="M267" s="6" t="n"/>
+      <c r="N267" s="6" t="n"/>
+      <c r="O267" s="6" t="n"/>
+      <c r="P267" s="6" t="n"/>
     </row>
     <row r="268">
-      <c r="A268" s="3" t="inlineStr">
-        <is>
-          <t>ev-068</t>
-        </is>
-      </c>
-      <c r="B268" s="3" t="inlineStr">
-        <is>
-          <t>periodistas</t>
-        </is>
-      </c>
-      <c r="C268" s="3" t="inlineStr">
-        <is>
-          <t>periodista</t>
-        </is>
-      </c>
-      <c r="D268" s="4" t="inlineStr">
-        <is>
-          <t>asesinato</t>
-        </is>
-      </c>
-      <c r="E268" s="3" t="inlineStr">
-        <is>
-          <t>masculino</t>
-        </is>
-      </c>
-      <c r="F268" s="3" t="inlineStr">
-        <is>
-          <t>desaparición y asesinato de periodista</t>
-        </is>
-      </c>
-      <c r="G268" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="H268" s="3" t="n">
-        <v>17.643</v>
-      </c>
-      <c r="I268" s="3" t="n">
-        <v>-101.552</v>
-      </c>
-      <c r="J268" s="5" t="inlineStr">
-        <is>
-          <t>Zihuatanejo de Azueta, Guerrero</t>
-        </is>
-      </c>
-      <c r="K268" s="5" t="inlineStr">
-        <is>
-          <t>Alex Serna, periodista ambiental, desaparecido el 20 de junio y asesinado</t>
-        </is>
-      </c>
-      <c r="L268" s="5" t="inlineStr">
-        <is>
-          <t>Manuel Alejandro Moreno Serna, periodista ambiental independiente, fue reportado desaparecido el 20 de junio tras denuncias sobre tala y daños en la región del río Salitreras; un audio atribuido a él afirmaba estar secuestrado en represalia. RSF lo registra como asesinado el 3 de julio. Ubicación aproximada (cabecera municipal). Figura como número 179 (Manuel Alejandro Moreno Serna) en el registro de periodistas asesinados de ARTICLE 19.</t>
-        </is>
-      </c>
-      <c r="M268" s="3" t="inlineStr">
-        <is>
-          <t>rsf</t>
-        </is>
-      </c>
-      <c r="N268" s="3" t="inlineStr">
-        <is>
-          <t>https://rsf.org/es/alex-serna-especializado-en-temas-ambientales-es-el-quinto-periodista-asesinado-en-m%C3%A9xico-desde</t>
-        </is>
-      </c>
-      <c r="O268" s="3" t="inlineStr">
-        <is>
-          <t>organización</t>
-        </is>
-      </c>
-      <c r="P268" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="A268" s="6" t="n"/>
+      <c r="B268" s="6" t="n"/>
+      <c r="C268" s="6" t="n"/>
+      <c r="D268" s="7" t="n"/>
+      <c r="E268" s="6" t="n"/>
+      <c r="F268" s="6" t="n"/>
+      <c r="G268" s="6" t="n"/>
+      <c r="H268" s="6" t="n"/>
+      <c r="I268" s="6" t="n"/>
+      <c r="J268" s="6" t="n"/>
+      <c r="K268" s="6" t="n"/>
+      <c r="L268" s="6" t="n"/>
+      <c r="M268" s="6" t="n"/>
+      <c r="N268" s="6" t="n"/>
+      <c r="O268" s="6" t="n"/>
+      <c r="P268" s="6" t="n"/>
     </row>
     <row r="269">
-      <c r="A269" s="3" t="inlineStr">
-        <is>
-          <t>ev-038</t>
-        </is>
-      </c>
-      <c r="B269" s="3" t="inlineStr">
-        <is>
-          <t>desplazamiento</t>
-        </is>
-      </c>
-      <c r="C269" s="3" t="inlineStr"/>
-      <c r="D269" s="4" t="inlineStr"/>
-      <c r="E269" s="3" t="inlineStr"/>
-      <c r="F269" s="3" t="inlineStr">
-        <is>
-          <t>desplazamiento masivo</t>
-        </is>
-      </c>
-      <c r="G269" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="H269" s="3" t="n">
-        <v>18.74</v>
-      </c>
-      <c r="I269" s="3" t="n">
-        <v>-102.788</v>
-      </c>
-      <c r="J269" s="5" t="inlineStr">
-        <is>
-          <t>Franja serrana Apatzingán-Aguililla, Michoacán</t>
-        </is>
-      </c>
-      <c r="K269" s="5" t="inlineStr">
-        <is>
-          <t>Alrededor de 400 personas dejan comunidades entre Apatzingán y Aguililla</t>
-        </is>
-      </c>
-      <c r="L269" s="5" t="inlineStr">
-        <is>
-          <t>El dirigente estatal del PRI afirmó que en el último mes y medio unas 400 personas abandonaron El Aguaje, El Naranjo Viejo, El Naranjo de Chila, Las Bateas y Loma de los Hoyos por la disputa entre grupos criminales. Cifra de un actor político, sin confirmación oficial. Ubicación aproximada (cabecera de Aguililla).</t>
-        </is>
-      </c>
-      <c r="M269" s="3" t="inlineStr">
-        <is>
-          <t>quadratin</t>
-        </is>
-      </c>
-      <c r="N269" s="3" t="inlineStr">
-        <is>
-          <t>https://www.quadratin.com.mx/justicia/suman-400-desplazados-en-apatzingan-y-aguililla-durante-el-ultimo-mes/</t>
-        </is>
-      </c>
-      <c r="O269" s="3" t="inlineStr">
-        <is>
-          <t>prensa</t>
-        </is>
-      </c>
-      <c r="P269" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="A269" s="6" t="n"/>
+      <c r="B269" s="6" t="n"/>
+      <c r="C269" s="6" t="n"/>
+      <c r="D269" s="7" t="n"/>
+      <c r="E269" s="6" t="n"/>
+      <c r="F269" s="6" t="n"/>
+      <c r="G269" s="6" t="n"/>
+      <c r="H269" s="6" t="n"/>
+      <c r="I269" s="6" t="n"/>
+      <c r="J269" s="6" t="n"/>
+      <c r="K269" s="6" t="n"/>
+      <c r="L269" s="6" t="n"/>
+      <c r="M269" s="6" t="n"/>
+      <c r="N269" s="6" t="n"/>
+      <c r="O269" s="6" t="n"/>
+      <c r="P269" s="6" t="n"/>
     </row>
     <row r="270">
-      <c r="A270" s="3" t="inlineStr">
-        <is>
-          <t>ev-039</t>
-        </is>
-      </c>
-      <c r="B270" s="3" t="inlineStr">
-        <is>
-          <t>desplazamiento</t>
-        </is>
-      </c>
-      <c r="C270" s="3" t="inlineStr"/>
-      <c r="D270" s="4" t="inlineStr"/>
-      <c r="E270" s="3" t="inlineStr"/>
-      <c r="F270" s="3" t="inlineStr">
-        <is>
-          <t>desplazamiento masivo</t>
-        </is>
-      </c>
-      <c r="G270" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="H270" s="3" t="n">
-        <v>27.865</v>
-      </c>
-      <c r="I270" s="3" t="n">
-        <v>-108.235</v>
-      </c>
-      <c r="J270" s="5" t="inlineStr">
-        <is>
-          <t>Uruachi y Moris, Chihuahua</t>
-        </is>
-      </c>
-      <c r="K270" s="5" t="inlineStr">
-        <is>
-          <t>Cerca de 10 comunidades indígenas de Moris y Uruachi salen por ataques con explosivos desde drones</t>
-        </is>
-      </c>
-      <c r="L270" s="5" t="inlineStr">
-        <is>
-          <t>Entre junio y julio de 2026 comunidades de Moris y Uruachi abandonaron sus territorios por ataques del grupo Los Salazar, con explosivos lanzados desde drones, según El Diario de Chihuahua. Fecha aproximada. Ubicación aproximada (cabecera de Uruachi).</t>
-        </is>
-      </c>
-      <c r="M270" s="3" t="inlineStr">
-        <is>
-          <t>diariochihuahua</t>
-        </is>
-      </c>
-      <c r="N270" s="3" t="inlineStr">
-        <is>
-          <t>https://www.eldiariodechihuahua.mx/estado/2026/jul/10/desplazo-crimen-a-mas-de-11-mil-en-la-sierra-816155.html</t>
-        </is>
-      </c>
-      <c r="O270" s="3" t="inlineStr">
-        <is>
-          <t>prensa</t>
-        </is>
-      </c>
-      <c r="P270" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="A270" s="6" t="n"/>
+      <c r="B270" s="6" t="n"/>
+      <c r="C270" s="6" t="n"/>
+      <c r="D270" s="7" t="n"/>
+      <c r="E270" s="6" t="n"/>
+      <c r="F270" s="6" t="n"/>
+      <c r="G270" s="6" t="n"/>
+      <c r="H270" s="6" t="n"/>
+      <c r="I270" s="6" t="n"/>
+      <c r="J270" s="6" t="n"/>
+      <c r="K270" s="6" t="n"/>
+      <c r="L270" s="6" t="n"/>
+      <c r="M270" s="6" t="n"/>
+      <c r="N270" s="6" t="n"/>
+      <c r="O270" s="6" t="n"/>
+      <c r="P270" s="6" t="n"/>
     </row>
     <row r="271">
-      <c r="A271" s="3" t="inlineStr">
-        <is>
-          <t>ev-040</t>
-        </is>
-      </c>
-      <c r="B271" s="3" t="inlineStr">
-        <is>
-          <t>desplazamiento</t>
-        </is>
-      </c>
-      <c r="C271" s="3" t="inlineStr"/>
-      <c r="D271" s="4" t="inlineStr"/>
-      <c r="E271" s="3" t="inlineStr"/>
-      <c r="F271" s="3" t="inlineStr">
-        <is>
-          <t>desplazamiento masivo</t>
-        </is>
-      </c>
-      <c r="G271" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="H271" s="3" t="n">
-        <v>26.095</v>
-      </c>
-      <c r="I271" s="3" t="n">
-        <v>-106.965</v>
-      </c>
-      <c r="J271" s="5" t="inlineStr">
-        <is>
-          <t>Cinco Llagas, Guadalupe y Calvo, Chihuahua</t>
-        </is>
-      </c>
-      <c r="K271" s="5" t="inlineStr">
-        <is>
-          <t>Llegan a Chihuahua 17 personas desplazadas de Cinco Llagas</t>
-        </is>
-      </c>
-      <c r="L271" s="5" t="inlineStr">
-        <is>
-          <t>La titular de la Comisión estatal de desplazamiento forzado informó el traslado de familias de Cinco Llagas para recibir atención, mientras comunidades de la sierra permanecen sin abasto de productos básicos por la inseguridad. Ubicación aproximada (cabecera municipal).</t>
-        </is>
-      </c>
-      <c r="M271" s="3" t="inlineStr">
-        <is>
-          <t>heraldochihuahua</t>
-        </is>
-      </c>
-      <c r="N271" s="3" t="inlineStr">
-        <is>
-          <t>https://oem.com.mx/elheraldodechihuahua/local/llegan-a-chihuahua-17-desplazados-por-violencia-comunidades-de-guadalupe-y-calvo-enfrentan-crisis-por-falta-de-alimentos-31001267</t>
-        </is>
-      </c>
-      <c r="O271" s="3" t="inlineStr">
-        <is>
-          <t>prensa</t>
-        </is>
-      </c>
-      <c r="P271" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="A271" s="6" t="n"/>
+      <c r="B271" s="6" t="n"/>
+      <c r="C271" s="6" t="n"/>
+      <c r="D271" s="7" t="n"/>
+      <c r="E271" s="6" t="n"/>
+      <c r="F271" s="6" t="n"/>
+      <c r="G271" s="6" t="n"/>
+      <c r="H271" s="6" t="n"/>
+      <c r="I271" s="6" t="n"/>
+      <c r="J271" s="6" t="n"/>
+      <c r="K271" s="6" t="n"/>
+      <c r="L271" s="6" t="n"/>
+      <c r="M271" s="6" t="n"/>
+      <c r="N271" s="6" t="n"/>
+      <c r="O271" s="6" t="n"/>
+      <c r="P271" s="6" t="n"/>
     </row>
     <row r="272">
-      <c r="A272" s="3" t="inlineStr">
-        <is>
-          <t>ev-069</t>
-        </is>
-      </c>
-      <c r="B272" s="3" t="inlineStr">
-        <is>
-          <t>periodistas</t>
-        </is>
-      </c>
-      <c r="C272" s="3" t="inlineStr">
-        <is>
-          <t>periodista</t>
-        </is>
-      </c>
-      <c r="D272" s="4" t="inlineStr">
-        <is>
-          <t>asesinato</t>
-        </is>
-      </c>
-      <c r="E272" s="3" t="inlineStr">
-        <is>
-          <t>masculino</t>
-        </is>
-      </c>
-      <c r="F272" s="3" t="inlineStr">
-        <is>
-          <t>asesinato de periodista</t>
-        </is>
-      </c>
-      <c r="G272" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="H272" s="3" t="n">
-        <v>19.284</v>
-      </c>
-      <c r="I272" s="3" t="n">
-        <v>-98.43899999999999</v>
-      </c>
-      <c r="J272" s="5" t="inlineStr">
-        <is>
-          <t>San Martín Texmelucan, Puebla</t>
-        </is>
-      </c>
-      <c r="K272" s="5" t="inlineStr">
-        <is>
-          <t>Asesinato de Josué Martínez Contreras, director de Noticias San Martín Texmelucan</t>
-        </is>
-      </c>
-      <c r="L272" s="5" t="inlineStr">
-        <is>
-          <t>Asesinado a tiros el 16 de julio. Una ex autoridad local señalada por amenazas previas fue detenida dos días después por otro delito. ARTICLE 19 documentó 39 agresiones en Puebla en 2025, la segunda cifra del país. Ubicación aproximada (cabecera municipal). Figura como número 180 en el registro de periodistas asesinados de ARTICLE 19.</t>
-        </is>
-      </c>
-      <c r="M272" s="3" t="inlineStr">
-        <is>
-          <t>rsf</t>
-        </is>
-      </c>
-      <c r="N272" s="3" t="inlineStr">
-        <is>
-          <t>https://rsf.org/es/m%C3%A9xico-sexto-periodista-asesinado-en-2026-el-gobierno-debe-actuar-con-urgencia-frente-la-violencia</t>
-        </is>
-      </c>
-      <c r="O272" s="3" t="inlineStr">
-        <is>
-          <t>organización</t>
-        </is>
-      </c>
-      <c r="P272" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="A272" s="6" t="n"/>
+      <c r="B272" s="6" t="n"/>
+      <c r="C272" s="6" t="n"/>
+      <c r="D272" s="7" t="n"/>
+      <c r="E272" s="6" t="n"/>
+      <c r="F272" s="6" t="n"/>
+      <c r="G272" s="6" t="n"/>
+      <c r="H272" s="6" t="n"/>
+      <c r="I272" s="6" t="n"/>
+      <c r="J272" s="6" t="n"/>
+      <c r="K272" s="6" t="n"/>
+      <c r="L272" s="6" t="n"/>
+      <c r="M272" s="6" t="n"/>
+      <c r="N272" s="6" t="n"/>
+      <c r="O272" s="6" t="n"/>
+      <c r="P272" s="6" t="n"/>
     </row>
     <row r="273">
-      <c r="A273" s="3" t="inlineStr">
-        <is>
-          <t>ev-070</t>
-        </is>
-      </c>
-      <c r="B273" s="3" t="inlineStr">
-        <is>
-          <t>periodistas</t>
-        </is>
-      </c>
-      <c r="C273" s="3" t="inlineStr">
-        <is>
-          <t>periodista</t>
-        </is>
-      </c>
-      <c r="D273" s="4" t="inlineStr">
-        <is>
-          <t>ataque_medio</t>
-        </is>
-      </c>
-      <c r="E273" s="3" t="inlineStr">
-        <is>
-          <t>masculino</t>
-        </is>
-      </c>
-      <c r="F273" s="3" t="inlineStr">
-        <is>
-          <t>ataque a medio</t>
-        </is>
-      </c>
-      <c r="G273" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="H273" s="3" t="n">
-        <v>24.809</v>
-      </c>
-      <c r="I273" s="3" t="n">
-        <v>-107.394</v>
-      </c>
-      <c r="J273" s="5" t="inlineStr">
-        <is>
-          <t>Culiacán, Sinaloa</t>
-        </is>
-      </c>
-      <c r="K273" s="5" t="inlineStr">
-        <is>
-          <t>Ataque armado contra domicilio vinculado al director de Grupo Adiscusión</t>
-        </is>
-      </c>
-      <c r="L273" s="5" t="inlineStr">
-        <is>
-          <t>El Instituto de Protección condenó el ataque y pidió investigar la posible relación con la actividad periodística de la víctima. Ubicación aproximada (cabecera municipal).</t>
-        </is>
-      </c>
-      <c r="M273" s="3" t="inlineStr">
-        <is>
-          <t>noroeste</t>
-        </is>
-      </c>
-      <c r="N273" s="3" t="inlineStr">
-        <is>
-          <t>https://www.noroeste.com.mx/culiacan/instituto-de-proteccion-a-periodistas-condena-ataque-contra-domicilio-vinculado-a-director-de-adiscusion-HP24187055</t>
-        </is>
-      </c>
-      <c r="O273" s="3" t="inlineStr">
-        <is>
-          <t>prensa</t>
-        </is>
-      </c>
-      <c r="P273" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="A273" s="6" t="n"/>
+      <c r="B273" s="6" t="n"/>
+      <c r="C273" s="6" t="n"/>
+      <c r="D273" s="7" t="n"/>
+      <c r="E273" s="6" t="n"/>
+      <c r="F273" s="6" t="n"/>
+      <c r="G273" s="6" t="n"/>
+      <c r="H273" s="6" t="n"/>
+      <c r="I273" s="6" t="n"/>
+      <c r="J273" s="6" t="n"/>
+      <c r="K273" s="6" t="n"/>
+      <c r="L273" s="6" t="n"/>
+      <c r="M273" s="6" t="n"/>
+      <c r="N273" s="6" t="n"/>
+      <c r="O273" s="6" t="n"/>
+      <c r="P273" s="6" t="n"/>
     </row>
     <row r="274">
-      <c r="A274" s="3" t="inlineStr">
-        <is>
-          <t>ev-071</t>
-        </is>
-      </c>
-      <c r="B274" s="3" t="inlineStr">
-        <is>
-          <t>periodistas</t>
-        </is>
-      </c>
-      <c r="C274" s="3" t="inlineStr">
-        <is>
-          <t>periodista</t>
-        </is>
-      </c>
-      <c r="D274" s="4" t="inlineStr">
-        <is>
-          <t>asesinato</t>
-        </is>
-      </c>
-      <c r="E274" s="3" t="inlineStr">
-        <is>
-          <t>masculino</t>
-        </is>
-      </c>
-      <c r="F274" s="3" t="inlineStr">
-        <is>
-          <t>asesinato de periodista</t>
-        </is>
-      </c>
-      <c r="G274" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="H274" s="3" t="n">
-        <v>17.146</v>
-      </c>
-      <c r="I274" s="3" t="n">
-        <v>-96.752</v>
-      </c>
-      <c r="J274" s="5" t="inlineStr">
-        <is>
-          <t>San Pablo Etla, Oaxaca</t>
-        </is>
-      </c>
-      <c r="K274" s="5" t="inlineStr">
-        <is>
-          <t>Asesinato de Francisco Alejandro Leyva Aguilar, periodista y articulista</t>
-        </is>
-      </c>
-      <c r="L274" s="5" t="inlineStr">
-        <is>
-          <t>Asesinado a tiros el 22 de julio; un año antes había denunciado oficialmente amenazas de muerte. Séptimo periodista asesinado en 2026 según RSF, sexto según CPJ. Ubicación aproximada (cabecera municipal). Figura como número 181 en el registro de periodistas asesinados de ARTICLE 19.</t>
-        </is>
-      </c>
-      <c r="M274" s="3" t="inlineStr">
-        <is>
-          <t>rsf</t>
-        </is>
-      </c>
-      <c r="N274" s="3" t="inlineStr">
-        <is>
-          <t>https://rsf.org/es/m%C3%A9xico-el-asesinato-de-francisco-alejandro-leyva-aguilar-s%C3%A9ptimo-periodista-asesinado-en-2026</t>
-        </is>
-      </c>
-      <c r="O274" s="3" t="inlineStr">
-        <is>
-          <t>organización</t>
-        </is>
-      </c>
-      <c r="P274" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="A274" s="6" t="n"/>
+      <c r="B274" s="6" t="n"/>
+      <c r="C274" s="6" t="n"/>
+      <c r="D274" s="7" t="n"/>
+      <c r="E274" s="6" t="n"/>
+      <c r="F274" s="6" t="n"/>
+      <c r="G274" s="6" t="n"/>
+      <c r="H274" s="6" t="n"/>
+      <c r="I274" s="6" t="n"/>
+      <c r="J274" s="6" t="n"/>
+      <c r="K274" s="6" t="n"/>
+      <c r="L274" s="6" t="n"/>
+      <c r="M274" s="6" t="n"/>
+      <c r="N274" s="6" t="n"/>
+      <c r="O274" s="6" t="n"/>
+      <c r="P274" s="6" t="n"/>
     </row>
     <row r="275">
-      <c r="A275" s="3" t="inlineStr">
-        <is>
-          <t>ev-041</t>
-        </is>
-      </c>
-      <c r="B275" s="3" t="inlineStr">
-        <is>
-          <t>desplazamiento</t>
-        </is>
-      </c>
-      <c r="C275" s="3" t="inlineStr"/>
-      <c r="D275" s="4" t="inlineStr"/>
-      <c r="E275" s="3" t="inlineStr"/>
-      <c r="F275" s="3" t="inlineStr">
-        <is>
-          <t>cruce de frontera</t>
-        </is>
-      </c>
-      <c r="G275" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="H275" s="3" t="n">
-        <v>15.664</v>
-      </c>
-      <c r="I275" s="3" t="n">
-        <v>-92.14</v>
-      </c>
-      <c r="J275" s="5" t="inlineStr">
-        <is>
-          <t>Frontera Comalapa, Chiapas</t>
-        </is>
-      </c>
-      <c r="K275" s="5" t="inlineStr">
-        <is>
-          <t>60 personas huyen de Frontera Comalapa a Huehuetenango, Guatemala</t>
-        </is>
-      </c>
-      <c r="L275" s="5" t="inlineStr">
-        <is>
-          <t>El Procurador de Derechos Humanos de Guatemala informó del ingreso de al menos 60 personas mexicanas desplazadas a la aldea Guaila, La Democracia, Huehuetenango, tras el asesinato del comisariado ejidal de El Sabinalito dos días antes. Guatemala envió ayuda humanitaria. Ubicación aproximada (cabecera municipal).</t>
-        </is>
-      </c>
-      <c r="M275" s="3" t="inlineStr">
-        <is>
-          <t>aztecachiapas</t>
-        </is>
-      </c>
-      <c r="N275" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aztecachiapas.com/noticias/familias-de-chiapas-buscan-refugio-en-guatemala-por-la-violencia/</t>
-        </is>
-      </c>
-      <c r="O275" s="3" t="inlineStr">
-        <is>
-          <t>prensa</t>
-        </is>
-      </c>
-      <c r="P275" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="A275" s="6" t="n"/>
+      <c r="B275" s="6" t="n"/>
+      <c r="C275" s="6" t="n"/>
+      <c r="D275" s="7" t="n"/>
+      <c r="E275" s="6" t="n"/>
+      <c r="F275" s="6" t="n"/>
+      <c r="G275" s="6" t="n"/>
+      <c r="H275" s="6" t="n"/>
+      <c r="I275" s="6" t="n"/>
+      <c r="J275" s="6" t="n"/>
+      <c r="K275" s="6" t="n"/>
+      <c r="L275" s="6" t="n"/>
+      <c r="M275" s="6" t="n"/>
+      <c r="N275" s="6" t="n"/>
+      <c r="O275" s="6" t="n"/>
+      <c r="P275" s="6" t="n"/>
     </row>
     <row r="276">
-      <c r="A276" s="3" t="inlineStr">
-        <is>
-          <t>ev-042</t>
-        </is>
-      </c>
-      <c r="B276" s="3" t="inlineStr">
-        <is>
-          <t>desplazamiento</t>
-        </is>
-      </c>
-      <c r="C276" s="3" t="inlineStr"/>
-      <c r="D276" s="4" t="inlineStr"/>
-      <c r="E276" s="3" t="inlineStr"/>
-      <c r="F276" s="3" t="inlineStr">
-        <is>
-          <t>informe</t>
-        </is>
-      </c>
-      <c r="G276" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="H276" s="3" t="n">
-        <v>26.095</v>
-      </c>
-      <c r="I276" s="3" t="n">
-        <v>-106.965</v>
-      </c>
-      <c r="J276" s="5" t="inlineStr">
-        <is>
-          <t>Guadalupe y Calvo, Chihuahua</t>
-        </is>
-      </c>
-      <c r="K276" s="5" t="inlineStr">
-        <is>
-          <t>Misión Civil de Observación: 4 mil 492 personas desplazadas de la sierra Tarahumara en 2025</t>
-        </is>
-      </c>
-      <c r="L276" s="5" t="inlineStr">
-        <is>
-          <t>El informe de la Misión Civil de Observación (Red TDT, Tlachinollan, Serapaz) documentó en mayo de 2026 a unas 200 personas desplazadas en Parral, Delicias y Chihuahua, provenientes de Atascaderos, Coloradas de la Virgen, La Sierrita, Uruachi y Guazapares, además de Tamazula (Durango) y San Miguel (Sinaloa). Entre 2023 y septiembre de 2025 hubo 83 denuncias por desplazamiento ante la fiscalía estatal y dos sentencias. Cifra regional ubicada en el municipio más afectado.</t>
-        </is>
-      </c>
-      <c r="M276" s="3" t="inlineStr">
-        <is>
-          <t>mco-chihuahua</t>
-        </is>
-      </c>
-      <c r="N276" s="3" t="inlineStr">
-        <is>
-          <t>https://www.jornada.com.mx/2026/08/12/estados/026n1est</t>
-        </is>
-      </c>
-      <c r="O276" s="3" t="inlineStr">
-        <is>
-          <t>organización</t>
-        </is>
-      </c>
-      <c r="P276" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="A276" s="6" t="n"/>
+      <c r="B276" s="6" t="n"/>
+      <c r="C276" s="6" t="n"/>
+      <c r="D276" s="7" t="n"/>
+      <c r="E276" s="6" t="n"/>
+      <c r="F276" s="6" t="n"/>
+      <c r="G276" s="6" t="n"/>
+      <c r="H276" s="6" t="n"/>
+      <c r="I276" s="6" t="n"/>
+      <c r="J276" s="6" t="n"/>
+      <c r="K276" s="6" t="n"/>
+      <c r="L276" s="6" t="n"/>
+      <c r="M276" s="6" t="n"/>
+      <c r="N276" s="6" t="n"/>
+      <c r="O276" s="6" t="n"/>
+      <c r="P276" s="6" t="n"/>
     </row>
     <row r="277">
-      <c r="A277" s="3" t="inlineStr">
-        <is>
-          <t>ev-072</t>
-        </is>
-      </c>
-      <c r="B277" s="3" t="inlineStr">
-        <is>
-          <t>periodistas</t>
-        </is>
-      </c>
-      <c r="C277" s="3" t="inlineStr">
-        <is>
-          <t>ambos</t>
-        </is>
-      </c>
-      <c r="D277" s="4" t="inlineStr">
-        <is>
-          <t>informe</t>
-        </is>
-      </c>
-      <c r="E277" s="3" t="inlineStr">
-        <is>
-          <t>no aplica</t>
-        </is>
-      </c>
-      <c r="F277" s="3" t="inlineStr">
-        <is>
-          <t>informe</t>
-        </is>
-      </c>
-      <c r="G277" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="H277" s="3" t="n">
-        <v>19.432</v>
-      </c>
-      <c r="I277" s="3" t="n">
-        <v>-99.133</v>
-      </c>
-      <c r="J277" s="5" t="inlineStr">
-        <is>
-          <t>Ciudad de México</t>
-        </is>
-      </c>
-      <c r="K277" s="5" t="inlineStr">
-        <is>
-          <t>Espacio OSC: el Mecanismo rechazó 70 por ciento de las solicitudes de protección entre 2024 y junio de 2026</t>
-        </is>
-      </c>
-      <c r="L277" s="5" t="inlineStr">
-        <is>
-          <t>De 409 solicitudes recibidas, 289 fueron rechazadas; las organizaciones señalan que algunas personas han perdido la vida con medidas o esperando incorporación. Al 31 de mayo de 2026 el Mecanismo protegía a 2 mil 20 personas (690 periodistas y mil 330 defensoras). Cifra nacional ubicada en la capital.</t>
-        </is>
-      </c>
-      <c r="M277" s="3" t="inlineStr">
-        <is>
-          <t>espacio-osc</t>
-        </is>
-      </c>
-      <c r="N277" s="3" t="inlineStr">
-        <is>
-          <t>https://www.proceso.com.mx/nacional/2026/9/4/osc-urge-al-gobierno-federal-a-fortalecer-mecanismo-de-proteccion-para-defensores-y-periodistas-379345.html</t>
-        </is>
-      </c>
-      <c r="O277" s="3" t="inlineStr">
-        <is>
-          <t>organización</t>
-        </is>
-      </c>
-      <c r="P277" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="A277" s="6" t="n"/>
+      <c r="B277" s="6" t="n"/>
+      <c r="C277" s="6" t="n"/>
+      <c r="D277" s="7" t="n"/>
+      <c r="E277" s="6" t="n"/>
+      <c r="F277" s="6" t="n"/>
+      <c r="G277" s="6" t="n"/>
+      <c r="H277" s="6" t="n"/>
+      <c r="I277" s="6" t="n"/>
+      <c r="J277" s="6" t="n"/>
+      <c r="K277" s="6" t="n"/>
+      <c r="L277" s="6" t="n"/>
+      <c r="M277" s="6" t="n"/>
+      <c r="N277" s="6" t="n"/>
+      <c r="O277" s="6" t="n"/>
+      <c r="P277" s="6" t="n"/>
     </row>
     <row r="278">
-      <c r="A278" s="3" t="inlineStr">
-        <is>
-          <t>ev-043</t>
-        </is>
-      </c>
-      <c r="B278" s="3" t="inlineStr">
-        <is>
-          <t>desplazamiento</t>
-        </is>
-      </c>
-      <c r="C278" s="3" t="inlineStr"/>
-      <c r="D278" s="4" t="inlineStr"/>
-      <c r="E278" s="3" t="inlineStr"/>
-      <c r="F278" s="3" t="inlineStr">
-        <is>
-          <t>informe</t>
-        </is>
-      </c>
-      <c r="G278" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="H278" s="3" t="n">
-        <v>16.753</v>
-      </c>
-      <c r="I278" s="3" t="n">
-        <v>-93.116</v>
-      </c>
-      <c r="J278" s="5" t="inlineStr">
-        <is>
-          <t>Tuxtla Gutiérrez, Chiapas</t>
-        </is>
-      </c>
-      <c r="K278" s="5" t="inlineStr">
-        <is>
-          <t>Frayba documenta 24 mil 290 personas desplazadas en Chiapas entre 2021 y octubre de 2025</t>
-        </is>
-      </c>
-      <c r="L278" s="5" t="inlineStr">
-        <is>
-          <t>El informe Chiapas, la paz pendiente (mayo de 2026) contabiliza 24 mil 290 personas desplazadas en Pantelhó, Frontera Comalapa, Chicomuselo, Oxchuc, Las Margaritas, Huixtán, Chenalhó, Ocosingo, La Trinitaria, Socoltenango, La Concordia, Bella Vista y Tila. El gobierno estatal sostiene que 95 por ciento ha regresado; el Frayba advierte que los retornos no siempre son duraderos. Cifra estatal ubicada en la capital.</t>
-        </is>
-      </c>
-      <c r="M278" s="3" t="inlineStr">
-        <is>
-          <t>frayba</t>
-        </is>
-      </c>
-      <c r="N278" s="3" t="inlineStr">
-        <is>
-          <t>https://www.jornada.com.mx/noticia/2026/05/26/opinion/desplazados-chiapas-la-vida-y-el-miedo</t>
-        </is>
-      </c>
-      <c r="O278" s="3" t="inlineStr">
-        <is>
-          <t>organización</t>
-        </is>
-      </c>
-      <c r="P278" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="A278" s="6" t="n"/>
+      <c r="B278" s="6" t="n"/>
+      <c r="C278" s="6" t="n"/>
+      <c r="D278" s="7" t="n"/>
+      <c r="E278" s="6" t="n"/>
+      <c r="F278" s="6" t="n"/>
+      <c r="G278" s="6" t="n"/>
+      <c r="H278" s="6" t="n"/>
+      <c r="I278" s="6" t="n"/>
+      <c r="J278" s="6" t="n"/>
+      <c r="K278" s="6" t="n"/>
+      <c r="L278" s="6" t="n"/>
+      <c r="M278" s="6" t="n"/>
+      <c r="N278" s="6" t="n"/>
+      <c r="O278" s="6" t="n"/>
+      <c r="P278" s="6" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="6" t="n"/>
@@ -34713,7 +32857,7 @@
       <formula1>=catalogos!$B$2:$B$6</formula1>
     </dataValidation>
     <dataValidation sqref="M2:M1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Valor no permitido" type="list">
-      <formula1>=catalogos!$C$2:$C$64</formula1>
+      <formula1>=catalogos!$C$2:$C$42</formula1>
     </dataValidation>
     <dataValidation sqref="P2:P1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Valor no permitido" type="list">
       <formula1>"si,no"</formula1>
@@ -34737,7 +32881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -34805,12 +32949,12 @@
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t>upm</t>
+          <t>mecanismo</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>Unidad de Política Migratoria (Segob), boletines estadísticos</t>
+          <t>Mecanismo de Protección para Personas Defensoras de DDHH y Periodistas (Segob)</t>
         </is>
       </c>
       <c r="E2" s="9" t="inlineStr">
@@ -34847,17 +32991,17 @@
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>comar</t>
+          <t>article19</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>COMAR, estadísticas de solicitudes de refugio</t>
+          <t>ARTICLE 19 México y Centroamérica, informe anual</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>oficial</t>
+          <t>organizacion</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
@@ -34889,12 +33033,12 @@
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>cbp</t>
+          <t>feadle</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>U.S. CBP, Southwest Land Border Encounters</t>
+          <t>FEADLE (FGR), informes estadísticos</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
@@ -34931,12 +33075,12 @@
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>mmp</t>
+          <t>cpj</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>OIM, Missing Migrants Project</t>
+          <t>Committee to Protect Journalists, base de datos</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -34969,12 +33113,12 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>redodem</t>
+          <t>cerezo</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>REDODEM, informes anuales de albergues</t>
+          <t>Comité Cerezo México y Red TDT, informes sobre personas defensoras</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
@@ -34995,17 +33139,17 @@
       <c r="B7" s="9" t="n"/>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>emif</t>
+          <t>globalwitness</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>EMIF Norte y Sur (El Colef)</t>
+          <t>Global Witness, personas defensoras de la tierra y el ambiente</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>oficial</t>
+          <t>organizacion</t>
         </is>
       </c>
       <c r="F7" s="9" t="n"/>
@@ -35021,12 +33165,12 @@
       <c r="B8" s="9" t="n"/>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>inegi-censo</t>
+          <t>conapo</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>INEGI, Censo 2020, causa de la migración interna</t>
+          <t>CONAPO, Proyecciones de la Población de México y de las Entidades Federativas (base 2020)</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
@@ -35047,17 +33191,17 @@
       <c r="B9" s="9" t="n"/>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>cmdpdh</t>
+          <t>infobae</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>CMDPDH, episodios de desplazamiento interno forzado masivo</t>
+          <t>Infobae México</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>organizacion</t>
+          <t>prensa</t>
         </is>
       </c>
       <c r="F9" s="9" t="n"/>
@@ -35073,17 +33217,17 @@
       <c r="B10" s="9" t="n"/>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>idmc</t>
+          <t>jornada</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>IDMC, Global Internal Displacement Database</t>
+          <t>La Jornada</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>organizacion</t>
+          <t>prensa</t>
         </is>
       </c>
       <c r="F10" s="9" t="n"/>
@@ -35095,17 +33239,17 @@
       <c r="B11" s="9" t="n"/>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>cndh-dfi</t>
+          <t>proceso</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>CNDH, informes sobre desplazamiento forzado interno</t>
+          <t>Proceso</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>oficial</t>
+          <t>prensa</t>
         </is>
       </c>
       <c r="F11" s="9" t="n"/>
@@ -35117,17 +33261,17 @@
       <c r="B12" s="9" t="n"/>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>rnpdno</t>
+          <t>sillarota</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>RNPDNO, Comisión Nacional de Búsqueda</t>
+          <t>La Silla Rota</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>oficial</t>
+          <t>prensa</t>
         </is>
       </c>
       <c r="F12" s="9" t="n"/>
@@ -35139,17 +33283,17 @@
       <c r="B13" s="9" t="n"/>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>fosas-quinto</t>
+          <t>riodoce</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>A dónde van los desaparecidos (Quinto Elemento Lab), fosas clandestinas</t>
+          <t>Ríodoce (Culiacán)</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>organizacion</t>
+          <t>prensa</t>
         </is>
       </c>
       <c r="F13" s="9" t="n"/>
@@ -35161,17 +33305,17 @@
       <c r="B14" s="9" t="n"/>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>ced-onu</t>
+          <t>noroeste</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>Comité contra la Desaparición Forzada (ONU), informe de visita a México</t>
+          <t>Noroeste (Sinaloa)</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>organizacion</t>
+          <t>prensa</t>
         </is>
       </c>
       <c r="F14" s="9" t="n"/>
@@ -35183,17 +33327,17 @@
       <c r="B15" s="9" t="n"/>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>ceb-sin</t>
+          <t>lineadirecta</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>Comisión Estatal de Búsqueda de Sinaloa y colectivos de búsqueda</t>
+          <t>Línea Directa (Sinaloa)</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>campo</t>
+          <t>prensa</t>
         </is>
       </c>
       <c r="F15" s="9" t="n"/>
@@ -35205,17 +33349,17 @@
       <c r="B16" s="9" t="n"/>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>mecanismo</t>
+          <t>luznoticias</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Mecanismo de Protección para Personas Defensoras de DDHH y Periodistas (Segob)</t>
+          <t>Luz Noticias (Sinaloa)</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>oficial</t>
+          <t>prensa</t>
         </is>
       </c>
       <c r="F16" s="9" t="n"/>
@@ -35227,17 +33371,17 @@
       <c r="B17" s="9" t="n"/>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>article19</t>
+          <t>aztecasinaloa</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>ARTICLE 19 México y Centroamérica, informe anual</t>
+          <t>TV Azteca Sinaloa</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>organizacion</t>
+          <t>prensa</t>
         </is>
       </c>
       <c r="F17" s="9" t="n"/>
@@ -35249,17 +33393,17 @@
       <c r="B18" s="9" t="n"/>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>feadle</t>
+          <t>aztecachiapas</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>FEADLE (FGR), informes estadísticos</t>
+          <t>TV Azteca Chiapas</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>oficial</t>
+          <t>prensa</t>
         </is>
       </c>
       <c r="F18" s="9" t="n"/>
@@ -35271,17 +33415,17 @@
       <c r="B19" s="9" t="n"/>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>cpj</t>
+          <t>diariochihuahua</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Committee to Protect Journalists, base de datos</t>
+          <t>El Diario de Chihuahua</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>organizacion</t>
+          <t>prensa</t>
         </is>
       </c>
       <c r="F19" s="9" t="n"/>
@@ -35293,17 +33437,17 @@
       <c r="B20" s="9" t="n"/>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>cerezo</t>
+          <t>heraldochihuahua</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Comité Cerezo México y Red TDT, informes sobre personas defensoras</t>
+          <t>El Heraldo de Chihuahua</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>organizacion</t>
+          <t>prensa</t>
         </is>
       </c>
       <c r="F20" s="9" t="n"/>
@@ -35315,17 +33459,17 @@
       <c r="B21" s="9" t="n"/>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>globalwitness</t>
+          <t>elimparcial</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Global Witness, personas defensoras de la tierra y el ambiente</t>
+          <t>El Imparcial</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>organizacion</t>
+          <t>prensa</t>
         </is>
       </c>
       <c r="F21" s="9" t="n"/>
@@ -35337,17 +33481,17 @@
       <c r="B22" s="9" t="n"/>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>sesnsp</t>
+          <t>meganoticias</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>SESNSP, incidencia delictiva del fuero común</t>
+          <t>Meganoticias</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>oficial</t>
+          <t>prensa</t>
         </is>
       </c>
       <c r="F22" s="9" t="n"/>
@@ -35359,17 +33503,17 @@
       <c r="B23" s="9" t="n"/>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>conapo</t>
+          <t>latinus</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>CONAPO, Proyecciones de la Población de México y de las Entidades Federativas (base 2020)</t>
+          <t>Latinus</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>oficial</t>
+          <t>prensa</t>
         </is>
       </c>
       <c r="F23" s="9" t="n"/>
@@ -35381,12 +33525,12 @@
       <c r="B24" s="9" t="n"/>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>prensa-local</t>
+          <t>milenio</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Prensa local (Noroeste, Riodoce, El Sol de Mazatlán, Línea Directa) y nacional</t>
+          <t>Milenio</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
@@ -35403,17 +33547,17 @@
       <c r="B25" s="9" t="n"/>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>sebides</t>
+          <t>quadratin</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Sebides Sinaloa (Secretaría de Bienestar y Desarrollo Sustentable), padrón de desplazados</t>
+          <t>Quadratín Michoacán</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>oficial</t>
+          <t>prensa</t>
         </is>
       </c>
       <c r="F25" s="9" t="n"/>
@@ -35425,17 +33569,17 @@
       <c r="B26" s="9" t="n"/>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>frayba</t>
+          <t>elfinanciero</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Centro de Derechos Humanos Fray Bartolomé de Las Casas (Frayba), informes sobre Chiapas</t>
+          <t>El Financiero</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>organizacion</t>
+          <t>prensa</t>
         </is>
       </c>
       <c r="F26" s="9" t="n"/>
@@ -35447,17 +33591,17 @@
       <c r="B27" s="9" t="n"/>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>ibero-pdh</t>
+          <t>expansion</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Programa de Derechos Humanos, Universidad Iberoamericana, monitoreo de desplazamiento interno</t>
+          <t>Expansión Política</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>organizacion</t>
+          <t>prensa</t>
         </is>
       </c>
       <c r="F27" s="9" t="n"/>
@@ -35469,17 +33613,17 @@
       <c r="B28" s="9" t="n"/>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>mco-chihuahua</t>
+          <t>unotv</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Misión Civil de Observación sobre desplazamiento forzado en Chihuahua (Red TDT, Tlachinollan, Serapaz)</t>
+          <t>UnoTV</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>organizacion</t>
+          <t>prensa</t>
         </is>
       </c>
       <c r="F28" s="9" t="n"/>
@@ -35491,17 +33635,17 @@
       <c r="B29" s="9" t="n"/>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>oshra</t>
+          <t>revistaespejo</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Observatorio de Seguridad Humana de la Región Apatzingán</t>
+          <t>Revista Espejo (Sinaloa)</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>organizacion</t>
+          <t>prensa</t>
         </is>
       </c>
       <c r="F29" s="9" t="n"/>
@@ -35513,17 +33657,17 @@
       <c r="B30" s="9" t="n"/>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>inegi-eic</t>
+          <t>razon</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>INEGI, Encuesta Intercensal 2025, desplazamiento por inseguridad o violencia</t>
+          <t>La Razón de México</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>oficial</t>
+          <t>prensa</t>
         </is>
       </c>
       <c r="F30" s="9" t="n"/>
@@ -35535,17 +33679,17 @@
       <c r="B31" s="9" t="n"/>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>infobae</t>
+          <t>rsf</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>Infobae México</t>
+          <t>Reporteros Sin Fronteras (RSF)</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>prensa</t>
+          <t>organizacion</t>
         </is>
       </c>
       <c r="F31" s="9" t="n"/>
@@ -35557,17 +33701,17 @@
       <c r="B32" s="9" t="n"/>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>jornada</t>
+          <t>instituto-sinaloa</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>La Jornada</t>
+          <t>Instituto para la Protección de Personas Defensoras de Derechos Humanos y Periodistas de Sinaloa</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>prensa</t>
+          <t>oficial</t>
         </is>
       </c>
       <c r="F32" s="9" t="n"/>
@@ -35579,17 +33723,17 @@
       <c r="B33" s="9" t="n"/>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>proceso</t>
+          <t>espacio-osc</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>Proceso</t>
+          <t>Espacio OSC para la Protección de Personas Defensoras y Periodistas</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>prensa</t>
+          <t>organizacion</t>
         </is>
       </c>
       <c r="F33" s="9" t="n"/>
@@ -35601,17 +33745,17 @@
       <c r="B34" s="9" t="n"/>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>sillarota</t>
+          <t>cemda</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>La Silla Rota</t>
+          <t>Centro Mexicano de Derecho Ambiental (CEMDA), informe sobre personas defensoras ambientales</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>prensa</t>
+          <t>organizacion</t>
         </is>
       </c>
       <c r="F34" s="9" t="n"/>
@@ -35623,17 +33767,17 @@
       <c r="B35" s="9" t="n"/>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>riodoce</t>
+          <t>asociacion-7-junio</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>Ríodoce (Culiacán)</t>
+          <t>Asociación de Periodistas y Comunicadores 7 de Junio (Sinaloa)</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>prensa</t>
+          <t>organizacion</t>
         </is>
       </c>
       <c r="F35" s="9" t="n"/>
@@ -35645,12 +33789,12 @@
       <c r="B36" s="9" t="n"/>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>noroeste</t>
+          <t>excelsior</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>Noroeste (Sinaloa)</t>
+          <t>Excélsior</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
@@ -35667,12 +33811,12 @@
       <c r="B37" s="9" t="n"/>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>lineadirecta</t>
+          <t>nmas</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Línea Directa (Sinaloa)</t>
+          <t>N+ (Televisa)</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
@@ -35689,12 +33833,12 @@
       <c r="B38" s="9" t="n"/>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>luznoticias</t>
+          <t>grupoanimal</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Luz Noticias (Sinaloa)</t>
+          <t>Animal Político (Grupo Animal)</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
@@ -35711,12 +33855,12 @@
       <c r="B39" s="9" t="n"/>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>aztecasinaloa</t>
+          <t>altavoz</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>TV Azteca Sinaloa</t>
+          <t>Noticiero Altavoz (Sinaloa)</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
@@ -35733,12 +33877,12 @@
       <c r="B40" s="9" t="n"/>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>aztecachiapas</t>
+          <t>sectorprimario</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>TV Azteca Chiapas</t>
+          <t>Sector Primario Informativo (Sinaloa)</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
@@ -35755,17 +33899,17 @@
       <c r="B41" s="9" t="n"/>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>diariochihuahua</t>
+          <t>ishr</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>El Diario de Chihuahua</t>
+          <t>International Service for Human Rights (ISHR), Protección nacional en México</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>prensa</t>
+          <t>organizacion</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -35777,506 +33921,22 @@
       <c r="B42" s="9" t="n"/>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>heraldochihuahua</t>
+          <t>inegi-censos</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>El Heraldo de Chihuahua</t>
+          <t>INEGI, Censos y Conteos de Población y Vivienda (1990-2020) y Encuesta Intercensal 2015</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
         <is>
-          <t>prensa</t>
+          <t>oficial</t>
         </is>
       </c>
       <c r="F42" s="9" t="n"/>
       <c r="G42" s="9" t="n"/>
       <c r="H42" s="9" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="9" t="n"/>
-      <c r="B43" s="9" t="n"/>
-      <c r="C43" s="9" t="inlineStr">
-        <is>
-          <t>elimparcial</t>
-        </is>
-      </c>
-      <c r="D43" s="9" t="inlineStr">
-        <is>
-          <t>El Imparcial</t>
-        </is>
-      </c>
-      <c r="E43" s="9" t="inlineStr">
-        <is>
-          <t>prensa</t>
-        </is>
-      </c>
-      <c r="F43" s="9" t="n"/>
-      <c r="G43" s="9" t="n"/>
-      <c r="H43" s="9" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="9" t="n"/>
-      <c r="B44" s="9" t="n"/>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>meganoticias</t>
-        </is>
-      </c>
-      <c r="D44" s="9" t="inlineStr">
-        <is>
-          <t>Meganoticias</t>
-        </is>
-      </c>
-      <c r="E44" s="9" t="inlineStr">
-        <is>
-          <t>prensa</t>
-        </is>
-      </c>
-      <c r="F44" s="9" t="n"/>
-      <c r="G44" s="9" t="n"/>
-      <c r="H44" s="9" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="9" t="n"/>
-      <c r="B45" s="9" t="n"/>
-      <c r="C45" s="9" t="inlineStr">
-        <is>
-          <t>latinus</t>
-        </is>
-      </c>
-      <c r="D45" s="9" t="inlineStr">
-        <is>
-          <t>Latinus</t>
-        </is>
-      </c>
-      <c r="E45" s="9" t="inlineStr">
-        <is>
-          <t>prensa</t>
-        </is>
-      </c>
-      <c r="F45" s="9" t="n"/>
-      <c r="G45" s="9" t="n"/>
-      <c r="H45" s="9" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="9" t="n"/>
-      <c r="B46" s="9" t="n"/>
-      <c r="C46" s="9" t="inlineStr">
-        <is>
-          <t>milenio</t>
-        </is>
-      </c>
-      <c r="D46" s="9" t="inlineStr">
-        <is>
-          <t>Milenio</t>
-        </is>
-      </c>
-      <c r="E46" s="9" t="inlineStr">
-        <is>
-          <t>prensa</t>
-        </is>
-      </c>
-      <c r="F46" s="9" t="n"/>
-      <c r="G46" s="9" t="n"/>
-      <c r="H46" s="9" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="9" t="n"/>
-      <c r="B47" s="9" t="n"/>
-      <c r="C47" s="9" t="inlineStr">
-        <is>
-          <t>quadratin</t>
-        </is>
-      </c>
-      <c r="D47" s="9" t="inlineStr">
-        <is>
-          <t>Quadratín Michoacán</t>
-        </is>
-      </c>
-      <c r="E47" s="9" t="inlineStr">
-        <is>
-          <t>prensa</t>
-        </is>
-      </c>
-      <c r="F47" s="9" t="n"/>
-      <c r="G47" s="9" t="n"/>
-      <c r="H47" s="9" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="9" t="n"/>
-      <c r="B48" s="9" t="n"/>
-      <c r="C48" s="9" t="inlineStr">
-        <is>
-          <t>elfinanciero</t>
-        </is>
-      </c>
-      <c r="D48" s="9" t="inlineStr">
-        <is>
-          <t>El Financiero</t>
-        </is>
-      </c>
-      <c r="E48" s="9" t="inlineStr">
-        <is>
-          <t>prensa</t>
-        </is>
-      </c>
-      <c r="F48" s="9" t="n"/>
-      <c r="G48" s="9" t="n"/>
-      <c r="H48" s="9" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="9" t="n"/>
-      <c r="B49" s="9" t="n"/>
-      <c r="C49" s="9" t="inlineStr">
-        <is>
-          <t>expansion</t>
-        </is>
-      </c>
-      <c r="D49" s="9" t="inlineStr">
-        <is>
-          <t>Expansión Política</t>
-        </is>
-      </c>
-      <c r="E49" s="9" t="inlineStr">
-        <is>
-          <t>prensa</t>
-        </is>
-      </c>
-      <c r="F49" s="9" t="n"/>
-      <c r="G49" s="9" t="n"/>
-      <c r="H49" s="9" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="9" t="n"/>
-      <c r="B50" s="9" t="n"/>
-      <c r="C50" s="9" t="inlineStr">
-        <is>
-          <t>unotv</t>
-        </is>
-      </c>
-      <c r="D50" s="9" t="inlineStr">
-        <is>
-          <t>UnoTV</t>
-        </is>
-      </c>
-      <c r="E50" s="9" t="inlineStr">
-        <is>
-          <t>prensa</t>
-        </is>
-      </c>
-      <c r="F50" s="9" t="n"/>
-      <c r="G50" s="9" t="n"/>
-      <c r="H50" s="9" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="9" t="n"/>
-      <c r="B51" s="9" t="n"/>
-      <c r="C51" s="9" t="inlineStr">
-        <is>
-          <t>revistaespejo</t>
-        </is>
-      </c>
-      <c r="D51" s="9" t="inlineStr">
-        <is>
-          <t>Revista Espejo (Sinaloa)</t>
-        </is>
-      </c>
-      <c r="E51" s="9" t="inlineStr">
-        <is>
-          <t>prensa</t>
-        </is>
-      </c>
-      <c r="F51" s="9" t="n"/>
-      <c r="G51" s="9" t="n"/>
-      <c r="H51" s="9" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="9" t="n"/>
-      <c r="B52" s="9" t="n"/>
-      <c r="C52" s="9" t="inlineStr">
-        <is>
-          <t>razon</t>
-        </is>
-      </c>
-      <c r="D52" s="9" t="inlineStr">
-        <is>
-          <t>La Razón de México</t>
-        </is>
-      </c>
-      <c r="E52" s="9" t="inlineStr">
-        <is>
-          <t>prensa</t>
-        </is>
-      </c>
-      <c r="F52" s="9" t="n"/>
-      <c r="G52" s="9" t="n"/>
-      <c r="H52" s="9" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="9" t="n"/>
-      <c r="B53" s="9" t="n"/>
-      <c r="C53" s="9" t="inlineStr">
-        <is>
-          <t>rsf</t>
-        </is>
-      </c>
-      <c r="D53" s="9" t="inlineStr">
-        <is>
-          <t>Reporteros Sin Fronteras (RSF)</t>
-        </is>
-      </c>
-      <c r="E53" s="9" t="inlineStr">
-        <is>
-          <t>organizacion</t>
-        </is>
-      </c>
-      <c r="F53" s="9" t="n"/>
-      <c r="G53" s="9" t="n"/>
-      <c r="H53" s="9" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="9" t="n"/>
-      <c r="B54" s="9" t="n"/>
-      <c r="C54" s="9" t="inlineStr">
-        <is>
-          <t>instituto-sinaloa</t>
-        </is>
-      </c>
-      <c r="D54" s="9" t="inlineStr">
-        <is>
-          <t>Instituto para la Protección de Personas Defensoras de Derechos Humanos y Periodistas de Sinaloa</t>
-        </is>
-      </c>
-      <c r="E54" s="9" t="inlineStr">
-        <is>
-          <t>oficial</t>
-        </is>
-      </c>
-      <c r="F54" s="9" t="n"/>
-      <c r="G54" s="9" t="n"/>
-      <c r="H54" s="9" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="9" t="n"/>
-      <c r="B55" s="9" t="n"/>
-      <c r="C55" s="9" t="inlineStr">
-        <is>
-          <t>espacio-osc</t>
-        </is>
-      </c>
-      <c r="D55" s="9" t="inlineStr">
-        <is>
-          <t>Espacio OSC para la Protección de Personas Defensoras y Periodistas</t>
-        </is>
-      </c>
-      <c r="E55" s="9" t="inlineStr">
-        <is>
-          <t>organizacion</t>
-        </is>
-      </c>
-      <c r="F55" s="9" t="n"/>
-      <c r="G55" s="9" t="n"/>
-      <c r="H55" s="9" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="9" t="n"/>
-      <c r="B56" s="9" t="n"/>
-      <c r="C56" s="9" t="inlineStr">
-        <is>
-          <t>cemda</t>
-        </is>
-      </c>
-      <c r="D56" s="9" t="inlineStr">
-        <is>
-          <t>Centro Mexicano de Derecho Ambiental (CEMDA), informe sobre personas defensoras ambientales</t>
-        </is>
-      </c>
-      <c r="E56" s="9" t="inlineStr">
-        <is>
-          <t>organizacion</t>
-        </is>
-      </c>
-      <c r="F56" s="9" t="n"/>
-      <c r="G56" s="9" t="n"/>
-      <c r="H56" s="9" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="9" t="n"/>
-      <c r="B57" s="9" t="n"/>
-      <c r="C57" s="9" t="inlineStr">
-        <is>
-          <t>asociacion-7-junio</t>
-        </is>
-      </c>
-      <c r="D57" s="9" t="inlineStr">
-        <is>
-          <t>Asociación de Periodistas y Comunicadores 7 de Junio (Sinaloa)</t>
-        </is>
-      </c>
-      <c r="E57" s="9" t="inlineStr">
-        <is>
-          <t>organizacion</t>
-        </is>
-      </c>
-      <c r="F57" s="9" t="n"/>
-      <c r="G57" s="9" t="n"/>
-      <c r="H57" s="9" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="9" t="n"/>
-      <c r="B58" s="9" t="n"/>
-      <c r="C58" s="9" t="inlineStr">
-        <is>
-          <t>excelsior</t>
-        </is>
-      </c>
-      <c r="D58" s="9" t="inlineStr">
-        <is>
-          <t>Excélsior</t>
-        </is>
-      </c>
-      <c r="E58" s="9" t="inlineStr">
-        <is>
-          <t>prensa</t>
-        </is>
-      </c>
-      <c r="F58" s="9" t="n"/>
-      <c r="G58" s="9" t="n"/>
-      <c r="H58" s="9" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="9" t="n"/>
-      <c r="B59" s="9" t="n"/>
-      <c r="C59" s="9" t="inlineStr">
-        <is>
-          <t>nmas</t>
-        </is>
-      </c>
-      <c r="D59" s="9" t="inlineStr">
-        <is>
-          <t>N+ (Televisa)</t>
-        </is>
-      </c>
-      <c r="E59" s="9" t="inlineStr">
-        <is>
-          <t>prensa</t>
-        </is>
-      </c>
-      <c r="F59" s="9" t="n"/>
-      <c r="G59" s="9" t="n"/>
-      <c r="H59" s="9" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="9" t="n"/>
-      <c r="B60" s="9" t="n"/>
-      <c r="C60" s="9" t="inlineStr">
-        <is>
-          <t>grupoanimal</t>
-        </is>
-      </c>
-      <c r="D60" s="9" t="inlineStr">
-        <is>
-          <t>Animal Político (Grupo Animal)</t>
-        </is>
-      </c>
-      <c r="E60" s="9" t="inlineStr">
-        <is>
-          <t>prensa</t>
-        </is>
-      </c>
-      <c r="F60" s="9" t="n"/>
-      <c r="G60" s="9" t="n"/>
-      <c r="H60" s="9" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="9" t="n"/>
-      <c r="B61" s="9" t="n"/>
-      <c r="C61" s="9" t="inlineStr">
-        <is>
-          <t>altavoz</t>
-        </is>
-      </c>
-      <c r="D61" s="9" t="inlineStr">
-        <is>
-          <t>Noticiero Altavoz (Sinaloa)</t>
-        </is>
-      </c>
-      <c r="E61" s="9" t="inlineStr">
-        <is>
-          <t>prensa</t>
-        </is>
-      </c>
-      <c r="F61" s="9" t="n"/>
-      <c r="G61" s="9" t="n"/>
-      <c r="H61" s="9" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="9" t="n"/>
-      <c r="B62" s="9" t="n"/>
-      <c r="C62" s="9" t="inlineStr">
-        <is>
-          <t>sectorprimario</t>
-        </is>
-      </c>
-      <c r="D62" s="9" t="inlineStr">
-        <is>
-          <t>Sector Primario Informativo (Sinaloa)</t>
-        </is>
-      </c>
-      <c r="E62" s="9" t="inlineStr">
-        <is>
-          <t>prensa</t>
-        </is>
-      </c>
-      <c r="F62" s="9" t="n"/>
-      <c r="G62" s="9" t="n"/>
-      <c r="H62" s="9" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="9" t="n"/>
-      <c r="B63" s="9" t="n"/>
-      <c r="C63" s="9" t="inlineStr">
-        <is>
-          <t>ishr</t>
-        </is>
-      </c>
-      <c r="D63" s="9" t="inlineStr">
-        <is>
-          <t>International Service for Human Rights (ISHR), Protección nacional en México</t>
-        </is>
-      </c>
-      <c r="E63" s="9" t="inlineStr">
-        <is>
-          <t>organizacion</t>
-        </is>
-      </c>
-      <c r="F63" s="9" t="n"/>
-      <c r="G63" s="9" t="n"/>
-      <c r="H63" s="9" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="9" t="n"/>
-      <c r="B64" s="9" t="n"/>
-      <c r="C64" s="9" t="inlineStr">
-        <is>
-          <t>inegi-censos</t>
-        </is>
-      </c>
-      <c r="D64" s="9" t="inlineStr">
-        <is>
-          <t>INEGI, Censos y Conteos de Población y Vivienda (1990-2020) y Encuesta Intercensal 2015</t>
-        </is>
-      </c>
-      <c r="E64" s="9" t="inlineStr">
-        <is>
-          <t>oficial</t>
-        </is>
-      </c>
-      <c r="F64" s="9" t="n"/>
-      <c r="G64" s="9" t="n"/>
-      <c r="H64" s="9" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/plantillas/eventos.xlsx
+++ b/plantillas/eventos.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>sexo</t>
+          <t>genero</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -19008,7 +19008,7 @@
       </c>
       <c r="E234" s="3" t="inlineStr">
         <is>
-          <t>femenino</t>
+          <t>lgbt</t>
         </is>
       </c>
       <c r="F234" s="3" t="inlineStr">
@@ -19751,7 +19751,7 @@
       </c>
       <c r="E243" s="3" t="inlineStr">
         <is>
-          <t>femenino</t>
+          <t>lgbt</t>
         </is>
       </c>
       <c r="F243" s="3" t="inlineStr">
@@ -37109,7 +37109,7 @@
       <formula1>=catalogos!$G$2:$G$9</formula1>
     </dataValidation>
     <dataValidation sqref="E2:E1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Valor no permitido" type="list">
-      <formula1>=catalogos!$H$2:$H$5</formula1>
+      <formula1>=catalogos!$H$2:$H$6</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Valor no permitido" type="list">
       <formula1>=catalogos!$I$2:$I$10</formula1>
@@ -37194,7 +37194,7 @@
       </c>
       <c r="H1" s="8" t="inlineStr">
         <is>
-          <t>sexo</t>
+          <t>genero</t>
         </is>
       </c>
       <c r="I1" s="8" t="inlineStr">
@@ -37335,7 +37335,7 @@
       </c>
       <c r="H4" s="9" t="inlineStr">
         <is>
-          <t>no determinado</t>
+          <t>lgbt</t>
         </is>
       </c>
       <c r="I4" s="9" t="inlineStr">
@@ -37378,7 +37378,7 @@
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>no aplica</t>
+          <t>no determinado</t>
         </is>
       </c>
       <c r="I5" s="9" t="inlineStr">
@@ -37419,7 +37419,11 @@
           <t>acoso_judicial</t>
         </is>
       </c>
-      <c r="H6" s="9" t="n"/>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>no aplica</t>
+        </is>
+      </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
           <t>lgbt</t>
@@ -38373,7 +38377,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>sexo: femenino, masculino, no determinado (persona no identificada) o no aplica (cifras e informes).</t>
+          <t>genero: femenino, masculino, lgbt, no determinado (persona no identificada) o no aplica (cifras e informes).</t>
         </is>
       </c>
     </row>
